--- a/VerveStacks_NGA_grids_kan/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_NGA_grids_kan/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NGA_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E8EF3B14-9273-4BD6-A37D-01982B1A002A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B116DB73-3C33-4455-BCB7-4032B2FDA50B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24578,7 +24578,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15E6F76F-AA31-4310-B232-F900661E6B29}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{794CAA10-11EA-4364-937F-D9B0D7A76A85}">
   <dimension ref="B9:H145"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -27316,7 +27316,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D56BB41-E9F4-48A9-BB44-63EDF3928C1C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1BCACFE-A23F-4E23-A884-CA3C6C9432E6}">
   <dimension ref="B9:L145"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_NGA_grids_kan/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_NGA_grids_kan/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NGA_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B116DB73-3C33-4455-BCB7-4032B2FDA50B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7B5F88A9-FBCA-41F6-B108-BF7FE5A10481}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24578,7 +24578,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{794CAA10-11EA-4364-937F-D9B0D7A76A85}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0138AFE7-544F-41FE-BD3C-380014FB1A8F}">
   <dimension ref="B9:H145"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -27316,7 +27316,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1BCACFE-A23F-4E23-A884-CA3C6C9432E6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0D089EA-DA44-42D6-94D7-5FF8F138B66A}">
   <dimension ref="B9:L145"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_NGA_grids_kan/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_NGA_grids_kan/ReportDefs_vervestacks.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NGA_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7B5F88A9-FBCA-41F6-B108-BF7FE5A10481}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{726CE689-94BB-4D38-985F-3731891D0DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ScenMap" sheetId="56" r:id="rId1"/>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5943" uniqueCount="920">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6103" uniqueCount="936">
   <si>
     <t>Unit</t>
   </si>
@@ -2843,6 +2843,54 @@
   </si>
   <si>
     <t>NGA-elc_wof_010</t>
+  </si>
+  <si>
+    <t>South-East</t>
+  </si>
+  <si>
+    <t>North-East</t>
+  </si>
+  <si>
+    <t>North-Central</t>
+  </si>
+  <si>
+    <t>South-South</t>
+  </si>
+  <si>
+    <t>North-West</t>
+  </si>
+  <si>
+    <t>South-West</t>
+  </si>
+  <si>
+    <t>Yola</t>
+  </si>
+  <si>
+    <t>Jos</t>
+  </si>
+  <si>
+    <t>Port Harcourt</t>
+  </si>
+  <si>
+    <t>Benin</t>
+  </si>
+  <si>
+    <t>Abuja</t>
+  </si>
+  <si>
+    <t>Ibadan</t>
+  </si>
+  <si>
+    <t>Ikeja</t>
+  </si>
+  <si>
+    <t>reg_geopol</t>
+  </si>
+  <si>
+    <t>reg_discos</t>
+  </si>
+  <si>
+    <t>~region_map</t>
   </si>
 </sst>
 </file>
@@ -3051,7 +3099,7 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
@@ -3062,6 +3110,12 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="20">
@@ -27317,10 +27371,15 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0D089EA-DA44-42D6-94D7-5FF8F138B66A}">
-  <dimension ref="B9:L145"/>
+  <dimension ref="B9:R145"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="16" max="16" width="10.1328125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="19.9296875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.59765625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="9" spans="2:12">
+    <row r="9" spans="2:18">
       <c r="B9" t="s">
         <v>59</v>
       </c>
@@ -27330,8 +27389,11 @@
       <c r="J9" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="10" spans="2:12">
+      <c r="P9" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="10" spans="2:18">
       <c r="B10" t="s">
         <v>48</v>
       </c>
@@ -27359,8 +27421,17 @@
       <c r="L10" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="11" spans="2:12">
+      <c r="P10" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q10" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="R10" s="9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="2:18">
       <c r="B11" t="s">
         <v>475</v>
       </c>
@@ -27388,8 +27459,17 @@
       <c r="L11" t="s">
         <v>647</v>
       </c>
-    </row>
-    <row r="12" spans="2:12">
+      <c r="P11" s="10" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q11" s="10" t="s">
+        <v>627</v>
+      </c>
+      <c r="R11" s="10" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="12" spans="2:18">
       <c r="B12" t="s">
         <v>475</v>
       </c>
@@ -27417,8 +27497,17 @@
       <c r="L12" t="s">
         <v>648</v>
       </c>
-    </row>
-    <row r="13" spans="2:12">
+      <c r="P12" s="10" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q12" s="10" t="s">
+        <v>618</v>
+      </c>
+      <c r="R12" s="10" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="13" spans="2:18">
       <c r="B13" t="s">
         <v>475</v>
       </c>
@@ -27446,8 +27535,17 @@
       <c r="L13" t="s">
         <v>649</v>
       </c>
-    </row>
-    <row r="14" spans="2:12">
+      <c r="P13" s="10" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q13" s="10" t="s">
+        <v>636</v>
+      </c>
+      <c r="R13" s="10" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="14" spans="2:18">
       <c r="B14" t="s">
         <v>475</v>
       </c>
@@ -27475,8 +27573,17 @@
       <c r="L14" t="s">
         <v>650</v>
       </c>
-    </row>
-    <row r="15" spans="2:12">
+      <c r="P14" s="10" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q14" s="10" t="s">
+        <v>641</v>
+      </c>
+      <c r="R14" s="10" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="15" spans="2:18">
       <c r="B15" t="s">
         <v>475</v>
       </c>
@@ -27504,8 +27611,17 @@
       <c r="L15" t="s">
         <v>651</v>
       </c>
-    </row>
-    <row r="16" spans="2:12">
+      <c r="P15" s="10" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q15" s="10" t="s">
+        <v>632</v>
+      </c>
+      <c r="R15" s="10" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="16" spans="2:18">
       <c r="B16" t="s">
         <v>475</v>
       </c>
@@ -27533,8 +27649,17 @@
       <c r="L16" t="s">
         <v>652</v>
       </c>
-    </row>
-    <row r="17" spans="2:12">
+      <c r="P16" s="10" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q16" s="10" t="s">
+        <v>635</v>
+      </c>
+      <c r="R16" s="10" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="17" spans="2:18">
       <c r="B17" t="s">
         <v>475</v>
       </c>
@@ -27562,8 +27687,17 @@
       <c r="L17" t="s">
         <v>653</v>
       </c>
-    </row>
-    <row r="18" spans="2:12">
+      <c r="P17" s="10" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q17" s="10" t="s">
+        <v>629</v>
+      </c>
+      <c r="R17" s="10" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="18" spans="2:18">
       <c r="B18" t="s">
         <v>475</v>
       </c>
@@ -27591,8 +27725,17 @@
       <c r="L18" t="s">
         <v>654</v>
       </c>
-    </row>
-    <row r="19" spans="2:12">
+      <c r="P18" s="10" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q18" s="10" t="s">
+        <v>624</v>
+      </c>
+      <c r="R18" s="10" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="19" spans="2:18">
       <c r="B19" t="s">
         <v>475</v>
       </c>
@@ -27620,8 +27763,17 @@
       <c r="L19" t="s">
         <v>655</v>
       </c>
-    </row>
-    <row r="20" spans="2:12">
+      <c r="P19" s="10" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q19" s="10" t="s">
+        <v>631</v>
+      </c>
+      <c r="R19" s="10" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="20" spans="2:18">
       <c r="B20" t="s">
         <v>475</v>
       </c>
@@ -27649,8 +27801,17 @@
       <c r="L20" t="s">
         <v>656</v>
       </c>
-    </row>
-    <row r="21" spans="2:12">
+      <c r="P20" s="10" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q20" s="10" t="s">
+        <v>633</v>
+      </c>
+      <c r="R20" s="10" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="21" spans="2:18">
       <c r="B21" t="s">
         <v>475</v>
       </c>
@@ -27678,8 +27839,17 @@
       <c r="L21" t="s">
         <v>657</v>
       </c>
-    </row>
-    <row r="22" spans="2:12">
+      <c r="P21" s="10" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q21" s="10" t="s">
+        <v>642</v>
+      </c>
+      <c r="R21" s="10" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="22" spans="2:18">
       <c r="B22" t="s">
         <v>475</v>
       </c>
@@ -27707,8 +27877,17 @@
       <c r="L22" t="s">
         <v>658</v>
       </c>
-    </row>
-    <row r="23" spans="2:12">
+      <c r="P22" s="10" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q22" s="10" t="s">
+        <v>612</v>
+      </c>
+      <c r="R22" s="10" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="23" spans="2:18">
       <c r="B23" t="s">
         <v>475</v>
       </c>
@@ -27736,8 +27915,17 @@
       <c r="L23" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="24" spans="2:12">
+      <c r="P23" s="10" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q23" s="10" t="s">
+        <v>620</v>
+      </c>
+      <c r="R23" s="10" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="24" spans="2:18">
       <c r="B24" t="s">
         <v>475</v>
       </c>
@@ -27765,8 +27953,17 @@
       <c r="L24" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="25" spans="2:12">
+      <c r="P24" s="10" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q24" s="10" t="s">
+        <v>638</v>
+      </c>
+      <c r="R24" s="10" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="25" spans="2:18">
       <c r="B25" t="s">
         <v>475</v>
       </c>
@@ -27794,8 +27991,17 @@
       <c r="L25" t="s">
         <v>661</v>
       </c>
-    </row>
-    <row r="26" spans="2:12">
+      <c r="P25" s="10" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q25" s="10" t="s">
+        <v>628</v>
+      </c>
+      <c r="R25" s="10" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="26" spans="2:18">
       <c r="B26" t="s">
         <v>475</v>
       </c>
@@ -27823,8 +28029,17 @@
       <c r="L26" t="s">
         <v>662</v>
       </c>
-    </row>
-    <row r="27" spans="2:12">
+      <c r="P26" s="10" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q26" s="10" t="s">
+        <v>615</v>
+      </c>
+      <c r="R26" s="10" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="27" spans="2:18">
       <c r="B27" t="s">
         <v>475</v>
       </c>
@@ -27852,8 +28067,17 @@
       <c r="L27" t="s">
         <v>663</v>
       </c>
-    </row>
-    <row r="28" spans="2:12">
+      <c r="P27" s="10" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q27" s="10" t="s">
+        <v>623</v>
+      </c>
+      <c r="R27" s="10" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="28" spans="2:18">
       <c r="B28" t="s">
         <v>475</v>
       </c>
@@ -27881,8 +28105,17 @@
       <c r="L28" t="s">
         <v>664</v>
       </c>
-    </row>
-    <row r="29" spans="2:12">
+      <c r="P28" s="10" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q28" s="10" t="s">
+        <v>614</v>
+      </c>
+      <c r="R28" s="10" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="29" spans="2:18">
       <c r="B29" t="s">
         <v>475</v>
       </c>
@@ -27910,8 +28143,17 @@
       <c r="L29" t="s">
         <v>665</v>
       </c>
-    </row>
-    <row r="30" spans="2:12">
+      <c r="P29" s="10" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q29" s="10" t="s">
+        <v>613</v>
+      </c>
+      <c r="R29" s="10" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="30" spans="2:18">
       <c r="B30" t="s">
         <v>475</v>
       </c>
@@ -27939,8 +28181,17 @@
       <c r="L30" t="s">
         <v>666</v>
       </c>
-    </row>
-    <row r="31" spans="2:12">
+      <c r="P30" s="10" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q30" s="10" t="s">
+        <v>622</v>
+      </c>
+      <c r="R30" s="10" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="31" spans="2:18">
       <c r="B31" t="s">
         <v>475</v>
       </c>
@@ -27968,8 +28219,17 @@
       <c r="L31" t="s">
         <v>667</v>
       </c>
-    </row>
-    <row r="32" spans="2:12">
+      <c r="P31" s="10" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q31" s="10" t="s">
+        <v>634</v>
+      </c>
+      <c r="R31" s="10" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="32" spans="2:18">
       <c r="B32" t="s">
         <v>475</v>
       </c>
@@ -27997,8 +28257,17 @@
       <c r="L32" t="s">
         <v>668</v>
       </c>
-    </row>
-    <row r="33" spans="2:12">
+      <c r="P32" s="10" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q32" s="10" t="s">
+        <v>621</v>
+      </c>
+      <c r="R32" s="10" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18">
       <c r="B33" t="s">
         <v>475</v>
       </c>
@@ -28026,8 +28295,17 @@
       <c r="L33" t="s">
         <v>669</v>
       </c>
-    </row>
-    <row r="34" spans="2:12">
+      <c r="P33" s="10" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q33" s="10" t="s">
+        <v>630</v>
+      </c>
+      <c r="R33" s="10" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18">
       <c r="B34" t="s">
         <v>475</v>
       </c>
@@ -28055,8 +28333,17 @@
       <c r="L34" t="s">
         <v>670</v>
       </c>
-    </row>
-    <row r="35" spans="2:12">
+      <c r="P34" s="10" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q34" s="10" t="s">
+        <v>616</v>
+      </c>
+      <c r="R34" s="10" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18">
       <c r="B35" t="s">
         <v>475</v>
       </c>
@@ -28084,8 +28371,17 @@
       <c r="L35" t="s">
         <v>671</v>
       </c>
-    </row>
-    <row r="36" spans="2:12">
+      <c r="P35" s="10" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q35" s="10" t="s">
+        <v>637</v>
+      </c>
+      <c r="R35" s="10" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="36" spans="2:18">
       <c r="B36" t="s">
         <v>475</v>
       </c>
@@ -28113,8 +28409,17 @@
       <c r="L36" t="s">
         <v>672</v>
       </c>
-    </row>
-    <row r="37" spans="2:12">
+      <c r="P36" s="10" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q36" s="10" t="s">
+        <v>643</v>
+      </c>
+      <c r="R36" s="10" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18">
       <c r="B37" t="s">
         <v>475</v>
       </c>
@@ -28142,8 +28447,17 @@
       <c r="L37" t="s">
         <v>673</v>
       </c>
-    </row>
-    <row r="38" spans="2:12">
+      <c r="P37" s="10" t="s">
+        <v>934</v>
+      </c>
+      <c r="Q37" s="10" t="s">
+        <v>627</v>
+      </c>
+      <c r="R37" s="10" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="38" spans="2:18">
       <c r="B38" t="s">
         <v>475</v>
       </c>
@@ -28171,8 +28485,17 @@
       <c r="L38" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="39" spans="2:12">
+      <c r="P38" s="10" t="s">
+        <v>934</v>
+      </c>
+      <c r="Q38" s="10" t="s">
+        <v>618</v>
+      </c>
+      <c r="R38" s="10" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="39" spans="2:18">
       <c r="B39" t="s">
         <v>475</v>
       </c>
@@ -28200,8 +28523,17 @@
       <c r="L39" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="40" spans="2:12">
+      <c r="P39" s="10" t="s">
+        <v>934</v>
+      </c>
+      <c r="Q39" s="10" t="s">
+        <v>636</v>
+      </c>
+      <c r="R39" s="10" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="40" spans="2:18">
       <c r="B40" t="s">
         <v>475</v>
       </c>
@@ -28229,8 +28561,17 @@
       <c r="L40" t="s">
         <v>676</v>
       </c>
-    </row>
-    <row r="41" spans="2:12">
+      <c r="P40" s="10" t="s">
+        <v>934</v>
+      </c>
+      <c r="Q40" s="10" t="s">
+        <v>641</v>
+      </c>
+      <c r="R40" s="10" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="41" spans="2:18">
       <c r="B41" t="s">
         <v>475</v>
       </c>
@@ -28258,8 +28599,17 @@
       <c r="L41" t="s">
         <v>677</v>
       </c>
-    </row>
-    <row r="42" spans="2:12">
+      <c r="P41" s="10" t="s">
+        <v>934</v>
+      </c>
+      <c r="Q41" s="10" t="s">
+        <v>632</v>
+      </c>
+      <c r="R41" s="10" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18">
       <c r="B42" t="s">
         <v>475</v>
       </c>
@@ -28287,8 +28637,17 @@
       <c r="L42" t="s">
         <v>678</v>
       </c>
-    </row>
-    <row r="43" spans="2:12">
+      <c r="P42" s="10" t="s">
+        <v>934</v>
+      </c>
+      <c r="Q42" s="10" t="s">
+        <v>635</v>
+      </c>
+      <c r="R42" s="10" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18">
       <c r="B43" t="s">
         <v>475</v>
       </c>
@@ -28316,8 +28675,17 @@
       <c r="L43" t="s">
         <v>679</v>
       </c>
-    </row>
-    <row r="44" spans="2:12">
+      <c r="P43" s="10" t="s">
+        <v>934</v>
+      </c>
+      <c r="Q43" s="10" t="s">
+        <v>629</v>
+      </c>
+      <c r="R43" s="10" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18">
       <c r="B44" t="s">
         <v>475</v>
       </c>
@@ -28345,8 +28713,17 @@
       <c r="L44" t="s">
         <v>680</v>
       </c>
-    </row>
-    <row r="45" spans="2:12">
+      <c r="P44" s="10" t="s">
+        <v>934</v>
+      </c>
+      <c r="Q44" s="10" t="s">
+        <v>624</v>
+      </c>
+      <c r="R44" s="10" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18">
       <c r="B45" t="s">
         <v>475</v>
       </c>
@@ -28374,8 +28751,17 @@
       <c r="L45" t="s">
         <v>681</v>
       </c>
-    </row>
-    <row r="46" spans="2:12">
+      <c r="P45" s="10" t="s">
+        <v>934</v>
+      </c>
+      <c r="Q45" s="10" t="s">
+        <v>631</v>
+      </c>
+      <c r="R45" s="10" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18">
       <c r="B46" t="s">
         <v>475</v>
       </c>
@@ -28403,8 +28789,17 @@
       <c r="L46" t="s">
         <v>682</v>
       </c>
-    </row>
-    <row r="47" spans="2:12">
+      <c r="P46" s="10" t="s">
+        <v>934</v>
+      </c>
+      <c r="Q46" s="10" t="s">
+        <v>633</v>
+      </c>
+      <c r="R46" s="10" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18">
       <c r="B47" t="s">
         <v>475</v>
       </c>
@@ -28432,8 +28827,17 @@
       <c r="L47" t="s">
         <v>683</v>
       </c>
-    </row>
-    <row r="48" spans="2:12">
+      <c r="P47" s="10" t="s">
+        <v>934</v>
+      </c>
+      <c r="Q47" s="10" t="s">
+        <v>642</v>
+      </c>
+      <c r="R47" s="10" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18">
       <c r="B48" t="s">
         <v>475</v>
       </c>
@@ -28461,8 +28865,17 @@
       <c r="L48" t="s">
         <v>684</v>
       </c>
-    </row>
-    <row r="49" spans="2:12">
+      <c r="P48" s="10" t="s">
+        <v>934</v>
+      </c>
+      <c r="Q48" s="10" t="s">
+        <v>612</v>
+      </c>
+      <c r="R48" s="10" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="49" spans="2:18">
       <c r="B49" t="s">
         <v>475</v>
       </c>
@@ -28490,8 +28903,17 @@
       <c r="L49" t="s">
         <v>685</v>
       </c>
-    </row>
-    <row r="50" spans="2:12">
+      <c r="P49" s="10" t="s">
+        <v>934</v>
+      </c>
+      <c r="Q49" s="10" t="s">
+        <v>620</v>
+      </c>
+      <c r="R49" s="10" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="50" spans="2:18">
       <c r="B50" t="s">
         <v>475</v>
       </c>
@@ -28519,8 +28941,17 @@
       <c r="L50" t="s">
         <v>686</v>
       </c>
-    </row>
-    <row r="51" spans="2:12">
+      <c r="P50" s="10" t="s">
+        <v>934</v>
+      </c>
+      <c r="Q50" s="10" t="s">
+        <v>638</v>
+      </c>
+      <c r="R50" s="10" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="51" spans="2:18">
       <c r="B51" t="s">
         <v>475</v>
       </c>
@@ -28548,8 +28979,17 @@
       <c r="L51" t="s">
         <v>687</v>
       </c>
-    </row>
-    <row r="52" spans="2:12">
+      <c r="P51" s="10" t="s">
+        <v>934</v>
+      </c>
+      <c r="Q51" s="10" t="s">
+        <v>628</v>
+      </c>
+      <c r="R51" s="10" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="52" spans="2:18">
       <c r="B52" t="s">
         <v>475</v>
       </c>
@@ -28577,8 +29017,17 @@
       <c r="L52" t="s">
         <v>688</v>
       </c>
-    </row>
-    <row r="53" spans="2:12">
+      <c r="P52" s="10" t="s">
+        <v>934</v>
+      </c>
+      <c r="Q52" s="10" t="s">
+        <v>615</v>
+      </c>
+      <c r="R52" s="10" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="53" spans="2:18">
       <c r="B53" t="s">
         <v>475</v>
       </c>
@@ -28606,8 +29055,17 @@
       <c r="L53" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="54" spans="2:12">
+      <c r="P53" s="10" t="s">
+        <v>934</v>
+      </c>
+      <c r="Q53" s="10" t="s">
+        <v>623</v>
+      </c>
+      <c r="R53" s="10" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="54" spans="2:18">
       <c r="B54" t="s">
         <v>475</v>
       </c>
@@ -28635,8 +29093,17 @@
       <c r="L54" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="55" spans="2:12">
+      <c r="P54" s="10" t="s">
+        <v>934</v>
+      </c>
+      <c r="Q54" s="10" t="s">
+        <v>614</v>
+      </c>
+      <c r="R54" s="10" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="55" spans="2:18">
       <c r="B55" t="s">
         <v>475</v>
       </c>
@@ -28664,8 +29131,17 @@
       <c r="L55" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="56" spans="2:12">
+      <c r="P55" s="10" t="s">
+        <v>934</v>
+      </c>
+      <c r="Q55" s="10" t="s">
+        <v>613</v>
+      </c>
+      <c r="R55" s="10" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="56" spans="2:18">
       <c r="B56" t="s">
         <v>475</v>
       </c>
@@ -28693,8 +29169,17 @@
       <c r="L56" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="57" spans="2:12">
+      <c r="P56" s="10" t="s">
+        <v>934</v>
+      </c>
+      <c r="Q56" s="10" t="s">
+        <v>622</v>
+      </c>
+      <c r="R56" s="10" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="57" spans="2:18">
       <c r="B57" t="s">
         <v>475</v>
       </c>
@@ -28722,8 +29207,17 @@
       <c r="L57" t="s">
         <v>693</v>
       </c>
-    </row>
-    <row r="58" spans="2:12">
+      <c r="P57" s="10" t="s">
+        <v>934</v>
+      </c>
+      <c r="Q57" s="10" t="s">
+        <v>634</v>
+      </c>
+      <c r="R57" s="10" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="58" spans="2:18">
       <c r="B58" t="s">
         <v>475</v>
       </c>
@@ -28751,8 +29245,17 @@
       <c r="L58" t="s">
         <v>694</v>
       </c>
-    </row>
-    <row r="59" spans="2:12">
+      <c r="P58" s="10" t="s">
+        <v>934</v>
+      </c>
+      <c r="Q58" s="10" t="s">
+        <v>621</v>
+      </c>
+      <c r="R58" s="10" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="59" spans="2:18">
       <c r="B59" t="s">
         <v>475</v>
       </c>
@@ -28780,8 +29283,17 @@
       <c r="L59" t="s">
         <v>695</v>
       </c>
-    </row>
-    <row r="60" spans="2:12">
+      <c r="P59" s="10" t="s">
+        <v>934</v>
+      </c>
+      <c r="Q59" s="10" t="s">
+        <v>630</v>
+      </c>
+      <c r="R59" s="10" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="60" spans="2:18">
       <c r="B60" t="s">
         <v>475</v>
       </c>
@@ -28809,8 +29321,17 @@
       <c r="L60" t="s">
         <v>696</v>
       </c>
-    </row>
-    <row r="61" spans="2:12">
+      <c r="P60" s="10" t="s">
+        <v>934</v>
+      </c>
+      <c r="Q60" s="10" t="s">
+        <v>616</v>
+      </c>
+      <c r="R60" s="10" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="61" spans="2:18">
       <c r="B61" t="s">
         <v>475</v>
       </c>
@@ -28838,8 +29359,17 @@
       <c r="L61" t="s">
         <v>697</v>
       </c>
-    </row>
-    <row r="62" spans="2:12">
+      <c r="P61" s="10" t="s">
+        <v>934</v>
+      </c>
+      <c r="Q61" s="10" t="s">
+        <v>637</v>
+      </c>
+      <c r="R61" s="10" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="62" spans="2:18">
       <c r="B62" t="s">
         <v>475</v>
       </c>
@@ -28867,8 +29397,17 @@
       <c r="L62" t="s">
         <v>698</v>
       </c>
-    </row>
-    <row r="63" spans="2:12">
+      <c r="P62" s="10" t="s">
+        <v>934</v>
+      </c>
+      <c r="Q62" s="10" t="s">
+        <v>643</v>
+      </c>
+      <c r="R62" s="10" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="63" spans="2:18">
       <c r="B63" t="s">
         <v>475</v>
       </c>
@@ -28897,7 +29436,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="64" spans="2:12">
+    <row r="64" spans="2:18">
       <c r="B64" t="s">
         <v>475</v>
       </c>

--- a/VerveStacks_NGA_grids_kan/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_NGA_grids_kan/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NGA_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{726CE689-94BB-4D38-985F-3731891D0DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95995D16-F110-4934-AE85-F946516ACD78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6103" uniqueCount="936">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6698" uniqueCount="940">
   <si>
     <t>Unit</t>
   </si>
@@ -2887,10 +2887,22 @@
     <t>reg_geopol</t>
   </si>
   <si>
-    <t>reg_discos</t>
-  </si>
-  <si>
-    <t>~region_map</t>
+    <t>Grouping</t>
+  </si>
+  <si>
+    <t>State</t>
+  </si>
+  <si>
+    <t>GroupName</t>
+  </si>
+  <si>
+    <t>Geopolitical</t>
+  </si>
+  <si>
+    <t>DisCos</t>
+  </si>
+  <si>
+    <t>reg_discom</t>
   </si>
 </sst>
 </file>
@@ -3108,14 +3120,14 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="18"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="19"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="20">
@@ -22861,10 +22873,10 @@
       <c r="N4" t="s">
         <v>74</v>
       </c>
-      <c r="T4" s="8" t="s">
+      <c r="T4" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="U4" s="8"/>
+      <c r="U4" s="10"/>
     </row>
     <row r="5" spans="1:21">
       <c r="A5" t="s">
@@ -27371,15 +27383,17 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0D089EA-DA44-42D6-94D7-5FF8F138B66A}">
-  <dimension ref="B9:R145"/>
+  <dimension ref="B9:AD145"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="16" max="16" width="10.1328125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="19.9296875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="11.59765625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.1328125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="9" spans="2:18">
+    <row r="9" spans="2:30">
       <c r="B9" t="s">
         <v>59</v>
       </c>
@@ -27389,11 +27403,14 @@
       <c r="J9" t="s">
         <v>68</v>
       </c>
-      <c r="P9" t="s">
-        <v>935</v>
-      </c>
-    </row>
-    <row r="10" spans="2:18">
+      <c r="O9" t="s">
+        <v>59</v>
+      </c>
+      <c r="S9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="10" spans="2:30">
       <c r="B10" t="s">
         <v>48</v>
       </c>
@@ -27421,17 +27438,26 @@
       <c r="L10" t="s">
         <v>50</v>
       </c>
-      <c r="P10" s="9" t="s">
+      <c r="O10" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="P10" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="Q10" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="R10" s="9" t="s">
+      <c r="Q10" s="8" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="11" spans="2:18">
+      <c r="S10" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="T10" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="U10" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="2:30">
       <c r="B11" t="s">
         <v>475</v>
       </c>
@@ -27459,17 +27485,37 @@
       <c r="L11" t="s">
         <v>647</v>
       </c>
-      <c r="P11" s="10" t="s">
+      <c r="O11" s="9" t="s">
+        <v>476</v>
+      </c>
+      <c r="P11" s="9" t="s">
         <v>933</v>
       </c>
-      <c r="Q11" s="10" t="s">
-        <v>627</v>
-      </c>
-      <c r="R11" s="10" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="12" spans="2:18">
+      <c r="Q11" s="9" t="str">
+        <f>VLOOKUP(H11,$Y$12:$Z$45,2,FALSE)</f>
+        <v>North-West</v>
+      </c>
+      <c r="S11" s="9" t="s">
+        <v>476</v>
+      </c>
+      <c r="T11" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U11" s="9" t="str">
+        <f>VLOOKUP(H11,$AC$12:$AD$45,2,FALSE)</f>
+        <v>Kaduna</v>
+      </c>
+      <c r="X11" s="8" t="s">
+        <v>934</v>
+      </c>
+      <c r="Y11" s="8" t="s">
+        <v>935</v>
+      </c>
+      <c r="Z11" s="8" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="12" spans="2:30">
       <c r="B12" t="s">
         <v>475</v>
       </c>
@@ -27497,17 +27543,46 @@
       <c r="L12" t="s">
         <v>648</v>
       </c>
-      <c r="P12" s="10" t="s">
+      <c r="O12" s="9" t="s">
+        <v>477</v>
+      </c>
+      <c r="P12" s="9" t="s">
         <v>933</v>
       </c>
-      <c r="Q12" s="10" t="s">
-        <v>618</v>
-      </c>
-      <c r="R12" s="10" t="s">
-        <v>921</v>
-      </c>
-    </row>
-    <row r="13" spans="2:18">
+      <c r="Q12" s="9" t="str">
+        <f t="shared" ref="Q12:Q75" si="0">VLOOKUP(H12,$Y$12:$Z$45,2,FALSE)</f>
+        <v>North-Central</v>
+      </c>
+      <c r="S12" s="9" t="s">
+        <v>477</v>
+      </c>
+      <c r="T12" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U12" s="9" t="str">
+        <f t="shared" ref="U12:U75" si="1">VLOOKUP(H12,$AC$12:$AD$45,2,FALSE)</f>
+        <v>Abuja</v>
+      </c>
+      <c r="X12" s="9" t="s">
+        <v>937</v>
+      </c>
+      <c r="Y12" s="9" t="s">
+        <v>612</v>
+      </c>
+      <c r="Z12" s="9" t="s">
+        <v>924</v>
+      </c>
+      <c r="AB12" s="9" t="s">
+        <v>938</v>
+      </c>
+      <c r="AC12" s="9" t="s">
+        <v>612</v>
+      </c>
+      <c r="AD12" s="9" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="13" spans="2:30">
       <c r="B13" t="s">
         <v>475</v>
       </c>
@@ -27535,17 +27610,46 @@
       <c r="L13" t="s">
         <v>649</v>
       </c>
-      <c r="P13" s="10" t="s">
+      <c r="O13" s="9" t="s">
+        <v>478</v>
+      </c>
+      <c r="P13" s="9" t="s">
         <v>933</v>
       </c>
-      <c r="Q13" s="10" t="s">
-        <v>636</v>
-      </c>
-      <c r="R13" s="10" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="14" spans="2:18">
+      <c r="Q13" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>South-West</v>
+      </c>
+      <c r="S13" s="9" t="s">
+        <v>478</v>
+      </c>
+      <c r="T13" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U13" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Ikeja</v>
+      </c>
+      <c r="X13" s="9" t="s">
+        <v>937</v>
+      </c>
+      <c r="Y13" s="9" t="s">
+        <v>613</v>
+      </c>
+      <c r="Z13" s="9" t="s">
+        <v>922</v>
+      </c>
+      <c r="AB13" s="9" t="s">
+        <v>938</v>
+      </c>
+      <c r="AC13" s="9" t="s">
+        <v>613</v>
+      </c>
+      <c r="AD13" s="9" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="14" spans="2:30">
       <c r="B14" t="s">
         <v>475</v>
       </c>
@@ -27573,17 +27677,46 @@
       <c r="L14" t="s">
         <v>650</v>
       </c>
-      <c r="P14" s="10" t="s">
+      <c r="O14" s="9" t="s">
+        <v>479</v>
+      </c>
+      <c r="P14" s="9" t="s">
         <v>933</v>
       </c>
-      <c r="Q14" s="10" t="s">
-        <v>641</v>
-      </c>
-      <c r="R14" s="10" t="s">
-        <v>921</v>
-      </c>
-    </row>
-    <row r="15" spans="2:18">
+      <c r="Q14" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>North-Central</v>
+      </c>
+      <c r="S14" s="9" t="s">
+        <v>479</v>
+      </c>
+      <c r="T14" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U14" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Abuja</v>
+      </c>
+      <c r="X14" s="9" t="s">
+        <v>937</v>
+      </c>
+      <c r="Y14" s="9" t="s">
+        <v>614</v>
+      </c>
+      <c r="Z14" s="9" t="s">
+        <v>925</v>
+      </c>
+      <c r="AB14" s="9" t="s">
+        <v>938</v>
+      </c>
+      <c r="AC14" s="9" t="s">
+        <v>614</v>
+      </c>
+      <c r="AD14" s="9" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="15" spans="2:30">
       <c r="B15" t="s">
         <v>475</v>
       </c>
@@ -27611,17 +27744,46 @@
       <c r="L15" t="s">
         <v>651</v>
       </c>
-      <c r="P15" s="10" t="s">
+      <c r="O15" s="9" t="s">
+        <v>480</v>
+      </c>
+      <c r="P15" s="9" t="s">
         <v>933</v>
       </c>
-      <c r="Q15" s="10" t="s">
-        <v>632</v>
-      </c>
-      <c r="R15" s="10" t="s">
+      <c r="Q15" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>North-Central</v>
+      </c>
+      <c r="S15" s="9" t="s">
+        <v>480</v>
+      </c>
+      <c r="T15" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U15" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Jos</v>
+      </c>
+      <c r="X15" s="9" t="s">
+        <v>937</v>
+      </c>
+      <c r="Y15" s="9" t="s">
+        <v>615</v>
+      </c>
+      <c r="Z15" s="9" t="s">
         <v>922</v>
       </c>
-    </row>
-    <row r="16" spans="2:18">
+      <c r="AB15" s="9" t="s">
+        <v>938</v>
+      </c>
+      <c r="AC15" s="9" t="s">
+        <v>615</v>
+      </c>
+      <c r="AD15" s="9" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="16" spans="2:30">
       <c r="B16" t="s">
         <v>475</v>
       </c>
@@ -27649,17 +27811,46 @@
       <c r="L16" t="s">
         <v>652</v>
       </c>
-      <c r="P16" s="10" t="s">
+      <c r="O16" s="9" t="s">
+        <v>481</v>
+      </c>
+      <c r="P16" s="9" t="s">
         <v>933</v>
       </c>
-      <c r="Q16" s="10" t="s">
-        <v>635</v>
-      </c>
-      <c r="R16" s="10" t="s">
-        <v>921</v>
-      </c>
-    </row>
-    <row r="17" spans="2:18">
+      <c r="Q16" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>North-East</v>
+      </c>
+      <c r="S16" s="9" t="s">
+        <v>481</v>
+      </c>
+      <c r="T16" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U16" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Jos</v>
+      </c>
+      <c r="X16" s="9" t="s">
+        <v>937</v>
+      </c>
+      <c r="Y16" s="9" t="s">
+        <v>616</v>
+      </c>
+      <c r="Z16" s="9" t="s">
+        <v>922</v>
+      </c>
+      <c r="AB16" s="9" t="s">
+        <v>938</v>
+      </c>
+      <c r="AC16" s="9" t="s">
+        <v>616</v>
+      </c>
+      <c r="AD16" s="9" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="17" spans="2:30">
       <c r="B17" t="s">
         <v>475</v>
       </c>
@@ -27687,17 +27878,46 @@
       <c r="L17" t="s">
         <v>653</v>
       </c>
-      <c r="P17" s="10" t="s">
+      <c r="O17" s="9" t="s">
+        <v>482</v>
+      </c>
+      <c r="P17" s="9" t="s">
         <v>933</v>
       </c>
-      <c r="Q17" s="10" t="s">
-        <v>629</v>
-      </c>
-      <c r="R17" s="10" t="s">
-        <v>923</v>
-      </c>
-    </row>
-    <row r="18" spans="2:18">
+      <c r="Q17" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>North-East</v>
+      </c>
+      <c r="S17" s="9" t="s">
+        <v>482</v>
+      </c>
+      <c r="T17" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U17" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Yola</v>
+      </c>
+      <c r="X17" s="9" t="s">
+        <v>937</v>
+      </c>
+      <c r="Y17" s="9" t="s">
+        <v>617</v>
+      </c>
+      <c r="Z17" s="9" t="s">
+        <v>921</v>
+      </c>
+      <c r="AB17" s="9" t="s">
+        <v>938</v>
+      </c>
+      <c r="AC17" s="9" t="s">
+        <v>617</v>
+      </c>
+      <c r="AD17" s="9" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="18" spans="2:30">
       <c r="B18" t="s">
         <v>475</v>
       </c>
@@ -27725,17 +27945,46 @@
       <c r="L18" t="s">
         <v>654</v>
       </c>
-      <c r="P18" s="10" t="s">
+      <c r="O18" s="9" t="s">
+        <v>483</v>
+      </c>
+      <c r="P18" s="9" t="s">
         <v>933</v>
       </c>
-      <c r="Q18" s="10" t="s">
-        <v>624</v>
-      </c>
-      <c r="R18" s="10" t="s">
-        <v>923</v>
-      </c>
-    </row>
-    <row r="19" spans="2:18">
+      <c r="Q18" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>South-South</v>
+      </c>
+      <c r="S18" s="9" t="s">
+        <v>483</v>
+      </c>
+      <c r="T18" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U18" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Port Harcourt</v>
+      </c>
+      <c r="X18" s="9" t="s">
+        <v>937</v>
+      </c>
+      <c r="Y18" s="9" t="s">
+        <v>618</v>
+      </c>
+      <c r="Z18" s="9" t="s">
+        <v>921</v>
+      </c>
+      <c r="AB18" s="9" t="s">
+        <v>938</v>
+      </c>
+      <c r="AC18" s="9" t="s">
+        <v>618</v>
+      </c>
+      <c r="AD18" s="9" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="19" spans="2:30">
       <c r="B19" t="s">
         <v>475</v>
       </c>
@@ -27763,17 +28012,46 @@
       <c r="L19" t="s">
         <v>655</v>
       </c>
-      <c r="P19" s="10" t="s">
+      <c r="O19" s="9" t="s">
+        <v>484</v>
+      </c>
+      <c r="P19" s="9" t="s">
         <v>933</v>
       </c>
-      <c r="Q19" s="10" t="s">
-        <v>631</v>
-      </c>
-      <c r="R19" s="10" t="s">
+      <c r="Q19" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>North-West</v>
+      </c>
+      <c r="S19" s="9" t="s">
+        <v>484</v>
+      </c>
+      <c r="T19" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U19" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Kano</v>
+      </c>
+      <c r="X19" s="9" t="s">
+        <v>937</v>
+      </c>
+      <c r="Y19" s="9" t="s">
+        <v>619</v>
+      </c>
+      <c r="Z19" s="9" t="s">
         <v>923</v>
       </c>
-    </row>
-    <row r="20" spans="2:18">
+      <c r="AB19" s="9" t="s">
+        <v>938</v>
+      </c>
+      <c r="AC19" s="9" t="s">
+        <v>619</v>
+      </c>
+      <c r="AD19" s="9" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="20" spans="2:30">
       <c r="B20" t="s">
         <v>475</v>
       </c>
@@ -27801,17 +28079,46 @@
       <c r="L20" t="s">
         <v>656</v>
       </c>
-      <c r="P20" s="10" t="s">
+      <c r="O20" s="9" t="s">
+        <v>485</v>
+      </c>
+      <c r="P20" s="9" t="s">
         <v>933</v>
       </c>
-      <c r="Q20" s="10" t="s">
-        <v>633</v>
-      </c>
-      <c r="R20" s="10" t="s">
-        <v>922</v>
-      </c>
-    </row>
-    <row r="21" spans="2:18">
+      <c r="Q20" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>South-West</v>
+      </c>
+      <c r="S20" s="9" t="s">
+        <v>485</v>
+      </c>
+      <c r="T20" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U20" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Ibadan</v>
+      </c>
+      <c r="X20" s="9" t="s">
+        <v>937</v>
+      </c>
+      <c r="Y20" s="9" t="s">
+        <v>620</v>
+      </c>
+      <c r="Z20" s="9" t="s">
+        <v>924</v>
+      </c>
+      <c r="AB20" s="9" t="s">
+        <v>938</v>
+      </c>
+      <c r="AC20" s="9" t="s">
+        <v>620</v>
+      </c>
+      <c r="AD20" s="9" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="21" spans="2:30">
       <c r="B21" t="s">
         <v>475</v>
       </c>
@@ -27839,17 +28146,46 @@
       <c r="L21" t="s">
         <v>657</v>
       </c>
-      <c r="P21" s="10" t="s">
+      <c r="O21" s="9" t="s">
+        <v>486</v>
+      </c>
+      <c r="P21" s="9" t="s">
         <v>933</v>
       </c>
-      <c r="Q21" s="10" t="s">
-        <v>642</v>
-      </c>
-      <c r="R21" s="10" t="s">
-        <v>924</v>
-      </c>
-    </row>
-    <row r="22" spans="2:18">
+      <c r="Q21" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>North-Central</v>
+      </c>
+      <c r="S21" s="9" t="s">
+        <v>486</v>
+      </c>
+      <c r="T21" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U21" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Abuja</v>
+      </c>
+      <c r="X21" s="9" t="s">
+        <v>937</v>
+      </c>
+      <c r="Y21" s="9" t="s">
+        <v>621</v>
+      </c>
+      <c r="Z21" s="9" t="s">
+        <v>925</v>
+      </c>
+      <c r="AB21" s="9" t="s">
+        <v>938</v>
+      </c>
+      <c r="AC21" s="9" t="s">
+        <v>621</v>
+      </c>
+      <c r="AD21" s="9" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="22" spans="2:30">
       <c r="B22" t="s">
         <v>475</v>
       </c>
@@ -27877,17 +28213,46 @@
       <c r="L22" t="s">
         <v>658</v>
       </c>
-      <c r="P22" s="10" t="s">
+      <c r="O22" s="9" t="s">
+        <v>487</v>
+      </c>
+      <c r="P22" s="9" t="s">
         <v>933</v>
       </c>
-      <c r="Q22" s="10" t="s">
-        <v>612</v>
-      </c>
-      <c r="R22" s="10" t="s">
-        <v>924</v>
-      </c>
-    </row>
-    <row r="23" spans="2:18">
+      <c r="Q22" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>South-West</v>
+      </c>
+      <c r="S22" s="9" t="s">
+        <v>487</v>
+      </c>
+      <c r="T22" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U22" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Ibadan</v>
+      </c>
+      <c r="X22" s="9" t="s">
+        <v>937</v>
+      </c>
+      <c r="Y22" s="9" t="s">
+        <v>622</v>
+      </c>
+      <c r="Z22" s="9" t="s">
+        <v>925</v>
+      </c>
+      <c r="AB22" s="9" t="s">
+        <v>938</v>
+      </c>
+      <c r="AC22" s="9" t="s">
+        <v>622</v>
+      </c>
+      <c r="AD22" s="9" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="23" spans="2:30">
       <c r="B23" t="s">
         <v>475</v>
       </c>
@@ -27915,17 +28280,46 @@
       <c r="L23" t="s">
         <v>659</v>
       </c>
-      <c r="P23" s="10" t="s">
+      <c r="O23" s="9" t="s">
+        <v>488</v>
+      </c>
+      <c r="P23" s="9" t="s">
         <v>933</v>
       </c>
-      <c r="Q23" s="10" t="s">
-        <v>620</v>
-      </c>
-      <c r="R23" s="10" t="s">
-        <v>924</v>
-      </c>
-    </row>
-    <row r="24" spans="2:18">
+      <c r="Q23" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>North-Central</v>
+      </c>
+      <c r="S23" s="9" t="s">
+        <v>488</v>
+      </c>
+      <c r="T23" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U23" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Ibadan</v>
+      </c>
+      <c r="X23" s="9" t="s">
+        <v>937</v>
+      </c>
+      <c r="Y23" s="9" t="s">
+        <v>623</v>
+      </c>
+      <c r="Z23" s="9" t="s">
+        <v>922</v>
+      </c>
+      <c r="AB23" s="9" t="s">
+        <v>938</v>
+      </c>
+      <c r="AC23" s="9" t="s">
+        <v>623</v>
+      </c>
+      <c r="AD23" s="9" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="24" spans="2:30">
       <c r="B24" t="s">
         <v>475</v>
       </c>
@@ -27953,17 +28347,46 @@
       <c r="L24" t="s">
         <v>660</v>
       </c>
-      <c r="P24" s="10" t="s">
+      <c r="O24" s="9" t="s">
+        <v>489</v>
+      </c>
+      <c r="P24" s="9" t="s">
         <v>933</v>
       </c>
-      <c r="Q24" s="10" t="s">
-        <v>638</v>
-      </c>
-      <c r="R24" s="10" t="s">
-        <v>924</v>
-      </c>
-    </row>
-    <row r="25" spans="2:18">
+      <c r="Q24" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>South-South</v>
+      </c>
+      <c r="S24" s="9" t="s">
+        <v>489</v>
+      </c>
+      <c r="T24" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U24" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Benin</v>
+      </c>
+      <c r="X24" s="9" t="s">
+        <v>937</v>
+      </c>
+      <c r="Y24" s="9" t="s">
+        <v>624</v>
+      </c>
+      <c r="Z24" s="9" t="s">
+        <v>923</v>
+      </c>
+      <c r="AB24" s="9" t="s">
+        <v>938</v>
+      </c>
+      <c r="AC24" s="9" t="s">
+        <v>624</v>
+      </c>
+      <c r="AD24" s="9" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="25" spans="2:30">
       <c r="B25" t="s">
         <v>475</v>
       </c>
@@ -27991,17 +28414,46 @@
       <c r="L25" t="s">
         <v>661</v>
       </c>
-      <c r="P25" s="10" t="s">
+      <c r="O25" s="9" t="s">
+        <v>490</v>
+      </c>
+      <c r="P25" s="9" t="s">
         <v>933</v>
       </c>
-      <c r="Q25" s="10" t="s">
-        <v>628</v>
-      </c>
-      <c r="R25" s="10" t="s">
-        <v>924</v>
-      </c>
-    </row>
-    <row r="26" spans="2:18">
+      <c r="Q25" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>South-East</v>
+      </c>
+      <c r="S25" s="9" t="s">
+        <v>490</v>
+      </c>
+      <c r="T25" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U25" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Enugu</v>
+      </c>
+      <c r="X25" s="9" t="s">
+        <v>937</v>
+      </c>
+      <c r="Y25" s="9" t="s">
+        <v>625</v>
+      </c>
+      <c r="Z25" s="9" t="s">
+        <v>920</v>
+      </c>
+      <c r="AB25" s="9" t="s">
+        <v>938</v>
+      </c>
+      <c r="AC25" s="9" t="s">
+        <v>625</v>
+      </c>
+      <c r="AD25" s="9" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="26" spans="2:30">
       <c r="B26" t="s">
         <v>475</v>
       </c>
@@ -28029,17 +28481,46 @@
       <c r="L26" t="s">
         <v>662</v>
       </c>
-      <c r="P26" s="10" t="s">
+      <c r="O26" s="9" t="s">
+        <v>491</v>
+      </c>
+      <c r="P26" s="9" t="s">
         <v>933</v>
       </c>
-      <c r="Q26" s="10" t="s">
-        <v>615</v>
-      </c>
-      <c r="R26" s="10" t="s">
-        <v>922</v>
-      </c>
-    </row>
-    <row r="27" spans="2:18">
+      <c r="Q26" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>North-Central</v>
+      </c>
+      <c r="S26" s="9" t="s">
+        <v>491</v>
+      </c>
+      <c r="T26" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U26" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Abuja</v>
+      </c>
+      <c r="X26" s="9" t="s">
+        <v>937</v>
+      </c>
+      <c r="Y26" s="9" t="s">
+        <v>626</v>
+      </c>
+      <c r="Z26" s="9" t="s">
+        <v>921</v>
+      </c>
+      <c r="AB26" s="9" t="s">
+        <v>938</v>
+      </c>
+      <c r="AC26" s="9" t="s">
+        <v>626</v>
+      </c>
+      <c r="AD26" s="9" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="27" spans="2:30">
       <c r="B27" t="s">
         <v>475</v>
       </c>
@@ -28067,17 +28548,46 @@
       <c r="L27" t="s">
         <v>663</v>
       </c>
-      <c r="P27" s="10" t="s">
+      <c r="O27" s="9" t="s">
+        <v>492</v>
+      </c>
+      <c r="P27" s="9" t="s">
         <v>933</v>
       </c>
-      <c r="Q27" s="10" t="s">
-        <v>623</v>
-      </c>
-      <c r="R27" s="10" t="s">
-        <v>922</v>
-      </c>
-    </row>
-    <row r="28" spans="2:18">
+      <c r="Q27" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>South-West</v>
+      </c>
+      <c r="S27" s="9" t="s">
+        <v>492</v>
+      </c>
+      <c r="T27" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U27" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Ikeja</v>
+      </c>
+      <c r="X27" s="9" t="s">
+        <v>937</v>
+      </c>
+      <c r="Y27" s="9" t="s">
+        <v>627</v>
+      </c>
+      <c r="Z27" s="9" t="s">
+        <v>920</v>
+      </c>
+      <c r="AB27" s="9" t="s">
+        <v>938</v>
+      </c>
+      <c r="AC27" s="9" t="s">
+        <v>627</v>
+      </c>
+      <c r="AD27" s="9" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="28" spans="2:30">
       <c r="B28" t="s">
         <v>475</v>
       </c>
@@ -28105,17 +28615,46 @@
       <c r="L28" t="s">
         <v>664</v>
       </c>
-      <c r="P28" s="10" t="s">
+      <c r="O28" s="9" t="s">
+        <v>493</v>
+      </c>
+      <c r="P28" s="9" t="s">
         <v>933</v>
       </c>
-      <c r="Q28" s="10" t="s">
-        <v>614</v>
-      </c>
-      <c r="R28" s="10" t="s">
-        <v>925</v>
-      </c>
-    </row>
-    <row r="29" spans="2:18">
+      <c r="Q28" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>North-Central</v>
+      </c>
+      <c r="S28" s="9" t="s">
+        <v>493</v>
+      </c>
+      <c r="T28" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U28" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Abuja</v>
+      </c>
+      <c r="X28" s="9" t="s">
+        <v>937</v>
+      </c>
+      <c r="Y28" s="9" t="s">
+        <v>628</v>
+      </c>
+      <c r="Z28" s="9" t="s">
+        <v>924</v>
+      </c>
+      <c r="AB28" s="9" t="s">
+        <v>938</v>
+      </c>
+      <c r="AC28" s="9" t="s">
+        <v>628</v>
+      </c>
+      <c r="AD28" s="9" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="29" spans="2:30">
       <c r="B29" t="s">
         <v>475</v>
       </c>
@@ -28143,17 +28682,46 @@
       <c r="L29" t="s">
         <v>665</v>
       </c>
-      <c r="P29" s="10" t="s">
+      <c r="O29" s="9" t="s">
+        <v>494</v>
+      </c>
+      <c r="P29" s="9" t="s">
         <v>933</v>
       </c>
-      <c r="Q29" s="10" t="s">
-        <v>613</v>
-      </c>
-      <c r="R29" s="10" t="s">
-        <v>922</v>
-      </c>
-    </row>
-    <row r="30" spans="2:18">
+      <c r="Q29" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>North-East</v>
+      </c>
+      <c r="S29" s="9" t="s">
+        <v>494</v>
+      </c>
+      <c r="T29" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U29" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Yola</v>
+      </c>
+      <c r="X29" s="9" t="s">
+        <v>937</v>
+      </c>
+      <c r="Y29" s="9" t="s">
+        <v>629</v>
+      </c>
+      <c r="Z29" s="9" t="s">
+        <v>923</v>
+      </c>
+      <c r="AB29" s="9" t="s">
+        <v>938</v>
+      </c>
+      <c r="AC29" s="9" t="s">
+        <v>629</v>
+      </c>
+      <c r="AD29" s="9" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="30" spans="2:30">
       <c r="B30" t="s">
         <v>475</v>
       </c>
@@ -28181,17 +28749,46 @@
       <c r="L30" t="s">
         <v>666</v>
       </c>
-      <c r="P30" s="10" t="s">
+      <c r="O30" s="9" t="s">
+        <v>495</v>
+      </c>
+      <c r="P30" s="9" t="s">
         <v>933</v>
       </c>
-      <c r="Q30" s="10" t="s">
-        <v>622</v>
-      </c>
-      <c r="R30" s="10" t="s">
+      <c r="Q30" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>South-East</v>
+      </c>
+      <c r="S30" s="9" t="s">
+        <v>495</v>
+      </c>
+      <c r="T30" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U30" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Enugu</v>
+      </c>
+      <c r="X30" s="9" t="s">
+        <v>937</v>
+      </c>
+      <c r="Y30" s="9" t="s">
+        <v>630</v>
+      </c>
+      <c r="Z30" s="9" t="s">
         <v>925</v>
       </c>
-    </row>
-    <row r="31" spans="2:18">
+      <c r="AB30" s="9" t="s">
+        <v>938</v>
+      </c>
+      <c r="AC30" s="9" t="s">
+        <v>630</v>
+      </c>
+      <c r="AD30" s="9" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="31" spans="2:30">
       <c r="B31" t="s">
         <v>475</v>
       </c>
@@ -28219,17 +28816,46 @@
       <c r="L31" t="s">
         <v>667</v>
       </c>
-      <c r="P31" s="10" t="s">
+      <c r="O31" s="9" t="s">
+        <v>496</v>
+      </c>
+      <c r="P31" s="9" t="s">
         <v>933</v>
       </c>
-      <c r="Q31" s="10" t="s">
-        <v>634</v>
-      </c>
-      <c r="R31" s="10" t="s">
-        <v>925</v>
-      </c>
-    </row>
-    <row r="32" spans="2:18">
+      <c r="Q31" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>North-West</v>
+      </c>
+      <c r="S31" s="9" t="s">
+        <v>496</v>
+      </c>
+      <c r="T31" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U31" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Kaduna</v>
+      </c>
+      <c r="X31" s="9" t="s">
+        <v>937</v>
+      </c>
+      <c r="Y31" s="9" t="s">
+        <v>631</v>
+      </c>
+      <c r="Z31" s="9" t="s">
+        <v>923</v>
+      </c>
+      <c r="AB31" s="9" t="s">
+        <v>938</v>
+      </c>
+      <c r="AC31" s="9" t="s">
+        <v>631</v>
+      </c>
+      <c r="AD31" s="9" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="32" spans="2:30">
       <c r="B32" t="s">
         <v>475</v>
       </c>
@@ -28257,17 +28883,46 @@
       <c r="L32" t="s">
         <v>668</v>
       </c>
-      <c r="P32" s="10" t="s">
+      <c r="O32" s="9" t="s">
+        <v>497</v>
+      </c>
+      <c r="P32" s="9" t="s">
         <v>933</v>
       </c>
-      <c r="Q32" s="10" t="s">
-        <v>621</v>
-      </c>
-      <c r="R32" s="10" t="s">
-        <v>925</v>
-      </c>
-    </row>
-    <row r="33" spans="2:18">
+      <c r="Q32" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>South-South</v>
+      </c>
+      <c r="S32" s="9" t="s">
+        <v>497</v>
+      </c>
+      <c r="T32" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U32" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Port Harcourt</v>
+      </c>
+      <c r="X32" s="9" t="s">
+        <v>937</v>
+      </c>
+      <c r="Y32" s="9" t="s">
+        <v>632</v>
+      </c>
+      <c r="Z32" s="9" t="s">
+        <v>922</v>
+      </c>
+      <c r="AB32" s="9" t="s">
+        <v>938</v>
+      </c>
+      <c r="AC32" s="9" t="s">
+        <v>632</v>
+      </c>
+      <c r="AD32" s="9" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="33" spans="2:30">
       <c r="B33" t="s">
         <v>475</v>
       </c>
@@ -28295,17 +28950,46 @@
       <c r="L33" t="s">
         <v>669</v>
       </c>
-      <c r="P33" s="10" t="s">
+      <c r="O33" s="9" t="s">
+        <v>498</v>
+      </c>
+      <c r="P33" s="9" t="s">
         <v>933</v>
       </c>
-      <c r="Q33" s="10" t="s">
-        <v>630</v>
-      </c>
-      <c r="R33" s="10" t="s">
-        <v>925</v>
-      </c>
-    </row>
-    <row r="34" spans="2:18">
+      <c r="Q33" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>South-South</v>
+      </c>
+      <c r="S33" s="9" t="s">
+        <v>498</v>
+      </c>
+      <c r="T33" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U33" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Port Harcourt</v>
+      </c>
+      <c r="X33" s="9" t="s">
+        <v>937</v>
+      </c>
+      <c r="Y33" s="9" t="s">
+        <v>633</v>
+      </c>
+      <c r="Z33" s="9" t="s">
+        <v>922</v>
+      </c>
+      <c r="AB33" s="9" t="s">
+        <v>938</v>
+      </c>
+      <c r="AC33" s="9" t="s">
+        <v>633</v>
+      </c>
+      <c r="AD33" s="9" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="34" spans="2:30">
       <c r="B34" t="s">
         <v>475</v>
       </c>
@@ -28333,17 +29017,46 @@
       <c r="L34" t="s">
         <v>670</v>
       </c>
-      <c r="P34" s="10" t="s">
+      <c r="O34" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="P34" s="9" t="s">
         <v>933</v>
       </c>
-      <c r="Q34" s="10" t="s">
-        <v>616</v>
-      </c>
-      <c r="R34" s="10" t="s">
-        <v>922</v>
-      </c>
-    </row>
-    <row r="35" spans="2:18">
+      <c r="Q34" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>South-West</v>
+      </c>
+      <c r="S34" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="T34" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U34" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Ibadan</v>
+      </c>
+      <c r="X34" s="9" t="s">
+        <v>937</v>
+      </c>
+      <c r="Y34" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="Z34" s="9" t="s">
+        <v>925</v>
+      </c>
+      <c r="AB34" s="9" t="s">
+        <v>938</v>
+      </c>
+      <c r="AC34" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="AD34" s="9" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30">
       <c r="B35" t="s">
         <v>475</v>
       </c>
@@ -28371,17 +29084,46 @@
       <c r="L35" t="s">
         <v>671</v>
       </c>
-      <c r="P35" s="10" t="s">
+      <c r="O35" s="9" t="s">
+        <v>500</v>
+      </c>
+      <c r="P35" s="9" t="s">
         <v>933</v>
       </c>
-      <c r="Q35" s="10" t="s">
-        <v>637</v>
-      </c>
-      <c r="R35" s="10" t="s">
-        <v>923</v>
-      </c>
-    </row>
-    <row r="36" spans="2:18">
+      <c r="Q35" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>South-South</v>
+      </c>
+      <c r="S35" s="9" t="s">
+        <v>500</v>
+      </c>
+      <c r="T35" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U35" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Benin</v>
+      </c>
+      <c r="X35" s="9" t="s">
+        <v>937</v>
+      </c>
+      <c r="Y35" s="9" t="s">
+        <v>635</v>
+      </c>
+      <c r="Z35" s="9" t="s">
+        <v>921</v>
+      </c>
+      <c r="AB35" s="9" t="s">
+        <v>938</v>
+      </c>
+      <c r="AC35" s="9" t="s">
+        <v>635</v>
+      </c>
+      <c r="AD35" s="9" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="36" spans="2:30">
       <c r="B36" t="s">
         <v>475</v>
       </c>
@@ -28409,17 +29151,46 @@
       <c r="L36" t="s">
         <v>672</v>
       </c>
-      <c r="P36" s="10" t="s">
+      <c r="O36" s="9" t="s">
+        <v>501</v>
+      </c>
+      <c r="P36" s="9" t="s">
         <v>933</v>
       </c>
-      <c r="Q36" s="10" t="s">
-        <v>643</v>
-      </c>
-      <c r="R36" s="10" t="s">
-        <v>924</v>
-      </c>
-    </row>
-    <row r="37" spans="2:18">
+      <c r="Q36" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>South-West</v>
+      </c>
+      <c r="S36" s="9" t="s">
+        <v>501</v>
+      </c>
+      <c r="T36" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U36" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Ibadan</v>
+      </c>
+      <c r="X36" s="9" t="s">
+        <v>937</v>
+      </c>
+      <c r="Y36" s="9" t="s">
+        <v>636</v>
+      </c>
+      <c r="Z36" s="9" t="s">
+        <v>920</v>
+      </c>
+      <c r="AB36" s="9" t="s">
+        <v>938</v>
+      </c>
+      <c r="AC36" s="9" t="s">
+        <v>636</v>
+      </c>
+      <c r="AD36" s="9" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="37" spans="2:30">
       <c r="B37" t="s">
         <v>475</v>
       </c>
@@ -28447,17 +29218,46 @@
       <c r="L37" t="s">
         <v>673</v>
       </c>
-      <c r="P37" s="10" t="s">
-        <v>934</v>
-      </c>
-      <c r="Q37" s="10" t="s">
-        <v>627</v>
-      </c>
-      <c r="R37" s="10" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="38" spans="2:18">
+      <c r="O37" s="9" t="s">
+        <v>502</v>
+      </c>
+      <c r="P37" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q37" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>North-Central</v>
+      </c>
+      <c r="S37" s="9" t="s">
+        <v>502</v>
+      </c>
+      <c r="T37" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U37" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Jos</v>
+      </c>
+      <c r="X37" s="9" t="s">
+        <v>937</v>
+      </c>
+      <c r="Y37" s="9" t="s">
+        <v>637</v>
+      </c>
+      <c r="Z37" s="9" t="s">
+        <v>923</v>
+      </c>
+      <c r="AB37" s="9" t="s">
+        <v>938</v>
+      </c>
+      <c r="AC37" s="9" t="s">
+        <v>637</v>
+      </c>
+      <c r="AD37" s="9" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="38" spans="2:30">
       <c r="B38" t="s">
         <v>475</v>
       </c>
@@ -28485,17 +29285,46 @@
       <c r="L38" t="s">
         <v>674</v>
       </c>
-      <c r="P38" s="10" t="s">
-        <v>934</v>
-      </c>
-      <c r="Q38" s="10" t="s">
-        <v>618</v>
-      </c>
-      <c r="R38" s="10" t="s">
-        <v>926</v>
-      </c>
-    </row>
-    <row r="39" spans="2:18">
+      <c r="O38" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="P38" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q38" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>North-Central</v>
+      </c>
+      <c r="S38" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="T38" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U38" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Abuja</v>
+      </c>
+      <c r="X38" s="9" t="s">
+        <v>937</v>
+      </c>
+      <c r="Y38" s="9" t="s">
+        <v>638</v>
+      </c>
+      <c r="Z38" s="9" t="s">
+        <v>924</v>
+      </c>
+      <c r="AB38" s="9" t="s">
+        <v>938</v>
+      </c>
+      <c r="AC38" s="9" t="s">
+        <v>638</v>
+      </c>
+      <c r="AD38" s="9" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="39" spans="2:30">
       <c r="B39" t="s">
         <v>475</v>
       </c>
@@ -28523,17 +29352,46 @@
       <c r="L39" t="s">
         <v>675</v>
       </c>
-      <c r="P39" s="10" t="s">
-        <v>934</v>
-      </c>
-      <c r="Q39" s="10" t="s">
-        <v>636</v>
-      </c>
-      <c r="R39" s="10" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="40" spans="2:18">
+      <c r="O39" s="9" t="s">
+        <v>504</v>
+      </c>
+      <c r="P39" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q39" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>North-Central</v>
+      </c>
+      <c r="S39" s="9" t="s">
+        <v>504</v>
+      </c>
+      <c r="T39" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U39" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Abuja</v>
+      </c>
+      <c r="X39" s="9" t="s">
+        <v>937</v>
+      </c>
+      <c r="Y39" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="Z39" s="9" t="s">
+        <v>921</v>
+      </c>
+      <c r="AB39" s="9" t="s">
+        <v>938</v>
+      </c>
+      <c r="AC39" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="AD39" s="9" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="40" spans="2:30">
       <c r="B40" t="s">
         <v>475</v>
       </c>
@@ -28561,17 +29419,46 @@
       <c r="L40" t="s">
         <v>676</v>
       </c>
-      <c r="P40" s="10" t="s">
-        <v>934</v>
-      </c>
-      <c r="Q40" s="10" t="s">
-        <v>641</v>
-      </c>
-      <c r="R40" s="10" t="s">
-        <v>927</v>
-      </c>
-    </row>
-    <row r="41" spans="2:18">
+      <c r="O40" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="P40" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q40" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>South-West</v>
+      </c>
+      <c r="S40" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="T40" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U40" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Benin</v>
+      </c>
+      <c r="X40" s="9" t="s">
+        <v>937</v>
+      </c>
+      <c r="Y40" s="9" t="s">
+        <v>640</v>
+      </c>
+      <c r="Z40" s="9" t="s">
+        <v>922</v>
+      </c>
+      <c r="AB40" s="9" t="s">
+        <v>938</v>
+      </c>
+      <c r="AC40" s="9" t="s">
+        <v>640</v>
+      </c>
+      <c r="AD40" s="9" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="41" spans="2:30">
       <c r="B41" t="s">
         <v>475</v>
       </c>
@@ -28599,17 +29486,46 @@
       <c r="L41" t="s">
         <v>677</v>
       </c>
-      <c r="P41" s="10" t="s">
-        <v>934</v>
-      </c>
-      <c r="Q41" s="10" t="s">
-        <v>632</v>
-      </c>
-      <c r="R41" s="10" t="s">
+      <c r="O41" s="9" t="s">
+        <v>506</v>
+      </c>
+      <c r="P41" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q41" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>South-South</v>
+      </c>
+      <c r="S41" s="9" t="s">
+        <v>506</v>
+      </c>
+      <c r="T41" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U41" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Benin</v>
+      </c>
+      <c r="X41" s="9" t="s">
+        <v>937</v>
+      </c>
+      <c r="Y41" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="Z41" s="9" t="s">
+        <v>921</v>
+      </c>
+      <c r="AB41" s="9" t="s">
+        <v>938</v>
+      </c>
+      <c r="AC41" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="AD41" s="9" t="s">
         <v>927</v>
       </c>
     </row>
-    <row r="42" spans="2:18">
+    <row r="42" spans="2:30">
       <c r="B42" t="s">
         <v>475</v>
       </c>
@@ -28637,17 +29553,46 @@
       <c r="L42" t="s">
         <v>678</v>
       </c>
-      <c r="P42" s="10" t="s">
-        <v>934</v>
-      </c>
-      <c r="Q42" s="10" t="s">
-        <v>635</v>
-      </c>
-      <c r="R42" s="10" t="s">
-        <v>926</v>
-      </c>
-    </row>
-    <row r="43" spans="2:18">
+      <c r="O42" s="9" t="s">
+        <v>507</v>
+      </c>
+      <c r="P42" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q42" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>South-South</v>
+      </c>
+      <c r="S42" s="9" t="s">
+        <v>507</v>
+      </c>
+      <c r="T42" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U42" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Benin</v>
+      </c>
+      <c r="X42" s="9" t="s">
+        <v>937</v>
+      </c>
+      <c r="Y42" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="Z42" s="9" t="s">
+        <v>924</v>
+      </c>
+      <c r="AB42" s="9" t="s">
+        <v>938</v>
+      </c>
+      <c r="AC42" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="AD42" s="9" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30">
       <c r="B43" t="s">
         <v>475</v>
       </c>
@@ -28675,17 +29620,46 @@
       <c r="L43" t="s">
         <v>679</v>
       </c>
-      <c r="P43" s="10" t="s">
-        <v>934</v>
-      </c>
-      <c r="Q43" s="10" t="s">
-        <v>629</v>
-      </c>
-      <c r="R43" s="10" t="s">
-        <v>928</v>
-      </c>
-    </row>
-    <row r="44" spans="2:18">
+      <c r="O43" s="9" t="s">
+        <v>508</v>
+      </c>
+      <c r="P43" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q43" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>North-East</v>
+      </c>
+      <c r="S43" s="9" t="s">
+        <v>508</v>
+      </c>
+      <c r="T43" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U43" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Yola</v>
+      </c>
+      <c r="X43" s="9" t="s">
+        <v>937</v>
+      </c>
+      <c r="Y43" s="9" t="s">
+        <v>643</v>
+      </c>
+      <c r="Z43" s="9" t="s">
+        <v>924</v>
+      </c>
+      <c r="AB43" s="9" t="s">
+        <v>938</v>
+      </c>
+      <c r="AC43" s="9" t="s">
+        <v>643</v>
+      </c>
+      <c r="AD43" s="9" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30">
       <c r="B44" t="s">
         <v>475</v>
       </c>
@@ -28713,17 +29687,46 @@
       <c r="L44" t="s">
         <v>680</v>
       </c>
-      <c r="P44" s="10" t="s">
-        <v>934</v>
-      </c>
-      <c r="Q44" s="10" t="s">
-        <v>624</v>
-      </c>
-      <c r="R44" s="10" t="s">
-        <v>929</v>
-      </c>
-    </row>
-    <row r="45" spans="2:18">
+      <c r="O44" s="9" t="s">
+        <v>509</v>
+      </c>
+      <c r="P44" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q44" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>South-West</v>
+      </c>
+      <c r="S44" s="9" t="s">
+        <v>509</v>
+      </c>
+      <c r="T44" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U44" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Ikeja</v>
+      </c>
+      <c r="X44" s="9" t="s">
+        <v>937</v>
+      </c>
+      <c r="Y44" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="Z44" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="AB44" s="9" t="s">
+        <v>938</v>
+      </c>
+      <c r="AC44" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="AD44" s="9" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30">
       <c r="B45" t="s">
         <v>475</v>
       </c>
@@ -28751,17 +29754,46 @@
       <c r="L45" t="s">
         <v>681</v>
       </c>
-      <c r="P45" s="10" t="s">
-        <v>934</v>
-      </c>
-      <c r="Q45" s="10" t="s">
-        <v>631</v>
-      </c>
-      <c r="R45" s="10" t="s">
-        <v>929</v>
-      </c>
-    </row>
-    <row r="46" spans="2:18">
+      <c r="O45" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="P45" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q45" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>South-East</v>
+      </c>
+      <c r="S45" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="T45" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U45" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Enugu</v>
+      </c>
+      <c r="X45" s="9" t="s">
+        <v>937</v>
+      </c>
+      <c r="Y45" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="Z45" s="9" t="s">
+        <v>924</v>
+      </c>
+      <c r="AB45" s="9" t="s">
+        <v>938</v>
+      </c>
+      <c r="AC45" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="AD45" s="9" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30">
       <c r="B46" t="s">
         <v>475</v>
       </c>
@@ -28789,17 +29821,28 @@
       <c r="L46" t="s">
         <v>682</v>
       </c>
-      <c r="P46" s="10" t="s">
-        <v>934</v>
-      </c>
-      <c r="Q46" s="10" t="s">
-        <v>633</v>
-      </c>
-      <c r="R46" s="10" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="47" spans="2:18">
+      <c r="O46" s="9" t="s">
+        <v>511</v>
+      </c>
+      <c r="P46" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q46" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>South-West</v>
+      </c>
+      <c r="S46" s="9" t="s">
+        <v>511</v>
+      </c>
+      <c r="T46" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U46" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Ikeja</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30">
       <c r="B47" t="s">
         <v>475</v>
       </c>
@@ -28827,17 +29870,28 @@
       <c r="L47" t="s">
         <v>683</v>
       </c>
-      <c r="P47" s="10" t="s">
-        <v>934</v>
-      </c>
-      <c r="Q47" s="10" t="s">
-        <v>642</v>
-      </c>
-      <c r="R47" s="10" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="48" spans="2:18">
+      <c r="O47" s="9" t="s">
+        <v>512</v>
+      </c>
+      <c r="P47" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q47" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>South-South</v>
+      </c>
+      <c r="S47" s="9" t="s">
+        <v>512</v>
+      </c>
+      <c r="T47" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U47" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Port Harcourt</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30">
       <c r="B48" t="s">
         <v>475</v>
       </c>
@@ -28865,17 +29919,28 @@
       <c r="L48" t="s">
         <v>684</v>
       </c>
-      <c r="P48" s="10" t="s">
-        <v>934</v>
-      </c>
-      <c r="Q48" s="10" t="s">
-        <v>612</v>
-      </c>
-      <c r="R48" s="10" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="49" spans="2:18">
+      <c r="O48" s="9" t="s">
+        <v>513</v>
+      </c>
+      <c r="P48" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q48" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>South-South</v>
+      </c>
+      <c r="S48" s="9" t="s">
+        <v>513</v>
+      </c>
+      <c r="T48" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U48" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Benin</v>
+      </c>
+    </row>
+    <row r="49" spans="2:21">
       <c r="B49" t="s">
         <v>475</v>
       </c>
@@ -28903,17 +29968,28 @@
       <c r="L49" t="s">
         <v>685</v>
       </c>
-      <c r="P49" s="10" t="s">
-        <v>934</v>
-      </c>
-      <c r="Q49" s="10" t="s">
-        <v>620</v>
-      </c>
-      <c r="R49" s="10" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="50" spans="2:18">
+      <c r="O49" s="9" t="s">
+        <v>514</v>
+      </c>
+      <c r="P49" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q49" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>North-West</v>
+      </c>
+      <c r="S49" s="9" t="s">
+        <v>514</v>
+      </c>
+      <c r="T49" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U49" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Kano</v>
+      </c>
+    </row>
+    <row r="50" spans="2:21">
       <c r="B50" t="s">
         <v>475</v>
       </c>
@@ -28941,17 +30017,28 @@
       <c r="L50" t="s">
         <v>686</v>
       </c>
-      <c r="P50" s="10" t="s">
-        <v>934</v>
-      </c>
-      <c r="Q50" s="10" t="s">
-        <v>638</v>
-      </c>
-      <c r="R50" s="10" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="51" spans="2:18">
+      <c r="O50" s="9" t="s">
+        <v>515</v>
+      </c>
+      <c r="P50" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q50" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>South-West</v>
+      </c>
+      <c r="S50" s="9" t="s">
+        <v>515</v>
+      </c>
+      <c r="T50" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U50" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Ibadan</v>
+      </c>
+    </row>
+    <row r="51" spans="2:21">
       <c r="B51" t="s">
         <v>475</v>
       </c>
@@ -28979,17 +30066,28 @@
       <c r="L51" t="s">
         <v>687</v>
       </c>
-      <c r="P51" s="10" t="s">
-        <v>934</v>
-      </c>
-      <c r="Q51" s="10" t="s">
-        <v>628</v>
-      </c>
-      <c r="R51" s="10" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="52" spans="2:18">
+      <c r="O51" s="9" t="s">
+        <v>516</v>
+      </c>
+      <c r="P51" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q51" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>North-Central</v>
+      </c>
+      <c r="S51" s="9" t="s">
+        <v>516</v>
+      </c>
+      <c r="T51" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U51" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Ibadan</v>
+      </c>
+    </row>
+    <row r="52" spans="2:21">
       <c r="B52" t="s">
         <v>475</v>
       </c>
@@ -29017,17 +30115,28 @@
       <c r="L52" t="s">
         <v>688</v>
       </c>
-      <c r="P52" s="10" t="s">
-        <v>934</v>
-      </c>
-      <c r="Q52" s="10" t="s">
-        <v>615</v>
-      </c>
-      <c r="R52" s="10" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="53" spans="2:18">
+      <c r="O52" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="P52" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q52" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>South-South</v>
+      </c>
+      <c r="S52" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="T52" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U52" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Port Harcourt</v>
+      </c>
+    </row>
+    <row r="53" spans="2:21">
       <c r="B53" t="s">
         <v>475</v>
       </c>
@@ -29055,17 +30164,28 @@
       <c r="L53" t="s">
         <v>689</v>
       </c>
-      <c r="P53" s="10" t="s">
-        <v>934</v>
-      </c>
-      <c r="Q53" s="10" t="s">
-        <v>623</v>
-      </c>
-      <c r="R53" s="10" t="s">
-        <v>931</v>
-      </c>
-    </row>
-    <row r="54" spans="2:18">
+      <c r="O53" s="9" t="s">
+        <v>518</v>
+      </c>
+      <c r="P53" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q53" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>South-South</v>
+      </c>
+      <c r="S53" s="9" t="s">
+        <v>518</v>
+      </c>
+      <c r="T53" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U53" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Benin</v>
+      </c>
+    </row>
+    <row r="54" spans="2:21">
       <c r="B54" t="s">
         <v>475</v>
       </c>
@@ -29093,17 +30213,28 @@
       <c r="L54" t="s">
         <v>690</v>
       </c>
-      <c r="P54" s="10" t="s">
-        <v>934</v>
-      </c>
-      <c r="Q54" s="10" t="s">
-        <v>614</v>
-      </c>
-      <c r="R54" s="10" t="s">
-        <v>932</v>
-      </c>
-    </row>
-    <row r="55" spans="2:18">
+      <c r="O54" s="9" t="s">
+        <v>519</v>
+      </c>
+      <c r="P54" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q54" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>North-Central</v>
+      </c>
+      <c r="S54" s="9" t="s">
+        <v>519</v>
+      </c>
+      <c r="T54" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U54" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Ibadan</v>
+      </c>
+    </row>
+    <row r="55" spans="2:21">
       <c r="B55" t="s">
         <v>475</v>
       </c>
@@ -29131,17 +30262,28 @@
       <c r="L55" t="s">
         <v>691</v>
       </c>
-      <c r="P55" s="10" t="s">
-        <v>934</v>
-      </c>
-      <c r="Q55" s="10" t="s">
-        <v>613</v>
-      </c>
-      <c r="R55" s="10" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="56" spans="2:18">
+      <c r="O55" s="9" t="s">
+        <v>520</v>
+      </c>
+      <c r="P55" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q55" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>South-East</v>
+      </c>
+      <c r="S55" s="9" t="s">
+        <v>520</v>
+      </c>
+      <c r="T55" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U55" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Enugu</v>
+      </c>
+    </row>
+    <row r="56" spans="2:21">
       <c r="B56" t="s">
         <v>475</v>
       </c>
@@ -29169,17 +30311,28 @@
       <c r="L56" t="s">
         <v>692</v>
       </c>
-      <c r="P56" s="10" t="s">
-        <v>934</v>
-      </c>
-      <c r="Q56" s="10" t="s">
-        <v>622</v>
-      </c>
-      <c r="R56" s="10" t="s">
-        <v>931</v>
-      </c>
-    </row>
-    <row r="57" spans="2:18">
+      <c r="O56" s="9" t="s">
+        <v>521</v>
+      </c>
+      <c r="P56" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q56" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>North-Central</v>
+      </c>
+      <c r="S56" s="9" t="s">
+        <v>521</v>
+      </c>
+      <c r="T56" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U56" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Abuja</v>
+      </c>
+    </row>
+    <row r="57" spans="2:21">
       <c r="B57" t="s">
         <v>475</v>
       </c>
@@ -29207,17 +30360,28 @@
       <c r="L57" t="s">
         <v>693</v>
       </c>
-      <c r="P57" s="10" t="s">
-        <v>934</v>
-      </c>
-      <c r="Q57" s="10" t="s">
-        <v>634</v>
-      </c>
-      <c r="R57" s="10" t="s">
-        <v>929</v>
-      </c>
-    </row>
-    <row r="58" spans="2:18">
+      <c r="O57" s="9" t="s">
+        <v>522</v>
+      </c>
+      <c r="P57" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q57" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>South-South</v>
+      </c>
+      <c r="S57" s="9" t="s">
+        <v>522</v>
+      </c>
+      <c r="T57" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U57" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Benin</v>
+      </c>
+    </row>
+    <row r="58" spans="2:21">
       <c r="B58" t="s">
         <v>475</v>
       </c>
@@ -29245,17 +30409,28 @@
       <c r="L58" t="s">
         <v>694</v>
       </c>
-      <c r="P58" s="10" t="s">
-        <v>934</v>
-      </c>
-      <c r="Q58" s="10" t="s">
-        <v>621</v>
-      </c>
-      <c r="R58" s="10" t="s">
-        <v>931</v>
-      </c>
-    </row>
-    <row r="59" spans="2:18">
+      <c r="O58" s="9" t="s">
+        <v>523</v>
+      </c>
+      <c r="P58" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q58" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>North-Central</v>
+      </c>
+      <c r="S58" s="9" t="s">
+        <v>523</v>
+      </c>
+      <c r="T58" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U58" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Abuja</v>
+      </c>
+    </row>
+    <row r="59" spans="2:21">
       <c r="B59" t="s">
         <v>475</v>
       </c>
@@ -29283,17 +30458,28 @@
       <c r="L59" t="s">
         <v>695</v>
       </c>
-      <c r="P59" s="10" t="s">
-        <v>934</v>
-      </c>
-      <c r="Q59" s="10" t="s">
-        <v>630</v>
-      </c>
-      <c r="R59" s="10" t="s">
-        <v>931</v>
-      </c>
-    </row>
-    <row r="60" spans="2:18">
+      <c r="O59" s="9" t="s">
+        <v>524</v>
+      </c>
+      <c r="P59" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q59" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>South-West</v>
+      </c>
+      <c r="S59" s="9" t="s">
+        <v>524</v>
+      </c>
+      <c r="T59" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U59" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Ibadan</v>
+      </c>
+    </row>
+    <row r="60" spans="2:21">
       <c r="B60" t="s">
         <v>475</v>
       </c>
@@ -29321,17 +30507,28 @@
       <c r="L60" t="s">
         <v>696</v>
       </c>
-      <c r="P60" s="10" t="s">
-        <v>934</v>
-      </c>
-      <c r="Q60" s="10" t="s">
-        <v>616</v>
-      </c>
-      <c r="R60" s="10" t="s">
-        <v>927</v>
-      </c>
-    </row>
-    <row r="61" spans="2:18">
+      <c r="O60" s="9" t="s">
+        <v>525</v>
+      </c>
+      <c r="P60" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q60" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>South-South</v>
+      </c>
+      <c r="S60" s="9" t="s">
+        <v>525</v>
+      </c>
+      <c r="T60" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U60" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Benin</v>
+      </c>
+    </row>
+    <row r="61" spans="2:21">
       <c r="B61" t="s">
         <v>475</v>
       </c>
@@ -29359,17 +30556,28 @@
       <c r="L61" t="s">
         <v>697</v>
       </c>
-      <c r="P61" s="10" t="s">
-        <v>934</v>
-      </c>
-      <c r="Q61" s="10" t="s">
-        <v>637</v>
-      </c>
-      <c r="R61" s="10" t="s">
-        <v>928</v>
-      </c>
-    </row>
-    <row r="62" spans="2:18">
+      <c r="O61" s="9" t="s">
+        <v>526</v>
+      </c>
+      <c r="P61" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q61" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>South-South</v>
+      </c>
+      <c r="S61" s="9" t="s">
+        <v>526</v>
+      </c>
+      <c r="T61" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U61" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Benin</v>
+      </c>
+    </row>
+    <row r="62" spans="2:21">
       <c r="B62" t="s">
         <v>475</v>
       </c>
@@ -29397,17 +30605,28 @@
       <c r="L62" t="s">
         <v>698</v>
       </c>
-      <c r="P62" s="10" t="s">
-        <v>934</v>
-      </c>
-      <c r="Q62" s="10" t="s">
-        <v>643</v>
-      </c>
-      <c r="R62" s="10" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="63" spans="2:18">
+      <c r="O62" s="9" t="s">
+        <v>527</v>
+      </c>
+      <c r="P62" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q62" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>South-South</v>
+      </c>
+      <c r="S62" s="9" t="s">
+        <v>527</v>
+      </c>
+      <c r="T62" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U62" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Benin</v>
+      </c>
+    </row>
+    <row r="63" spans="2:21">
       <c r="B63" t="s">
         <v>475</v>
       </c>
@@ -29435,8 +30654,28 @@
       <c r="L63" t="s">
         <v>699</v>
       </c>
-    </row>
-    <row r="64" spans="2:18">
+      <c r="O63" t="s">
+        <v>528</v>
+      </c>
+      <c r="P63" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q63" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>North-West</v>
+      </c>
+      <c r="S63" t="s">
+        <v>528</v>
+      </c>
+      <c r="T63" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U63" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Kano</v>
+      </c>
+    </row>
+    <row r="64" spans="2:21">
       <c r="B64" t="s">
         <v>475</v>
       </c>
@@ -29464,8 +30703,28 @@
       <c r="L64" t="s">
         <v>700</v>
       </c>
-    </row>
-    <row r="65" spans="2:12">
+      <c r="O64" t="s">
+        <v>529</v>
+      </c>
+      <c r="P64" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q64" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>North-West</v>
+      </c>
+      <c r="S64" t="s">
+        <v>529</v>
+      </c>
+      <c r="T64" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U64" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Kano</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21">
       <c r="B65" t="s">
         <v>475</v>
       </c>
@@ -29493,8 +30752,28 @@
       <c r="L65" t="s">
         <v>701</v>
       </c>
-    </row>
-    <row r="66" spans="2:12">
+      <c r="O65" t="s">
+        <v>530</v>
+      </c>
+      <c r="P65" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q65" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>North-Central</v>
+      </c>
+      <c r="S65" t="s">
+        <v>530</v>
+      </c>
+      <c r="T65" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U65" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Abuja</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21">
       <c r="B66" t="s">
         <v>475</v>
       </c>
@@ -29522,8 +30801,28 @@
       <c r="L66" t="s">
         <v>702</v>
       </c>
-    </row>
-    <row r="67" spans="2:12">
+      <c r="O66" t="s">
+        <v>531</v>
+      </c>
+      <c r="P66" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q66" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>South-West</v>
+      </c>
+      <c r="S66" t="s">
+        <v>531</v>
+      </c>
+      <c r="T66" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U66" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Ibadan</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21">
       <c r="B67" t="s">
         <v>475</v>
       </c>
@@ -29551,8 +30850,28 @@
       <c r="L67" t="s">
         <v>703</v>
       </c>
-    </row>
-    <row r="68" spans="2:12">
+      <c r="O67" t="s">
+        <v>532</v>
+      </c>
+      <c r="P67" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q67" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>North-Central</v>
+      </c>
+      <c r="S67" t="s">
+        <v>532</v>
+      </c>
+      <c r="T67" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U67" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Jos</v>
+      </c>
+    </row>
+    <row r="68" spans="2:21">
       <c r="B68" t="s">
         <v>475</v>
       </c>
@@ -29580,8 +30899,28 @@
       <c r="L68" t="s">
         <v>704</v>
       </c>
-    </row>
-    <row r="69" spans="2:12">
+      <c r="O68" t="s">
+        <v>533</v>
+      </c>
+      <c r="P68" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q68" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>South-East</v>
+      </c>
+      <c r="S68" t="s">
+        <v>533</v>
+      </c>
+      <c r="T68" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U68" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Enugu</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21">
       <c r="B69" t="s">
         <v>475</v>
       </c>
@@ -29609,8 +30948,28 @@
       <c r="L69" t="s">
         <v>705</v>
       </c>
-    </row>
-    <row r="70" spans="2:12">
+      <c r="O69" t="s">
+        <v>534</v>
+      </c>
+      <c r="P69" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q69" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>North-Central</v>
+      </c>
+      <c r="S69" t="s">
+        <v>534</v>
+      </c>
+      <c r="T69" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U69" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Abuja</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21">
       <c r="B70" t="s">
         <v>475</v>
       </c>
@@ -29638,8 +30997,28 @@
       <c r="L70" t="s">
         <v>706</v>
       </c>
-    </row>
-    <row r="71" spans="2:12">
+      <c r="O70" t="s">
+        <v>535</v>
+      </c>
+      <c r="P70" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q70" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>South-South</v>
+      </c>
+      <c r="S70" t="s">
+        <v>535</v>
+      </c>
+      <c r="T70" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U70" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Benin</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21">
       <c r="B71" t="s">
         <v>475</v>
       </c>
@@ -29667,8 +31046,28 @@
       <c r="L71" t="s">
         <v>707</v>
       </c>
-    </row>
-    <row r="72" spans="2:12">
+      <c r="O71" t="s">
+        <v>536</v>
+      </c>
+      <c r="P71" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q71" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>South-East</v>
+      </c>
+      <c r="S71" t="s">
+        <v>536</v>
+      </c>
+      <c r="T71" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U71" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Enugu</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21">
       <c r="B72" t="s">
         <v>475</v>
       </c>
@@ -29696,8 +31095,28 @@
       <c r="L72" t="s">
         <v>708</v>
       </c>
-    </row>
-    <row r="73" spans="2:12">
+      <c r="O72" t="s">
+        <v>537</v>
+      </c>
+      <c r="P72" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q72" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>South-South</v>
+      </c>
+      <c r="S72" t="s">
+        <v>537</v>
+      </c>
+      <c r="T72" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U72" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Benin</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21">
       <c r="B73" t="s">
         <v>475</v>
       </c>
@@ -29725,8 +31144,28 @@
       <c r="L73" t="s">
         <v>709</v>
       </c>
-    </row>
-    <row r="74" spans="2:12">
+      <c r="O73" t="s">
+        <v>538</v>
+      </c>
+      <c r="P73" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q73" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>South-West</v>
+      </c>
+      <c r="S73" t="s">
+        <v>538</v>
+      </c>
+      <c r="T73" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U73" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Ibadan</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21">
       <c r="B74" t="s">
         <v>475</v>
       </c>
@@ -29754,8 +31193,28 @@
       <c r="L74" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="75" spans="2:12">
+      <c r="O74" t="s">
+        <v>539</v>
+      </c>
+      <c r="P74" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q74" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>North-Central</v>
+      </c>
+      <c r="S74" t="s">
+        <v>539</v>
+      </c>
+      <c r="T74" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U74" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Ibadan</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21">
       <c r="B75" t="s">
         <v>475</v>
       </c>
@@ -29783,8 +31242,28 @@
       <c r="L75" t="s">
         <v>711</v>
       </c>
-    </row>
-    <row r="76" spans="2:12">
+      <c r="O75" t="s">
+        <v>540</v>
+      </c>
+      <c r="P75" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q75" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>South-West</v>
+      </c>
+      <c r="S75" t="s">
+        <v>540</v>
+      </c>
+      <c r="T75" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U75" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Ibadan</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21">
       <c r="B76" t="s">
         <v>475</v>
       </c>
@@ -29812,8 +31291,28 @@
       <c r="L76" t="s">
         <v>712</v>
       </c>
-    </row>
-    <row r="77" spans="2:12">
+      <c r="O76" t="s">
+        <v>541</v>
+      </c>
+      <c r="P76" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q76" s="9" t="str">
+        <f t="shared" ref="Q76:Q139" si="2">VLOOKUP(H76,$Y$12:$Z$45,2,FALSE)</f>
+        <v>South-West</v>
+      </c>
+      <c r="S76" t="s">
+        <v>541</v>
+      </c>
+      <c r="T76" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U76" s="9" t="str">
+        <f t="shared" ref="U76:U139" si="3">VLOOKUP(H76,$AC$12:$AD$45,2,FALSE)</f>
+        <v>Ibadan</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21">
       <c r="B77" t="s">
         <v>475</v>
       </c>
@@ -29841,8 +31340,28 @@
       <c r="L77" t="s">
         <v>713</v>
       </c>
-    </row>
-    <row r="78" spans="2:12">
+      <c r="O77" t="s">
+        <v>542</v>
+      </c>
+      <c r="P77" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q77" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>South-South</v>
+      </c>
+      <c r="S77" t="s">
+        <v>542</v>
+      </c>
+      <c r="T77" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U77" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>Benin</v>
+      </c>
+    </row>
+    <row r="78" spans="2:21">
       <c r="B78" t="s">
         <v>475</v>
       </c>
@@ -29870,8 +31389,28 @@
       <c r="L78" t="s">
         <v>714</v>
       </c>
-    </row>
-    <row r="79" spans="2:12">
+      <c r="O78" t="s">
+        <v>543</v>
+      </c>
+      <c r="P78" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q78" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>South-West</v>
+      </c>
+      <c r="S78" t="s">
+        <v>543</v>
+      </c>
+      <c r="T78" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U78" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>Benin</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21">
       <c r="B79" t="s">
         <v>475</v>
       </c>
@@ -29899,8 +31438,28 @@
       <c r="L79" t="s">
         <v>715</v>
       </c>
-    </row>
-    <row r="80" spans="2:12">
+      <c r="O79" t="s">
+        <v>544</v>
+      </c>
+      <c r="P79" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q79" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>South-South</v>
+      </c>
+      <c r="S79" t="s">
+        <v>544</v>
+      </c>
+      <c r="T79" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U79" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>Port Harcourt</v>
+      </c>
+    </row>
+    <row r="80" spans="2:21">
       <c r="B80" t="s">
         <v>475</v>
       </c>
@@ -29928,8 +31487,28 @@
       <c r="L80" t="s">
         <v>716</v>
       </c>
-    </row>
-    <row r="81" spans="2:12">
+      <c r="O80" t="s">
+        <v>545</v>
+      </c>
+      <c r="P80" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q80" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>South-South</v>
+      </c>
+      <c r="S80" t="s">
+        <v>545</v>
+      </c>
+      <c r="T80" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U80" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>Port Harcourt</v>
+      </c>
+    </row>
+    <row r="81" spans="2:21">
       <c r="B81" t="s">
         <v>475</v>
       </c>
@@ -29957,8 +31536,28 @@
       <c r="L81" t="s">
         <v>717</v>
       </c>
-    </row>
-    <row r="82" spans="2:12">
+      <c r="O81" t="s">
+        <v>546</v>
+      </c>
+      <c r="P81" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q81" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>South-South</v>
+      </c>
+      <c r="S81" t="s">
+        <v>546</v>
+      </c>
+      <c r="T81" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U81" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>Benin</v>
+      </c>
+    </row>
+    <row r="82" spans="2:21">
       <c r="B82" t="s">
         <v>475</v>
       </c>
@@ -29986,8 +31585,28 @@
       <c r="L82" t="s">
         <v>718</v>
       </c>
-    </row>
-    <row r="83" spans="2:12">
+      <c r="O82" t="s">
+        <v>547</v>
+      </c>
+      <c r="P82" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q82" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>South-South</v>
+      </c>
+      <c r="S82" t="s">
+        <v>547</v>
+      </c>
+      <c r="T82" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U82" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>Benin</v>
+      </c>
+    </row>
+    <row r="83" spans="2:21">
       <c r="B83" t="s">
         <v>475</v>
       </c>
@@ -30015,8 +31634,28 @@
       <c r="L83" t="s">
         <v>719</v>
       </c>
-    </row>
-    <row r="84" spans="2:12">
+      <c r="O83" t="s">
+        <v>548</v>
+      </c>
+      <c r="P83" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q83" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>South-South</v>
+      </c>
+      <c r="S83" t="s">
+        <v>548</v>
+      </c>
+      <c r="T83" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U83" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>Benin</v>
+      </c>
+    </row>
+    <row r="84" spans="2:21">
       <c r="B84" t="s">
         <v>475</v>
       </c>
@@ -30044,8 +31683,28 @@
       <c r="L84" t="s">
         <v>720</v>
       </c>
-    </row>
-    <row r="85" spans="2:12">
+      <c r="O84" t="s">
+        <v>549</v>
+      </c>
+      <c r="P84" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q84" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>South-South</v>
+      </c>
+      <c r="S84" t="s">
+        <v>549</v>
+      </c>
+      <c r="T84" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U84" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>Port Harcourt</v>
+      </c>
+    </row>
+    <row r="85" spans="2:21">
       <c r="B85" t="s">
         <v>475</v>
       </c>
@@ -30073,8 +31732,28 @@
       <c r="L85" t="s">
         <v>721</v>
       </c>
-    </row>
-    <row r="86" spans="2:12">
+      <c r="O85" t="s">
+        <v>550</v>
+      </c>
+      <c r="P85" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q85" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>South-South</v>
+      </c>
+      <c r="S85" t="s">
+        <v>550</v>
+      </c>
+      <c r="T85" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U85" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>Port Harcourt</v>
+      </c>
+    </row>
+    <row r="86" spans="2:21">
       <c r="B86" t="s">
         <v>475</v>
       </c>
@@ -30102,8 +31781,28 @@
       <c r="L86" t="s">
         <v>722</v>
       </c>
-    </row>
-    <row r="87" spans="2:12">
+      <c r="O86" t="s">
+        <v>551</v>
+      </c>
+      <c r="P86" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q86" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>South-South</v>
+      </c>
+      <c r="S86" t="s">
+        <v>551</v>
+      </c>
+      <c r="T86" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U86" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>Port Harcourt</v>
+      </c>
+    </row>
+    <row r="87" spans="2:21">
       <c r="B87" t="s">
         <v>475</v>
       </c>
@@ -30131,8 +31830,28 @@
       <c r="L87" t="s">
         <v>723</v>
       </c>
-    </row>
-    <row r="88" spans="2:12">
+      <c r="O87" t="s">
+        <v>552</v>
+      </c>
+      <c r="P87" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q87" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>North-East</v>
+      </c>
+      <c r="S87" t="s">
+        <v>552</v>
+      </c>
+      <c r="T87" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U87" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>Yola</v>
+      </c>
+    </row>
+    <row r="88" spans="2:21">
       <c r="B88" t="s">
         <v>475</v>
       </c>
@@ -30160,8 +31879,28 @@
       <c r="L88" t="s">
         <v>724</v>
       </c>
-    </row>
-    <row r="89" spans="2:12">
+      <c r="O88" t="s">
+        <v>553</v>
+      </c>
+      <c r="P88" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q88" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>North-East</v>
+      </c>
+      <c r="S88" t="s">
+        <v>553</v>
+      </c>
+      <c r="T88" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U88" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>Yola</v>
+      </c>
+    </row>
+    <row r="89" spans="2:21">
       <c r="B89" t="s">
         <v>475</v>
       </c>
@@ -30189,8 +31928,28 @@
       <c r="L89" t="s">
         <v>725</v>
       </c>
-    </row>
-    <row r="90" spans="2:12">
+      <c r="O89" t="s">
+        <v>554</v>
+      </c>
+      <c r="P89" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q89" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>North-East</v>
+      </c>
+      <c r="S89" t="s">
+        <v>554</v>
+      </c>
+      <c r="T89" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U89" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>Yola</v>
+      </c>
+    </row>
+    <row r="90" spans="2:21">
       <c r="B90" t="s">
         <v>475</v>
       </c>
@@ -30218,8 +31977,28 @@
       <c r="L90" t="s">
         <v>726</v>
       </c>
-    </row>
-    <row r="91" spans="2:12">
+      <c r="O90" t="s">
+        <v>555</v>
+      </c>
+      <c r="P90" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q90" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>North-East</v>
+      </c>
+      <c r="S90" t="s">
+        <v>555</v>
+      </c>
+      <c r="T90" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U90" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>Yola</v>
+      </c>
+    </row>
+    <row r="91" spans="2:21">
       <c r="B91" t="s">
         <v>475</v>
       </c>
@@ -30247,8 +32026,28 @@
       <c r="L91" t="s">
         <v>727</v>
       </c>
-    </row>
-    <row r="92" spans="2:12">
+      <c r="O91" t="s">
+        <v>556</v>
+      </c>
+      <c r="P91" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q91" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>North-East</v>
+      </c>
+      <c r="S91" t="s">
+        <v>556</v>
+      </c>
+      <c r="T91" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U91" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>Yola</v>
+      </c>
+    </row>
+    <row r="92" spans="2:21">
       <c r="B92" t="s">
         <v>475</v>
       </c>
@@ -30276,8 +32075,28 @@
       <c r="L92" t="s">
         <v>728</v>
       </c>
-    </row>
-    <row r="93" spans="2:12">
+      <c r="O92" t="s">
+        <v>557</v>
+      </c>
+      <c r="P92" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q92" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>North-East</v>
+      </c>
+      <c r="S92" t="s">
+        <v>557</v>
+      </c>
+      <c r="T92" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U92" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>Yola</v>
+      </c>
+    </row>
+    <row r="93" spans="2:21">
       <c r="B93" t="s">
         <v>475</v>
       </c>
@@ -30305,8 +32124,28 @@
       <c r="L93" t="s">
         <v>729</v>
       </c>
-    </row>
-    <row r="94" spans="2:12">
+      <c r="O93" t="s">
+        <v>558</v>
+      </c>
+      <c r="P93" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q93" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>North-Central</v>
+      </c>
+      <c r="S93" t="s">
+        <v>558</v>
+      </c>
+      <c r="T93" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U93" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>Jos</v>
+      </c>
+    </row>
+    <row r="94" spans="2:21">
       <c r="B94" t="s">
         <v>475</v>
       </c>
@@ -30334,8 +32173,28 @@
       <c r="L94" t="s">
         <v>730</v>
       </c>
-    </row>
-    <row r="95" spans="2:12">
+      <c r="O94" t="s">
+        <v>559</v>
+      </c>
+      <c r="P94" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q94" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>North-Central</v>
+      </c>
+      <c r="S94" t="s">
+        <v>559</v>
+      </c>
+      <c r="T94" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U94" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>Abuja</v>
+      </c>
+    </row>
+    <row r="95" spans="2:21">
       <c r="B95" t="s">
         <v>475</v>
       </c>
@@ -30363,8 +32222,28 @@
       <c r="L95" t="s">
         <v>731</v>
       </c>
-    </row>
-    <row r="96" spans="2:12">
+      <c r="O95" t="s">
+        <v>560</v>
+      </c>
+      <c r="P95" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q95" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>North-Central</v>
+      </c>
+      <c r="S95" t="s">
+        <v>560</v>
+      </c>
+      <c r="T95" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U95" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>Jos</v>
+      </c>
+    </row>
+    <row r="96" spans="2:21">
       <c r="B96" t="s">
         <v>475</v>
       </c>
@@ -30392,8 +32271,28 @@
       <c r="L96" t="s">
         <v>732</v>
       </c>
-    </row>
-    <row r="97" spans="2:12">
+      <c r="O96" t="s">
+        <v>561</v>
+      </c>
+      <c r="P96" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q96" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>North-Central</v>
+      </c>
+      <c r="S96" t="s">
+        <v>561</v>
+      </c>
+      <c r="T96" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U96" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>Jos</v>
+      </c>
+    </row>
+    <row r="97" spans="2:21">
       <c r="B97" t="s">
         <v>475</v>
       </c>
@@ -30421,8 +32320,28 @@
       <c r="L97" t="s">
         <v>733</v>
       </c>
-    </row>
-    <row r="98" spans="2:12">
+      <c r="O97" t="s">
+        <v>562</v>
+      </c>
+      <c r="P97" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q97" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>North-Central</v>
+      </c>
+      <c r="S97" t="s">
+        <v>562</v>
+      </c>
+      <c r="T97" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U97" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>Abuja</v>
+      </c>
+    </row>
+    <row r="98" spans="2:21">
       <c r="B98" t="s">
         <v>475</v>
       </c>
@@ -30450,8 +32369,28 @@
       <c r="L98" t="s">
         <v>734</v>
       </c>
-    </row>
-    <row r="99" spans="2:12">
+      <c r="O98" t="s">
+        <v>563</v>
+      </c>
+      <c r="P98" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q98" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>North-Central</v>
+      </c>
+      <c r="S98" t="s">
+        <v>563</v>
+      </c>
+      <c r="T98" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U98" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>Abuja</v>
+      </c>
+    </row>
+    <row r="99" spans="2:21">
       <c r="B99" t="s">
         <v>475</v>
       </c>
@@ -30479,8 +32418,28 @@
       <c r="L99" t="s">
         <v>735</v>
       </c>
-    </row>
-    <row r="100" spans="2:12">
+      <c r="O99" t="s">
+        <v>564</v>
+      </c>
+      <c r="P99" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q99" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>North-East</v>
+      </c>
+      <c r="S99" t="s">
+        <v>564</v>
+      </c>
+      <c r="T99" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U99" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>Jos</v>
+      </c>
+    </row>
+    <row r="100" spans="2:21">
       <c r="B100" t="s">
         <v>475</v>
       </c>
@@ -30508,8 +32467,28 @@
       <c r="L100" t="s">
         <v>736</v>
       </c>
-    </row>
-    <row r="101" spans="2:12">
+      <c r="O100" t="s">
+        <v>565</v>
+      </c>
+      <c r="P100" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q100" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>North-West</v>
+      </c>
+      <c r="S100" t="s">
+        <v>565</v>
+      </c>
+      <c r="T100" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U100" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>Kano</v>
+      </c>
+    </row>
+    <row r="101" spans="2:21">
       <c r="B101" t="s">
         <v>475</v>
       </c>
@@ -30537,8 +32516,28 @@
       <c r="L101" t="s">
         <v>737</v>
       </c>
-    </row>
-    <row r="102" spans="2:12">
+      <c r="O101" t="s">
+        <v>566</v>
+      </c>
+      <c r="P101" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q101" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>North-West</v>
+      </c>
+      <c r="S101" t="s">
+        <v>566</v>
+      </c>
+      <c r="T101" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U101" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>Kano</v>
+      </c>
+    </row>
+    <row r="102" spans="2:21">
       <c r="B102" t="s">
         <v>475</v>
       </c>
@@ -30566,8 +32565,28 @@
       <c r="L102" t="s">
         <v>738</v>
       </c>
-    </row>
-    <row r="103" spans="2:12">
+      <c r="O102" t="s">
+        <v>567</v>
+      </c>
+      <c r="P102" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q102" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>North-West</v>
+      </c>
+      <c r="S102" t="s">
+        <v>567</v>
+      </c>
+      <c r="T102" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U102" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>Kaduna</v>
+      </c>
+    </row>
+    <row r="103" spans="2:21">
       <c r="B103" t="s">
         <v>475</v>
       </c>
@@ -30595,8 +32614,28 @@
       <c r="L103" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="104" spans="2:12">
+      <c r="O103" t="s">
+        <v>568</v>
+      </c>
+      <c r="P103" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q103" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>North-West</v>
+      </c>
+      <c r="S103" t="s">
+        <v>568</v>
+      </c>
+      <c r="T103" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U103" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>Kaduna</v>
+      </c>
+    </row>
+    <row r="104" spans="2:21">
       <c r="B104" t="s">
         <v>475</v>
       </c>
@@ -30624,8 +32663,28 @@
       <c r="L104" t="s">
         <v>740</v>
       </c>
-    </row>
-    <row r="105" spans="2:12">
+      <c r="O104" t="s">
+        <v>569</v>
+      </c>
+      <c r="P104" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q104" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>North-Central</v>
+      </c>
+      <c r="S104" t="s">
+        <v>569</v>
+      </c>
+      <c r="T104" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U104" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>Abuja</v>
+      </c>
+    </row>
+    <row r="105" spans="2:21">
       <c r="B105" t="s">
         <v>475</v>
       </c>
@@ -30653,8 +32712,28 @@
       <c r="L105" t="s">
         <v>741</v>
       </c>
-    </row>
-    <row r="106" spans="2:12">
+      <c r="O105" t="s">
+        <v>570</v>
+      </c>
+      <c r="P105" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q105" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>North-West</v>
+      </c>
+      <c r="S105" t="s">
+        <v>570</v>
+      </c>
+      <c r="T105" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U105" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>Kaduna</v>
+      </c>
+    </row>
+    <row r="106" spans="2:21">
       <c r="B106" t="s">
         <v>475</v>
       </c>
@@ -30682,8 +32761,28 @@
       <c r="L106" t="s">
         <v>742</v>
       </c>
-    </row>
-    <row r="107" spans="2:12">
+      <c r="O106" t="s">
+        <v>571</v>
+      </c>
+      <c r="P106" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q106" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>North-Central</v>
+      </c>
+      <c r="S106" t="s">
+        <v>571</v>
+      </c>
+      <c r="T106" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U106" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>Abuja</v>
+      </c>
+    </row>
+    <row r="107" spans="2:21">
       <c r="B107" t="s">
         <v>475</v>
       </c>
@@ -30711,8 +32810,28 @@
       <c r="L107" t="s">
         <v>743</v>
       </c>
-    </row>
-    <row r="108" spans="2:12">
+      <c r="O107" t="s">
+        <v>572</v>
+      </c>
+      <c r="P107" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q107" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>North-West</v>
+      </c>
+      <c r="S107" t="s">
+        <v>572</v>
+      </c>
+      <c r="T107" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U107" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>Kaduna</v>
+      </c>
+    </row>
+    <row r="108" spans="2:21">
       <c r="B108" t="s">
         <v>475</v>
       </c>
@@ -30740,8 +32859,28 @@
       <c r="L108" t="s">
         <v>744</v>
       </c>
-    </row>
-    <row r="109" spans="2:12">
+      <c r="O108" t="s">
+        <v>573</v>
+      </c>
+      <c r="P108" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q108" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>North-Central</v>
+      </c>
+      <c r="S108" t="s">
+        <v>573</v>
+      </c>
+      <c r="T108" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U108" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>Ibadan</v>
+      </c>
+    </row>
+    <row r="109" spans="2:21">
       <c r="B109" t="s">
         <v>475</v>
       </c>
@@ -30769,8 +32908,28 @@
       <c r="L109" t="s">
         <v>745</v>
       </c>
-    </row>
-    <row r="110" spans="2:12">
+      <c r="O109" t="s">
+        <v>574</v>
+      </c>
+      <c r="P109" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q109" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>North-Central</v>
+      </c>
+      <c r="S109" t="s">
+        <v>574</v>
+      </c>
+      <c r="T109" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U109" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>Jos</v>
+      </c>
+    </row>
+    <row r="110" spans="2:21">
       <c r="B110" t="s">
         <v>475</v>
       </c>
@@ -30798,8 +32957,28 @@
       <c r="L110" t="s">
         <v>746</v>
       </c>
-    </row>
-    <row r="111" spans="2:12">
+      <c r="O110" t="s">
+        <v>575</v>
+      </c>
+      <c r="P110" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q110" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>North-East</v>
+      </c>
+      <c r="S110" t="s">
+        <v>575</v>
+      </c>
+      <c r="T110" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U110" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>Yola</v>
+      </c>
+    </row>
+    <row r="111" spans="2:21">
       <c r="B111" t="s">
         <v>475</v>
       </c>
@@ -30827,8 +33006,28 @@
       <c r="L111" t="s">
         <v>747</v>
       </c>
-    </row>
-    <row r="112" spans="2:12">
+      <c r="O111" t="s">
+        <v>576</v>
+      </c>
+      <c r="P111" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q111" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>North-East</v>
+      </c>
+      <c r="S111" t="s">
+        <v>576</v>
+      </c>
+      <c r="T111" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U111" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>Yola</v>
+      </c>
+    </row>
+    <row r="112" spans="2:21">
       <c r="B112" t="s">
         <v>475</v>
       </c>
@@ -30856,8 +33055,28 @@
       <c r="L112" t="s">
         <v>748</v>
       </c>
-    </row>
-    <row r="113" spans="2:12">
+      <c r="O112" t="s">
+        <v>577</v>
+      </c>
+      <c r="P112" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q112" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>North-East</v>
+      </c>
+      <c r="S112" t="s">
+        <v>577</v>
+      </c>
+      <c r="T112" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U112" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>Yola</v>
+      </c>
+    </row>
+    <row r="113" spans="2:21">
       <c r="B113" t="s">
         <v>475</v>
       </c>
@@ -30885,8 +33104,28 @@
       <c r="L113" t="s">
         <v>749</v>
       </c>
-    </row>
-    <row r="114" spans="2:12">
+      <c r="O113" t="s">
+        <v>578</v>
+      </c>
+      <c r="P113" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q113" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>North-Central</v>
+      </c>
+      <c r="S113" t="s">
+        <v>578</v>
+      </c>
+      <c r="T113" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U113" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>Jos</v>
+      </c>
+    </row>
+    <row r="114" spans="2:21">
       <c r="B114" t="s">
         <v>475</v>
       </c>
@@ -30914,8 +33153,28 @@
       <c r="L114" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="115" spans="2:12">
+      <c r="O114" t="s">
+        <v>579</v>
+      </c>
+      <c r="P114" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q114" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>North-Central</v>
+      </c>
+      <c r="S114" t="s">
+        <v>579</v>
+      </c>
+      <c r="T114" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U114" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>Ibadan</v>
+      </c>
+    </row>
+    <row r="115" spans="2:21">
       <c r="B115" t="s">
         <v>475</v>
       </c>
@@ -30943,8 +33202,28 @@
       <c r="L115" t="s">
         <v>751</v>
       </c>
-    </row>
-    <row r="116" spans="2:12">
+      <c r="O115" t="s">
+        <v>580</v>
+      </c>
+      <c r="P115" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q115" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>North-Central</v>
+      </c>
+      <c r="S115" t="s">
+        <v>580</v>
+      </c>
+      <c r="T115" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U115" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>Ibadan</v>
+      </c>
+    </row>
+    <row r="116" spans="2:21">
       <c r="B116" t="s">
         <v>475</v>
       </c>
@@ -30972,8 +33251,28 @@
       <c r="L116" t="s">
         <v>752</v>
       </c>
-    </row>
-    <row r="117" spans="2:12">
+      <c r="O116" t="s">
+        <v>581</v>
+      </c>
+      <c r="P116" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q116" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>Unknown</v>
+      </c>
+      <c r="S116" t="s">
+        <v>581</v>
+      </c>
+      <c r="T116" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U116" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>Unknown</v>
+      </c>
+    </row>
+    <row r="117" spans="2:21">
       <c r="B117" t="s">
         <v>475</v>
       </c>
@@ -31001,8 +33300,28 @@
       <c r="L117" t="s">
         <v>753</v>
       </c>
-    </row>
-    <row r="118" spans="2:12">
+      <c r="O117" t="s">
+        <v>582</v>
+      </c>
+      <c r="P117" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q117" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>North-Central</v>
+      </c>
+      <c r="S117" t="s">
+        <v>582</v>
+      </c>
+      <c r="T117" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U117" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>Abuja</v>
+      </c>
+    </row>
+    <row r="118" spans="2:21">
       <c r="B118" t="s">
         <v>475</v>
       </c>
@@ -31030,8 +33349,28 @@
       <c r="L118" t="s">
         <v>754</v>
       </c>
-    </row>
-    <row r="119" spans="2:12">
+      <c r="O118" t="s">
+        <v>583</v>
+      </c>
+      <c r="P118" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q118" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>North-West</v>
+      </c>
+      <c r="S118" t="s">
+        <v>583</v>
+      </c>
+      <c r="T118" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U118" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>Kaduna</v>
+      </c>
+    </row>
+    <row r="119" spans="2:21">
       <c r="B119" t="s">
         <v>475</v>
       </c>
@@ -31059,8 +33398,28 @@
       <c r="L119" t="s">
         <v>755</v>
       </c>
-    </row>
-    <row r="120" spans="2:12">
+      <c r="O119" t="s">
+        <v>584</v>
+      </c>
+      <c r="P119" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q119" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>North-West</v>
+      </c>
+      <c r="S119" t="s">
+        <v>584</v>
+      </c>
+      <c r="T119" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U119" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>Kaduna</v>
+      </c>
+    </row>
+    <row r="120" spans="2:21">
       <c r="B120" t="s">
         <v>475</v>
       </c>
@@ -31088,8 +33447,28 @@
       <c r="L120" t="s">
         <v>756</v>
       </c>
-    </row>
-    <row r="121" spans="2:12">
+      <c r="O120" t="s">
+        <v>585</v>
+      </c>
+      <c r="P120" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q120" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>North-Central</v>
+      </c>
+      <c r="S120" t="s">
+        <v>585</v>
+      </c>
+      <c r="T120" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U120" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>Abuja</v>
+      </c>
+    </row>
+    <row r="121" spans="2:21">
       <c r="B121" t="s">
         <v>475</v>
       </c>
@@ -31117,8 +33496,28 @@
       <c r="L121" t="s">
         <v>757</v>
       </c>
-    </row>
-    <row r="122" spans="2:12">
+      <c r="O121" t="s">
+        <v>586</v>
+      </c>
+      <c r="P121" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q121" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>North-West</v>
+      </c>
+      <c r="S121" t="s">
+        <v>586</v>
+      </c>
+      <c r="T121" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U121" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>Kaduna</v>
+      </c>
+    </row>
+    <row r="122" spans="2:21">
       <c r="B122" t="s">
         <v>475</v>
       </c>
@@ -31146,8 +33545,28 @@
       <c r="L122" t="s">
         <v>758</v>
       </c>
-    </row>
-    <row r="123" spans="2:12">
+      <c r="O122" t="s">
+        <v>587</v>
+      </c>
+      <c r="P122" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q122" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>North-West</v>
+      </c>
+      <c r="S122" t="s">
+        <v>587</v>
+      </c>
+      <c r="T122" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U122" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>Kaduna</v>
+      </c>
+    </row>
+    <row r="123" spans="2:21">
       <c r="B123" t="s">
         <v>475</v>
       </c>
@@ -31175,8 +33594,28 @@
       <c r="L123" t="s">
         <v>759</v>
       </c>
-    </row>
-    <row r="124" spans="2:12">
+      <c r="O123" t="s">
+        <v>588</v>
+      </c>
+      <c r="P123" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q123" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>North-West</v>
+      </c>
+      <c r="S123" t="s">
+        <v>588</v>
+      </c>
+      <c r="T123" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U123" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>Kaduna</v>
+      </c>
+    </row>
+    <row r="124" spans="2:21">
       <c r="B124" t="s">
         <v>475</v>
       </c>
@@ -31204,8 +33643,28 @@
       <c r="L124" t="s">
         <v>760</v>
       </c>
-    </row>
-    <row r="125" spans="2:12">
+      <c r="O124" t="s">
+        <v>589</v>
+      </c>
+      <c r="P124" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q124" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>North-East</v>
+      </c>
+      <c r="S124" t="s">
+        <v>589</v>
+      </c>
+      <c r="T124" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U124" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>Yola</v>
+      </c>
+    </row>
+    <row r="125" spans="2:21">
       <c r="B125" t="s">
         <v>475</v>
       </c>
@@ -31233,8 +33692,28 @@
       <c r="L125" t="s">
         <v>761</v>
       </c>
-    </row>
-    <row r="126" spans="2:12">
+      <c r="O125" t="s">
+        <v>590</v>
+      </c>
+      <c r="P125" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q125" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>North-East</v>
+      </c>
+      <c r="S125" t="s">
+        <v>590</v>
+      </c>
+      <c r="T125" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U125" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>Yola</v>
+      </c>
+    </row>
+    <row r="126" spans="2:21">
       <c r="B126" t="s">
         <v>475</v>
       </c>
@@ -31262,8 +33741,28 @@
       <c r="L126" t="s">
         <v>762</v>
       </c>
-    </row>
-    <row r="127" spans="2:12">
+      <c r="O126" t="s">
+        <v>591</v>
+      </c>
+      <c r="P126" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q126" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>North-East</v>
+      </c>
+      <c r="S126" t="s">
+        <v>591</v>
+      </c>
+      <c r="T126" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U126" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>Yola</v>
+      </c>
+    </row>
+    <row r="127" spans="2:21">
       <c r="B127" t="s">
         <v>475</v>
       </c>
@@ -31291,8 +33790,28 @@
       <c r="L127" t="s">
         <v>763</v>
       </c>
-    </row>
-    <row r="128" spans="2:12">
+      <c r="O127" t="s">
+        <v>592</v>
+      </c>
+      <c r="P127" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q127" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>North-East</v>
+      </c>
+      <c r="S127" t="s">
+        <v>592</v>
+      </c>
+      <c r="T127" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U127" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>Yola</v>
+      </c>
+    </row>
+    <row r="128" spans="2:21">
       <c r="B128" t="s">
         <v>475</v>
       </c>
@@ -31320,8 +33839,28 @@
       <c r="L128" t="s">
         <v>764</v>
       </c>
-    </row>
-    <row r="129" spans="2:12">
+      <c r="O128" t="s">
+        <v>593</v>
+      </c>
+      <c r="P128" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q128" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>North-East</v>
+      </c>
+      <c r="S128" t="s">
+        <v>593</v>
+      </c>
+      <c r="T128" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U128" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>Jos</v>
+      </c>
+    </row>
+    <row r="129" spans="2:21">
       <c r="B129" t="s">
         <v>475</v>
       </c>
@@ -31349,8 +33888,28 @@
       <c r="L129" t="s">
         <v>765</v>
       </c>
-    </row>
-    <row r="130" spans="2:12">
+      <c r="O129" t="s">
+        <v>594</v>
+      </c>
+      <c r="P129" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q129" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>North-East</v>
+      </c>
+      <c r="S129" t="s">
+        <v>594</v>
+      </c>
+      <c r="T129" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U129" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>Jos</v>
+      </c>
+    </row>
+    <row r="130" spans="2:21">
       <c r="B130" t="s">
         <v>475</v>
       </c>
@@ -31378,8 +33937,28 @@
       <c r="L130" t="s">
         <v>766</v>
       </c>
-    </row>
-    <row r="131" spans="2:12">
+      <c r="O130" t="s">
+        <v>595</v>
+      </c>
+      <c r="P130" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q130" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>North-West</v>
+      </c>
+      <c r="S130" t="s">
+        <v>595</v>
+      </c>
+      <c r="T130" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U130" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>Kano</v>
+      </c>
+    </row>
+    <row r="131" spans="2:21">
       <c r="B131" t="s">
         <v>475</v>
       </c>
@@ -31407,8 +33986,28 @@
       <c r="L131" t="s">
         <v>767</v>
       </c>
-    </row>
-    <row r="132" spans="2:12">
+      <c r="O131" t="s">
+        <v>596</v>
+      </c>
+      <c r="P131" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q131" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>North-West</v>
+      </c>
+      <c r="S131" t="s">
+        <v>596</v>
+      </c>
+      <c r="T131" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U131" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>Kaduna</v>
+      </c>
+    </row>
+    <row r="132" spans="2:21">
       <c r="B132" t="s">
         <v>475</v>
       </c>
@@ -31436,8 +34035,28 @@
       <c r="L132" t="s">
         <v>768</v>
       </c>
-    </row>
-    <row r="133" spans="2:12">
+      <c r="O132" t="s">
+        <v>597</v>
+      </c>
+      <c r="P132" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q132" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>North-East</v>
+      </c>
+      <c r="S132" t="s">
+        <v>597</v>
+      </c>
+      <c r="T132" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U132" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>Jos</v>
+      </c>
+    </row>
+    <row r="133" spans="2:21">
       <c r="B133" t="s">
         <v>475</v>
       </c>
@@ -31465,8 +34084,28 @@
       <c r="L133" t="s">
         <v>769</v>
       </c>
-    </row>
-    <row r="134" spans="2:12">
+      <c r="O133" t="s">
+        <v>598</v>
+      </c>
+      <c r="P133" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q133" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>North-West</v>
+      </c>
+      <c r="S133" t="s">
+        <v>598</v>
+      </c>
+      <c r="T133" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U133" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>Kano</v>
+      </c>
+    </row>
+    <row r="134" spans="2:21">
       <c r="B134" t="s">
         <v>475</v>
       </c>
@@ -31494,8 +34133,28 @@
       <c r="L134" t="s">
         <v>770</v>
       </c>
-    </row>
-    <row r="135" spans="2:12">
+      <c r="O134" t="s">
+        <v>599</v>
+      </c>
+      <c r="P134" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q134" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>North-East</v>
+      </c>
+      <c r="S134" t="s">
+        <v>599</v>
+      </c>
+      <c r="T134" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U134" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>Yola</v>
+      </c>
+    </row>
+    <row r="135" spans="2:21">
       <c r="B135" t="s">
         <v>475</v>
       </c>
@@ -31523,8 +34182,28 @@
       <c r="L135" t="s">
         <v>771</v>
       </c>
-    </row>
-    <row r="136" spans="2:12">
+      <c r="O135" t="s">
+        <v>600</v>
+      </c>
+      <c r="P135" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q135" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>North-East</v>
+      </c>
+      <c r="S135" t="s">
+        <v>600</v>
+      </c>
+      <c r="T135" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U135" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>Jos</v>
+      </c>
+    </row>
+    <row r="136" spans="2:21">
       <c r="B136" t="s">
         <v>475</v>
       </c>
@@ -31552,8 +34231,28 @@
       <c r="L136" t="s">
         <v>772</v>
       </c>
-    </row>
-    <row r="137" spans="2:12">
+      <c r="O136" t="s">
+        <v>601</v>
+      </c>
+      <c r="P136" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q136" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>South-West</v>
+      </c>
+      <c r="S136" t="s">
+        <v>601</v>
+      </c>
+      <c r="T136" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U136" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>Ibadan</v>
+      </c>
+    </row>
+    <row r="137" spans="2:21">
       <c r="B137" t="s">
         <v>475</v>
       </c>
@@ -31581,8 +34280,28 @@
       <c r="L137" t="s">
         <v>773</v>
       </c>
-    </row>
-    <row r="138" spans="2:12">
+      <c r="O137" t="s">
+        <v>602</v>
+      </c>
+      <c r="P137" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q137" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>Unknown</v>
+      </c>
+      <c r="S137" t="s">
+        <v>602</v>
+      </c>
+      <c r="T137" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U137" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>Unknown</v>
+      </c>
+    </row>
+    <row r="138" spans="2:21">
       <c r="B138" t="s">
         <v>475</v>
       </c>
@@ -31610,8 +34329,28 @@
       <c r="L138" t="s">
         <v>774</v>
       </c>
-    </row>
-    <row r="139" spans="2:12">
+      <c r="O138" t="s">
+        <v>603</v>
+      </c>
+      <c r="P138" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q138" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>Unknown</v>
+      </c>
+      <c r="S138" t="s">
+        <v>603</v>
+      </c>
+      <c r="T138" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U138" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>Unknown</v>
+      </c>
+    </row>
+    <row r="139" spans="2:21">
       <c r="B139" t="s">
         <v>475</v>
       </c>
@@ -31639,8 +34378,28 @@
       <c r="L139" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="140" spans="2:12">
+      <c r="O139" t="s">
+        <v>604</v>
+      </c>
+      <c r="P139" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q139" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>Unknown</v>
+      </c>
+      <c r="S139" t="s">
+        <v>604</v>
+      </c>
+      <c r="T139" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U139" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>Unknown</v>
+      </c>
+    </row>
+    <row r="140" spans="2:21">
       <c r="B140" t="s">
         <v>475</v>
       </c>
@@ -31668,8 +34427,28 @@
       <c r="L140" t="s">
         <v>776</v>
       </c>
-    </row>
-    <row r="141" spans="2:12">
+      <c r="O140" t="s">
+        <v>605</v>
+      </c>
+      <c r="P140" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q140" s="9" t="str">
+        <f t="shared" ref="Q140:Q145" si="4">VLOOKUP(H140,$Y$12:$Z$45,2,FALSE)</f>
+        <v>Unknown</v>
+      </c>
+      <c r="S140" t="s">
+        <v>605</v>
+      </c>
+      <c r="T140" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U140" s="9" t="str">
+        <f t="shared" ref="U140:U145" si="5">VLOOKUP(H140,$AC$12:$AD$45,2,FALSE)</f>
+        <v>Unknown</v>
+      </c>
+    </row>
+    <row r="141" spans="2:21">
       <c r="B141" t="s">
         <v>475</v>
       </c>
@@ -31697,8 +34476,28 @@
       <c r="L141" t="s">
         <v>777</v>
       </c>
-    </row>
-    <row r="142" spans="2:12">
+      <c r="O141" t="s">
+        <v>606</v>
+      </c>
+      <c r="P141" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q141" s="9" t="str">
+        <f t="shared" si="4"/>
+        <v>Unknown</v>
+      </c>
+      <c r="S141" t="s">
+        <v>606</v>
+      </c>
+      <c r="T141" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U141" s="9" t="str">
+        <f t="shared" si="5"/>
+        <v>Unknown</v>
+      </c>
+    </row>
+    <row r="142" spans="2:21">
       <c r="B142" t="s">
         <v>475</v>
       </c>
@@ -31726,8 +34525,28 @@
       <c r="L142" t="s">
         <v>778</v>
       </c>
-    </row>
-    <row r="143" spans="2:12">
+      <c r="O142" t="s">
+        <v>607</v>
+      </c>
+      <c r="P142" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q142" s="9" t="str">
+        <f t="shared" si="4"/>
+        <v>Unknown</v>
+      </c>
+      <c r="S142" t="s">
+        <v>607</v>
+      </c>
+      <c r="T142" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U142" s="9" t="str">
+        <f t="shared" si="5"/>
+        <v>Unknown</v>
+      </c>
+    </row>
+    <row r="143" spans="2:21">
       <c r="B143" t="s">
         <v>475</v>
       </c>
@@ -31755,8 +34574,28 @@
       <c r="L143" t="s">
         <v>779</v>
       </c>
-    </row>
-    <row r="144" spans="2:12">
+      <c r="O143" t="s">
+        <v>608</v>
+      </c>
+      <c r="P143" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q143" s="9" t="str">
+        <f t="shared" si="4"/>
+        <v>Unknown</v>
+      </c>
+      <c r="S143" t="s">
+        <v>608</v>
+      </c>
+      <c r="T143" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U143" s="9" t="str">
+        <f t="shared" si="5"/>
+        <v>Unknown</v>
+      </c>
+    </row>
+    <row r="144" spans="2:21">
       <c r="B144" t="s">
         <v>475</v>
       </c>
@@ -31784,8 +34623,28 @@
       <c r="L144" t="s">
         <v>780</v>
       </c>
-    </row>
-    <row r="145" spans="2:12">
+      <c r="O144" t="s">
+        <v>609</v>
+      </c>
+      <c r="P144" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q144" s="9" t="str">
+        <f t="shared" si="4"/>
+        <v>Unknown</v>
+      </c>
+      <c r="S144" t="s">
+        <v>609</v>
+      </c>
+      <c r="T144" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U144" s="9" t="str">
+        <f t="shared" si="5"/>
+        <v>Unknown</v>
+      </c>
+    </row>
+    <row r="145" spans="2:21">
       <c r="B145" t="s">
         <v>475</v>
       </c>
@@ -31812,6 +34671,26 @@
       </c>
       <c r="L145" t="s">
         <v>781</v>
+      </c>
+      <c r="O145" t="s">
+        <v>610</v>
+      </c>
+      <c r="P145" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q145" s="9" t="str">
+        <f t="shared" si="4"/>
+        <v>Unknown</v>
+      </c>
+      <c r="S145" t="s">
+        <v>610</v>
+      </c>
+      <c r="T145" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="U145" s="9" t="str">
+        <f t="shared" si="5"/>
+        <v>Unknown</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_NGA_grids_kan/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_NGA_grids_kan/ReportDefs_vervestacks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NGA_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95995D16-F110-4934-AE85-F946516ACD78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{96BDD199-9496-4C03-A739-FA4365C0BA1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ScenMap" sheetId="56" r:id="rId1"/>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6698" uniqueCount="940">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5943" uniqueCount="920">
   <si>
     <t>Unit</t>
   </si>
@@ -2843,66 +2843,6 @@
   </si>
   <si>
     <t>NGA-elc_wof_010</t>
-  </si>
-  <si>
-    <t>South-East</t>
-  </si>
-  <si>
-    <t>North-East</t>
-  </si>
-  <si>
-    <t>North-Central</t>
-  </si>
-  <si>
-    <t>South-South</t>
-  </si>
-  <si>
-    <t>North-West</t>
-  </si>
-  <si>
-    <t>South-West</t>
-  </si>
-  <si>
-    <t>Yola</t>
-  </si>
-  <si>
-    <t>Jos</t>
-  </si>
-  <si>
-    <t>Port Harcourt</t>
-  </si>
-  <si>
-    <t>Benin</t>
-  </si>
-  <si>
-    <t>Abuja</t>
-  </si>
-  <si>
-    <t>Ibadan</t>
-  </si>
-  <si>
-    <t>Ikeja</t>
-  </si>
-  <si>
-    <t>reg_geopol</t>
-  </si>
-  <si>
-    <t>Grouping</t>
-  </si>
-  <si>
-    <t>State</t>
-  </si>
-  <si>
-    <t>GroupName</t>
-  </si>
-  <si>
-    <t>Geopolitical</t>
-  </si>
-  <si>
-    <t>DisCos</t>
-  </si>
-  <si>
-    <t>reg_discom</t>
   </si>
 </sst>
 </file>
@@ -3111,7 +3051,7 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
@@ -3120,12 +3060,6 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="18"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="19"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -22873,10 +22807,10 @@
       <c r="N4" t="s">
         <v>74</v>
       </c>
-      <c r="T4" s="10" t="s">
+      <c r="T4" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="U4" s="10"/>
+      <c r="U4" s="8"/>
     </row>
     <row r="5" spans="1:21">
       <c r="A5" t="s">
@@ -24644,7 +24578,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0138AFE7-544F-41FE-BD3C-380014FB1A8F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{968A3CF8-471D-402F-B706-4A6B04C21177}">
   <dimension ref="B9:H145"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -27382,18 +27316,11 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0D089EA-DA44-42D6-94D7-5FF8F138B66A}">
-  <dimension ref="B9:AD145"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{132F03D2-DD83-40E9-A246-CA00D7A1F898}">
+  <dimension ref="B9:L145"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
-  <cols>
-    <col min="16" max="16" width="10.1328125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="19.9296875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.59765625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.1328125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="9.73046875" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="9" spans="2:30">
+    <row r="9" spans="2:12">
       <c r="B9" t="s">
         <v>59</v>
       </c>
@@ -27403,14 +27330,8 @@
       <c r="J9" t="s">
         <v>68</v>
       </c>
-      <c r="O9" t="s">
-        <v>59</v>
-      </c>
-      <c r="S9" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="10" spans="2:30">
+    </row>
+    <row r="10" spans="2:12">
       <c r="B10" t="s">
         <v>48</v>
       </c>
@@ -27438,26 +27359,8 @@
       <c r="L10" t="s">
         <v>50</v>
       </c>
-      <c r="O10" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="P10" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q10" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="S10" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="T10" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="U10" s="8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" spans="2:30">
+    </row>
+    <row r="11" spans="2:12">
       <c r="B11" t="s">
         <v>475</v>
       </c>
@@ -27485,37 +27388,8 @@
       <c r="L11" t="s">
         <v>647</v>
       </c>
-      <c r="O11" s="9" t="s">
-        <v>476</v>
-      </c>
-      <c r="P11" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q11" s="9" t="str">
-        <f>VLOOKUP(H11,$Y$12:$Z$45,2,FALSE)</f>
-        <v>North-West</v>
-      </c>
-      <c r="S11" s="9" t="s">
-        <v>476</v>
-      </c>
-      <c r="T11" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U11" s="9" t="str">
-        <f>VLOOKUP(H11,$AC$12:$AD$45,2,FALSE)</f>
-        <v>Kaduna</v>
-      </c>
-      <c r="X11" s="8" t="s">
-        <v>934</v>
-      </c>
-      <c r="Y11" s="8" t="s">
-        <v>935</v>
-      </c>
-      <c r="Z11" s="8" t="s">
-        <v>936</v>
-      </c>
-    </row>
-    <row r="12" spans="2:30">
+    </row>
+    <row r="12" spans="2:12">
       <c r="B12" t="s">
         <v>475</v>
       </c>
@@ -27543,46 +27417,8 @@
       <c r="L12" t="s">
         <v>648</v>
       </c>
-      <c r="O12" s="9" t="s">
-        <v>477</v>
-      </c>
-      <c r="P12" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q12" s="9" t="str">
-        <f t="shared" ref="Q12:Q75" si="0">VLOOKUP(H12,$Y$12:$Z$45,2,FALSE)</f>
-        <v>North-Central</v>
-      </c>
-      <c r="S12" s="9" t="s">
-        <v>477</v>
-      </c>
-      <c r="T12" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U12" s="9" t="str">
-        <f t="shared" ref="U12:U75" si="1">VLOOKUP(H12,$AC$12:$AD$45,2,FALSE)</f>
-        <v>Abuja</v>
-      </c>
-      <c r="X12" s="9" t="s">
-        <v>937</v>
-      </c>
-      <c r="Y12" s="9" t="s">
-        <v>612</v>
-      </c>
-      <c r="Z12" s="9" t="s">
-        <v>924</v>
-      </c>
-      <c r="AB12" s="9" t="s">
-        <v>938</v>
-      </c>
-      <c r="AC12" s="9" t="s">
-        <v>612</v>
-      </c>
-      <c r="AD12" s="9" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="13" spans="2:30">
+    </row>
+    <row r="13" spans="2:12">
       <c r="B13" t="s">
         <v>475</v>
       </c>
@@ -27610,46 +27446,8 @@
       <c r="L13" t="s">
         <v>649</v>
       </c>
-      <c r="O13" s="9" t="s">
-        <v>478</v>
-      </c>
-      <c r="P13" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q13" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>South-West</v>
-      </c>
-      <c r="S13" s="9" t="s">
-        <v>478</v>
-      </c>
-      <c r="T13" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U13" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Ikeja</v>
-      </c>
-      <c r="X13" s="9" t="s">
-        <v>937</v>
-      </c>
-      <c r="Y13" s="9" t="s">
-        <v>613</v>
-      </c>
-      <c r="Z13" s="9" t="s">
-        <v>922</v>
-      </c>
-      <c r="AB13" s="9" t="s">
-        <v>938</v>
-      </c>
-      <c r="AC13" s="9" t="s">
-        <v>613</v>
-      </c>
-      <c r="AD13" s="9" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="14" spans="2:30">
+    </row>
+    <row r="14" spans="2:12">
       <c r="B14" t="s">
         <v>475</v>
       </c>
@@ -27677,46 +27475,8 @@
       <c r="L14" t="s">
         <v>650</v>
       </c>
-      <c r="O14" s="9" t="s">
-        <v>479</v>
-      </c>
-      <c r="P14" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q14" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>North-Central</v>
-      </c>
-      <c r="S14" s="9" t="s">
-        <v>479</v>
-      </c>
-      <c r="T14" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U14" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Abuja</v>
-      </c>
-      <c r="X14" s="9" t="s">
-        <v>937</v>
-      </c>
-      <c r="Y14" s="9" t="s">
-        <v>614</v>
-      </c>
-      <c r="Z14" s="9" t="s">
-        <v>925</v>
-      </c>
-      <c r="AB14" s="9" t="s">
-        <v>938</v>
-      </c>
-      <c r="AC14" s="9" t="s">
-        <v>614</v>
-      </c>
-      <c r="AD14" s="9" t="s">
-        <v>932</v>
-      </c>
-    </row>
-    <row r="15" spans="2:30">
+    </row>
+    <row r="15" spans="2:12">
       <c r="B15" t="s">
         <v>475</v>
       </c>
@@ -27744,46 +27504,8 @@
       <c r="L15" t="s">
         <v>651</v>
       </c>
-      <c r="O15" s="9" t="s">
-        <v>480</v>
-      </c>
-      <c r="P15" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q15" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>North-Central</v>
-      </c>
-      <c r="S15" s="9" t="s">
-        <v>480</v>
-      </c>
-      <c r="T15" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U15" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Jos</v>
-      </c>
-      <c r="X15" s="9" t="s">
-        <v>937</v>
-      </c>
-      <c r="Y15" s="9" t="s">
-        <v>615</v>
-      </c>
-      <c r="Z15" s="9" t="s">
-        <v>922</v>
-      </c>
-      <c r="AB15" s="9" t="s">
-        <v>938</v>
-      </c>
-      <c r="AC15" s="9" t="s">
-        <v>615</v>
-      </c>
-      <c r="AD15" s="9" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="16" spans="2:30">
+    </row>
+    <row r="16" spans="2:12">
       <c r="B16" t="s">
         <v>475</v>
       </c>
@@ -27811,46 +27533,8 @@
       <c r="L16" t="s">
         <v>652</v>
       </c>
-      <c r="O16" s="9" t="s">
-        <v>481</v>
-      </c>
-      <c r="P16" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q16" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>North-East</v>
-      </c>
-      <c r="S16" s="9" t="s">
-        <v>481</v>
-      </c>
-      <c r="T16" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U16" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Jos</v>
-      </c>
-      <c r="X16" s="9" t="s">
-        <v>937</v>
-      </c>
-      <c r="Y16" s="9" t="s">
-        <v>616</v>
-      </c>
-      <c r="Z16" s="9" t="s">
-        <v>922</v>
-      </c>
-      <c r="AB16" s="9" t="s">
-        <v>938</v>
-      </c>
-      <c r="AC16" s="9" t="s">
-        <v>616</v>
-      </c>
-      <c r="AD16" s="9" t="s">
-        <v>927</v>
-      </c>
-    </row>
-    <row r="17" spans="2:30">
+    </row>
+    <row r="17" spans="2:12">
       <c r="B17" t="s">
         <v>475</v>
       </c>
@@ -27878,46 +27562,8 @@
       <c r="L17" t="s">
         <v>653</v>
       </c>
-      <c r="O17" s="9" t="s">
-        <v>482</v>
-      </c>
-      <c r="P17" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q17" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>North-East</v>
-      </c>
-      <c r="S17" s="9" t="s">
-        <v>482</v>
-      </c>
-      <c r="T17" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U17" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Yola</v>
-      </c>
-      <c r="X17" s="9" t="s">
-        <v>937</v>
-      </c>
-      <c r="Y17" s="9" t="s">
-        <v>617</v>
-      </c>
-      <c r="Z17" s="9" t="s">
-        <v>921</v>
-      </c>
-      <c r="AB17" s="9" t="s">
-        <v>938</v>
-      </c>
-      <c r="AC17" s="9" t="s">
-        <v>617</v>
-      </c>
-      <c r="AD17" s="9" t="s">
-        <v>927</v>
-      </c>
-    </row>
-    <row r="18" spans="2:30">
+    </row>
+    <row r="18" spans="2:12">
       <c r="B18" t="s">
         <v>475</v>
       </c>
@@ -27945,46 +27591,8 @@
       <c r="L18" t="s">
         <v>654</v>
       </c>
-      <c r="O18" s="9" t="s">
-        <v>483</v>
-      </c>
-      <c r="P18" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q18" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>South-South</v>
-      </c>
-      <c r="S18" s="9" t="s">
-        <v>483</v>
-      </c>
-      <c r="T18" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U18" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Port Harcourt</v>
-      </c>
-      <c r="X18" s="9" t="s">
-        <v>937</v>
-      </c>
-      <c r="Y18" s="9" t="s">
-        <v>618</v>
-      </c>
-      <c r="Z18" s="9" t="s">
-        <v>921</v>
-      </c>
-      <c r="AB18" s="9" t="s">
-        <v>938</v>
-      </c>
-      <c r="AC18" s="9" t="s">
-        <v>618</v>
-      </c>
-      <c r="AD18" s="9" t="s">
-        <v>926</v>
-      </c>
-    </row>
-    <row r="19" spans="2:30">
+    </row>
+    <row r="19" spans="2:12">
       <c r="B19" t="s">
         <v>475</v>
       </c>
@@ -28012,46 +27620,8 @@
       <c r="L19" t="s">
         <v>655</v>
       </c>
-      <c r="O19" s="9" t="s">
-        <v>484</v>
-      </c>
-      <c r="P19" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q19" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>North-West</v>
-      </c>
-      <c r="S19" s="9" t="s">
-        <v>484</v>
-      </c>
-      <c r="T19" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U19" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Kano</v>
-      </c>
-      <c r="X19" s="9" t="s">
-        <v>937</v>
-      </c>
-      <c r="Y19" s="9" t="s">
-        <v>619</v>
-      </c>
-      <c r="Z19" s="9" t="s">
-        <v>923</v>
-      </c>
-      <c r="AB19" s="9" t="s">
-        <v>938</v>
-      </c>
-      <c r="AC19" s="9" t="s">
-        <v>619</v>
-      </c>
-      <c r="AD19" s="9" t="s">
-        <v>928</v>
-      </c>
-    </row>
-    <row r="20" spans="2:30">
+    </row>
+    <row r="20" spans="2:12">
       <c r="B20" t="s">
         <v>475</v>
       </c>
@@ -28079,46 +27649,8 @@
       <c r="L20" t="s">
         <v>656</v>
       </c>
-      <c r="O20" s="9" t="s">
-        <v>485</v>
-      </c>
-      <c r="P20" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q20" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>South-West</v>
-      </c>
-      <c r="S20" s="9" t="s">
-        <v>485</v>
-      </c>
-      <c r="T20" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U20" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Ibadan</v>
-      </c>
-      <c r="X20" s="9" t="s">
-        <v>937</v>
-      </c>
-      <c r="Y20" s="9" t="s">
-        <v>620</v>
-      </c>
-      <c r="Z20" s="9" t="s">
-        <v>924</v>
-      </c>
-      <c r="AB20" s="9" t="s">
-        <v>938</v>
-      </c>
-      <c r="AC20" s="9" t="s">
-        <v>620</v>
-      </c>
-      <c r="AD20" s="9" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="21" spans="2:30">
+    </row>
+    <row r="21" spans="2:12">
       <c r="B21" t="s">
         <v>475</v>
       </c>
@@ -28146,46 +27678,8 @@
       <c r="L21" t="s">
         <v>657</v>
       </c>
-      <c r="O21" s="9" t="s">
-        <v>486</v>
-      </c>
-      <c r="P21" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q21" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>North-Central</v>
-      </c>
-      <c r="S21" s="9" t="s">
-        <v>486</v>
-      </c>
-      <c r="T21" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U21" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Abuja</v>
-      </c>
-      <c r="X21" s="9" t="s">
-        <v>937</v>
-      </c>
-      <c r="Y21" s="9" t="s">
-        <v>621</v>
-      </c>
-      <c r="Z21" s="9" t="s">
-        <v>925</v>
-      </c>
-      <c r="AB21" s="9" t="s">
-        <v>938</v>
-      </c>
-      <c r="AC21" s="9" t="s">
-        <v>621</v>
-      </c>
-      <c r="AD21" s="9" t="s">
-        <v>931</v>
-      </c>
-    </row>
-    <row r="22" spans="2:30">
+    </row>
+    <row r="22" spans="2:12">
       <c r="B22" t="s">
         <v>475</v>
       </c>
@@ -28213,46 +27707,8 @@
       <c r="L22" t="s">
         <v>658</v>
       </c>
-      <c r="O22" s="9" t="s">
-        <v>487</v>
-      </c>
-      <c r="P22" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q22" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>South-West</v>
-      </c>
-      <c r="S22" s="9" t="s">
-        <v>487</v>
-      </c>
-      <c r="T22" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U22" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Ibadan</v>
-      </c>
-      <c r="X22" s="9" t="s">
-        <v>937</v>
-      </c>
-      <c r="Y22" s="9" t="s">
-        <v>622</v>
-      </c>
-      <c r="Z22" s="9" t="s">
-        <v>925</v>
-      </c>
-      <c r="AB22" s="9" t="s">
-        <v>938</v>
-      </c>
-      <c r="AC22" s="9" t="s">
-        <v>622</v>
-      </c>
-      <c r="AD22" s="9" t="s">
-        <v>931</v>
-      </c>
-    </row>
-    <row r="23" spans="2:30">
+    </row>
+    <row r="23" spans="2:12">
       <c r="B23" t="s">
         <v>475</v>
       </c>
@@ -28280,46 +27736,8 @@
       <c r="L23" t="s">
         <v>659</v>
       </c>
-      <c r="O23" s="9" t="s">
-        <v>488</v>
-      </c>
-      <c r="P23" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q23" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>North-Central</v>
-      </c>
-      <c r="S23" s="9" t="s">
-        <v>488</v>
-      </c>
-      <c r="T23" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U23" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Ibadan</v>
-      </c>
-      <c r="X23" s="9" t="s">
-        <v>937</v>
-      </c>
-      <c r="Y23" s="9" t="s">
-        <v>623</v>
-      </c>
-      <c r="Z23" s="9" t="s">
-        <v>922</v>
-      </c>
-      <c r="AB23" s="9" t="s">
-        <v>938</v>
-      </c>
-      <c r="AC23" s="9" t="s">
-        <v>623</v>
-      </c>
-      <c r="AD23" s="9" t="s">
-        <v>931</v>
-      </c>
-    </row>
-    <row r="24" spans="2:30">
+    </row>
+    <row r="24" spans="2:12">
       <c r="B24" t="s">
         <v>475</v>
       </c>
@@ -28347,46 +27765,8 @@
       <c r="L24" t="s">
         <v>660</v>
       </c>
-      <c r="O24" s="9" t="s">
-        <v>489</v>
-      </c>
-      <c r="P24" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q24" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>South-South</v>
-      </c>
-      <c r="S24" s="9" t="s">
-        <v>489</v>
-      </c>
-      <c r="T24" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U24" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Benin</v>
-      </c>
-      <c r="X24" s="9" t="s">
-        <v>937</v>
-      </c>
-      <c r="Y24" s="9" t="s">
-        <v>624</v>
-      </c>
-      <c r="Z24" s="9" t="s">
-        <v>923</v>
-      </c>
-      <c r="AB24" s="9" t="s">
-        <v>938</v>
-      </c>
-      <c r="AC24" s="9" t="s">
-        <v>624</v>
-      </c>
-      <c r="AD24" s="9" t="s">
-        <v>929</v>
-      </c>
-    </row>
-    <row r="25" spans="2:30">
+    </row>
+    <row r="25" spans="2:12">
       <c r="B25" t="s">
         <v>475</v>
       </c>
@@ -28414,46 +27794,8 @@
       <c r="L25" t="s">
         <v>661</v>
       </c>
-      <c r="O25" s="9" t="s">
-        <v>490</v>
-      </c>
-      <c r="P25" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q25" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>South-East</v>
-      </c>
-      <c r="S25" s="9" t="s">
-        <v>490</v>
-      </c>
-      <c r="T25" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U25" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Enugu</v>
-      </c>
-      <c r="X25" s="9" t="s">
-        <v>937</v>
-      </c>
-      <c r="Y25" s="9" t="s">
-        <v>625</v>
-      </c>
-      <c r="Z25" s="9" t="s">
-        <v>920</v>
-      </c>
-      <c r="AB25" s="9" t="s">
-        <v>938</v>
-      </c>
-      <c r="AC25" s="9" t="s">
-        <v>625</v>
-      </c>
-      <c r="AD25" s="9" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="26" spans="2:30">
+    </row>
+    <row r="26" spans="2:12">
       <c r="B26" t="s">
         <v>475</v>
       </c>
@@ -28481,46 +27823,8 @@
       <c r="L26" t="s">
         <v>662</v>
       </c>
-      <c r="O26" s="9" t="s">
-        <v>491</v>
-      </c>
-      <c r="P26" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q26" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>North-Central</v>
-      </c>
-      <c r="S26" s="9" t="s">
-        <v>491</v>
-      </c>
-      <c r="T26" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U26" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Abuja</v>
-      </c>
-      <c r="X26" s="9" t="s">
-        <v>937</v>
-      </c>
-      <c r="Y26" s="9" t="s">
-        <v>626</v>
-      </c>
-      <c r="Z26" s="9" t="s">
-        <v>921</v>
-      </c>
-      <c r="AB26" s="9" t="s">
-        <v>938</v>
-      </c>
-      <c r="AC26" s="9" t="s">
-        <v>626</v>
-      </c>
-      <c r="AD26" s="9" t="s">
-        <v>926</v>
-      </c>
-    </row>
-    <row r="27" spans="2:30">
+    </row>
+    <row r="27" spans="2:12">
       <c r="B27" t="s">
         <v>475</v>
       </c>
@@ -28548,46 +27852,8 @@
       <c r="L27" t="s">
         <v>663</v>
       </c>
-      <c r="O27" s="9" t="s">
-        <v>492</v>
-      </c>
-      <c r="P27" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q27" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>South-West</v>
-      </c>
-      <c r="S27" s="9" t="s">
-        <v>492</v>
-      </c>
-      <c r="T27" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U27" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Ikeja</v>
-      </c>
-      <c r="X27" s="9" t="s">
-        <v>937</v>
-      </c>
-      <c r="Y27" s="9" t="s">
-        <v>627</v>
-      </c>
-      <c r="Z27" s="9" t="s">
-        <v>920</v>
-      </c>
-      <c r="AB27" s="9" t="s">
-        <v>938</v>
-      </c>
-      <c r="AC27" s="9" t="s">
-        <v>627</v>
-      </c>
-      <c r="AD27" s="9" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="28" spans="2:30">
+    </row>
+    <row r="28" spans="2:12">
       <c r="B28" t="s">
         <v>475</v>
       </c>
@@ -28615,46 +27881,8 @@
       <c r="L28" t="s">
         <v>664</v>
       </c>
-      <c r="O28" s="9" t="s">
-        <v>493</v>
-      </c>
-      <c r="P28" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q28" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>North-Central</v>
-      </c>
-      <c r="S28" s="9" t="s">
-        <v>493</v>
-      </c>
-      <c r="T28" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U28" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Abuja</v>
-      </c>
-      <c r="X28" s="9" t="s">
-        <v>937</v>
-      </c>
-      <c r="Y28" s="9" t="s">
-        <v>628</v>
-      </c>
-      <c r="Z28" s="9" t="s">
-        <v>924</v>
-      </c>
-      <c r="AB28" s="9" t="s">
-        <v>938</v>
-      </c>
-      <c r="AC28" s="9" t="s">
-        <v>628</v>
-      </c>
-      <c r="AD28" s="9" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="29" spans="2:30">
+    </row>
+    <row r="29" spans="2:12">
       <c r="B29" t="s">
         <v>475</v>
       </c>
@@ -28682,46 +27910,8 @@
       <c r="L29" t="s">
         <v>665</v>
       </c>
-      <c r="O29" s="9" t="s">
-        <v>494</v>
-      </c>
-      <c r="P29" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q29" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>North-East</v>
-      </c>
-      <c r="S29" s="9" t="s">
-        <v>494</v>
-      </c>
-      <c r="T29" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U29" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Yola</v>
-      </c>
-      <c r="X29" s="9" t="s">
-        <v>937</v>
-      </c>
-      <c r="Y29" s="9" t="s">
-        <v>629</v>
-      </c>
-      <c r="Z29" s="9" t="s">
-        <v>923</v>
-      </c>
-      <c r="AB29" s="9" t="s">
-        <v>938</v>
-      </c>
-      <c r="AC29" s="9" t="s">
-        <v>629</v>
-      </c>
-      <c r="AD29" s="9" t="s">
-        <v>928</v>
-      </c>
-    </row>
-    <row r="30" spans="2:30">
+    </row>
+    <row r="30" spans="2:12">
       <c r="B30" t="s">
         <v>475</v>
       </c>
@@ -28749,46 +27939,8 @@
       <c r="L30" t="s">
         <v>666</v>
       </c>
-      <c r="O30" s="9" t="s">
-        <v>495</v>
-      </c>
-      <c r="P30" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q30" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>South-East</v>
-      </c>
-      <c r="S30" s="9" t="s">
-        <v>495</v>
-      </c>
-      <c r="T30" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U30" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Enugu</v>
-      </c>
-      <c r="X30" s="9" t="s">
-        <v>937</v>
-      </c>
-      <c r="Y30" s="9" t="s">
-        <v>630</v>
-      </c>
-      <c r="Z30" s="9" t="s">
-        <v>925</v>
-      </c>
-      <c r="AB30" s="9" t="s">
-        <v>938</v>
-      </c>
-      <c r="AC30" s="9" t="s">
-        <v>630</v>
-      </c>
-      <c r="AD30" s="9" t="s">
-        <v>931</v>
-      </c>
-    </row>
-    <row r="31" spans="2:30">
+    </row>
+    <row r="31" spans="2:12">
       <c r="B31" t="s">
         <v>475</v>
       </c>
@@ -28816,46 +27968,8 @@
       <c r="L31" t="s">
         <v>667</v>
       </c>
-      <c r="O31" s="9" t="s">
-        <v>496</v>
-      </c>
-      <c r="P31" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q31" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>North-West</v>
-      </c>
-      <c r="S31" s="9" t="s">
-        <v>496</v>
-      </c>
-      <c r="T31" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U31" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Kaduna</v>
-      </c>
-      <c r="X31" s="9" t="s">
-        <v>937</v>
-      </c>
-      <c r="Y31" s="9" t="s">
-        <v>631</v>
-      </c>
-      <c r="Z31" s="9" t="s">
-        <v>923</v>
-      </c>
-      <c r="AB31" s="9" t="s">
-        <v>938</v>
-      </c>
-      <c r="AC31" s="9" t="s">
-        <v>631</v>
-      </c>
-      <c r="AD31" s="9" t="s">
-        <v>929</v>
-      </c>
-    </row>
-    <row r="32" spans="2:30">
+    </row>
+    <row r="32" spans="2:12">
       <c r="B32" t="s">
         <v>475</v>
       </c>
@@ -28883,46 +27997,8 @@
       <c r="L32" t="s">
         <v>668</v>
       </c>
-      <c r="O32" s="9" t="s">
-        <v>497</v>
-      </c>
-      <c r="P32" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q32" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>South-South</v>
-      </c>
-      <c r="S32" s="9" t="s">
-        <v>497</v>
-      </c>
-      <c r="T32" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U32" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Port Harcourt</v>
-      </c>
-      <c r="X32" s="9" t="s">
-        <v>937</v>
-      </c>
-      <c r="Y32" s="9" t="s">
-        <v>632</v>
-      </c>
-      <c r="Z32" s="9" t="s">
-        <v>922</v>
-      </c>
-      <c r="AB32" s="9" t="s">
-        <v>938</v>
-      </c>
-      <c r="AC32" s="9" t="s">
-        <v>632</v>
-      </c>
-      <c r="AD32" s="9" t="s">
-        <v>927</v>
-      </c>
-    </row>
-    <row r="33" spans="2:30">
+    </row>
+    <row r="33" spans="2:12">
       <c r="B33" t="s">
         <v>475</v>
       </c>
@@ -28950,46 +28026,8 @@
       <c r="L33" t="s">
         <v>669</v>
       </c>
-      <c r="O33" s="9" t="s">
-        <v>498</v>
-      </c>
-      <c r="P33" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q33" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>South-South</v>
-      </c>
-      <c r="S33" s="9" t="s">
-        <v>498</v>
-      </c>
-      <c r="T33" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U33" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Port Harcourt</v>
-      </c>
-      <c r="X33" s="9" t="s">
-        <v>937</v>
-      </c>
-      <c r="Y33" s="9" t="s">
-        <v>633</v>
-      </c>
-      <c r="Z33" s="9" t="s">
-        <v>922</v>
-      </c>
-      <c r="AB33" s="9" t="s">
-        <v>938</v>
-      </c>
-      <c r="AC33" s="9" t="s">
-        <v>633</v>
-      </c>
-      <c r="AD33" s="9" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="34" spans="2:30">
+    </row>
+    <row r="34" spans="2:12">
       <c r="B34" t="s">
         <v>475</v>
       </c>
@@ -29017,46 +28055,8 @@
       <c r="L34" t="s">
         <v>670</v>
       </c>
-      <c r="O34" s="9" t="s">
-        <v>499</v>
-      </c>
-      <c r="P34" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q34" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>South-West</v>
-      </c>
-      <c r="S34" s="9" t="s">
-        <v>499</v>
-      </c>
-      <c r="T34" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U34" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Ibadan</v>
-      </c>
-      <c r="X34" s="9" t="s">
-        <v>937</v>
-      </c>
-      <c r="Y34" s="9" t="s">
-        <v>634</v>
-      </c>
-      <c r="Z34" s="9" t="s">
-        <v>925</v>
-      </c>
-      <c r="AB34" s="9" t="s">
-        <v>938</v>
-      </c>
-      <c r="AC34" s="9" t="s">
-        <v>634</v>
-      </c>
-      <c r="AD34" s="9" t="s">
-        <v>929</v>
-      </c>
-    </row>
-    <row r="35" spans="2:30">
+    </row>
+    <row r="35" spans="2:12">
       <c r="B35" t="s">
         <v>475</v>
       </c>
@@ -29084,46 +28084,8 @@
       <c r="L35" t="s">
         <v>671</v>
       </c>
-      <c r="O35" s="9" t="s">
-        <v>500</v>
-      </c>
-      <c r="P35" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q35" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>South-South</v>
-      </c>
-      <c r="S35" s="9" t="s">
-        <v>500</v>
-      </c>
-      <c r="T35" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U35" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Benin</v>
-      </c>
-      <c r="X35" s="9" t="s">
-        <v>937</v>
-      </c>
-      <c r="Y35" s="9" t="s">
-        <v>635</v>
-      </c>
-      <c r="Z35" s="9" t="s">
-        <v>921</v>
-      </c>
-      <c r="AB35" s="9" t="s">
-        <v>938</v>
-      </c>
-      <c r="AC35" s="9" t="s">
-        <v>635</v>
-      </c>
-      <c r="AD35" s="9" t="s">
-        <v>926</v>
-      </c>
-    </row>
-    <row r="36" spans="2:30">
+    </row>
+    <row r="36" spans="2:12">
       <c r="B36" t="s">
         <v>475</v>
       </c>
@@ -29151,46 +28113,8 @@
       <c r="L36" t="s">
         <v>672</v>
       </c>
-      <c r="O36" s="9" t="s">
-        <v>501</v>
-      </c>
-      <c r="P36" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q36" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>South-West</v>
-      </c>
-      <c r="S36" s="9" t="s">
-        <v>501</v>
-      </c>
-      <c r="T36" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U36" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Ibadan</v>
-      </c>
-      <c r="X36" s="9" t="s">
-        <v>937</v>
-      </c>
-      <c r="Y36" s="9" t="s">
-        <v>636</v>
-      </c>
-      <c r="Z36" s="9" t="s">
-        <v>920</v>
-      </c>
-      <c r="AB36" s="9" t="s">
-        <v>938</v>
-      </c>
-      <c r="AC36" s="9" t="s">
-        <v>636</v>
-      </c>
-      <c r="AD36" s="9" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="37" spans="2:30">
+    </row>
+    <row r="37" spans="2:12">
       <c r="B37" t="s">
         <v>475</v>
       </c>
@@ -29218,46 +28142,8 @@
       <c r="L37" t="s">
         <v>673</v>
       </c>
-      <c r="O37" s="9" t="s">
-        <v>502</v>
-      </c>
-      <c r="P37" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q37" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>North-Central</v>
-      </c>
-      <c r="S37" s="9" t="s">
-        <v>502</v>
-      </c>
-      <c r="T37" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U37" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Jos</v>
-      </c>
-      <c r="X37" s="9" t="s">
-        <v>937</v>
-      </c>
-      <c r="Y37" s="9" t="s">
-        <v>637</v>
-      </c>
-      <c r="Z37" s="9" t="s">
-        <v>923</v>
-      </c>
-      <c r="AB37" s="9" t="s">
-        <v>938</v>
-      </c>
-      <c r="AC37" s="9" t="s">
-        <v>637</v>
-      </c>
-      <c r="AD37" s="9" t="s">
-        <v>928</v>
-      </c>
-    </row>
-    <row r="38" spans="2:30">
+    </row>
+    <row r="38" spans="2:12">
       <c r="B38" t="s">
         <v>475</v>
       </c>
@@ -29285,46 +28171,8 @@
       <c r="L38" t="s">
         <v>674</v>
       </c>
-      <c r="O38" s="9" t="s">
-        <v>503</v>
-      </c>
-      <c r="P38" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q38" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>North-Central</v>
-      </c>
-      <c r="S38" s="9" t="s">
-        <v>503</v>
-      </c>
-      <c r="T38" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U38" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Abuja</v>
-      </c>
-      <c r="X38" s="9" t="s">
-        <v>937</v>
-      </c>
-      <c r="Y38" s="9" t="s">
-        <v>638</v>
-      </c>
-      <c r="Z38" s="9" t="s">
-        <v>924</v>
-      </c>
-      <c r="AB38" s="9" t="s">
-        <v>938</v>
-      </c>
-      <c r="AC38" s="9" t="s">
-        <v>638</v>
-      </c>
-      <c r="AD38" s="9" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="39" spans="2:30">
+    </row>
+    <row r="39" spans="2:12">
       <c r="B39" t="s">
         <v>475</v>
       </c>
@@ -29352,46 +28200,8 @@
       <c r="L39" t="s">
         <v>675</v>
       </c>
-      <c r="O39" s="9" t="s">
-        <v>504</v>
-      </c>
-      <c r="P39" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q39" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>North-Central</v>
-      </c>
-      <c r="S39" s="9" t="s">
-        <v>504</v>
-      </c>
-      <c r="T39" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U39" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Abuja</v>
-      </c>
-      <c r="X39" s="9" t="s">
-        <v>937</v>
-      </c>
-      <c r="Y39" s="9" t="s">
-        <v>639</v>
-      </c>
-      <c r="Z39" s="9" t="s">
-        <v>921</v>
-      </c>
-      <c r="AB39" s="9" t="s">
-        <v>938</v>
-      </c>
-      <c r="AC39" s="9" t="s">
-        <v>639</v>
-      </c>
-      <c r="AD39" s="9" t="s">
-        <v>926</v>
-      </c>
-    </row>
-    <row r="40" spans="2:30">
+    </row>
+    <row r="40" spans="2:12">
       <c r="B40" t="s">
         <v>475</v>
       </c>
@@ -29419,46 +28229,8 @@
       <c r="L40" t="s">
         <v>676</v>
       </c>
-      <c r="O40" s="9" t="s">
-        <v>505</v>
-      </c>
-      <c r="P40" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q40" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>South-West</v>
-      </c>
-      <c r="S40" s="9" t="s">
-        <v>505</v>
-      </c>
-      <c r="T40" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U40" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Benin</v>
-      </c>
-      <c r="X40" s="9" t="s">
-        <v>937</v>
-      </c>
-      <c r="Y40" s="9" t="s">
-        <v>640</v>
-      </c>
-      <c r="Z40" s="9" t="s">
-        <v>922</v>
-      </c>
-      <c r="AB40" s="9" t="s">
-        <v>938</v>
-      </c>
-      <c r="AC40" s="9" t="s">
-        <v>640</v>
-      </c>
-      <c r="AD40" s="9" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="41" spans="2:30">
+    </row>
+    <row r="41" spans="2:12">
       <c r="B41" t="s">
         <v>475</v>
       </c>
@@ -29486,46 +28258,8 @@
       <c r="L41" t="s">
         <v>677</v>
       </c>
-      <c r="O41" s="9" t="s">
-        <v>506</v>
-      </c>
-      <c r="P41" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q41" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>South-South</v>
-      </c>
-      <c r="S41" s="9" t="s">
-        <v>506</v>
-      </c>
-      <c r="T41" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U41" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Benin</v>
-      </c>
-      <c r="X41" s="9" t="s">
-        <v>937</v>
-      </c>
-      <c r="Y41" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="Z41" s="9" t="s">
-        <v>921</v>
-      </c>
-      <c r="AB41" s="9" t="s">
-        <v>938</v>
-      </c>
-      <c r="AC41" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="AD41" s="9" t="s">
-        <v>927</v>
-      </c>
-    </row>
-    <row r="42" spans="2:30">
+    </row>
+    <row r="42" spans="2:12">
       <c r="B42" t="s">
         <v>475</v>
       </c>
@@ -29553,46 +28287,8 @@
       <c r="L42" t="s">
         <v>678</v>
       </c>
-      <c r="O42" s="9" t="s">
-        <v>507</v>
-      </c>
-      <c r="P42" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q42" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>South-South</v>
-      </c>
-      <c r="S42" s="9" t="s">
-        <v>507</v>
-      </c>
-      <c r="T42" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U42" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Benin</v>
-      </c>
-      <c r="X42" s="9" t="s">
-        <v>937</v>
-      </c>
-      <c r="Y42" s="9" t="s">
-        <v>642</v>
-      </c>
-      <c r="Z42" s="9" t="s">
-        <v>924</v>
-      </c>
-      <c r="AB42" s="9" t="s">
-        <v>938</v>
-      </c>
-      <c r="AC42" s="9" t="s">
-        <v>642</v>
-      </c>
-      <c r="AD42" s="9" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="43" spans="2:30">
+    </row>
+    <row r="43" spans="2:12">
       <c r="B43" t="s">
         <v>475</v>
       </c>
@@ -29620,46 +28316,8 @@
       <c r="L43" t="s">
         <v>679</v>
       </c>
-      <c r="O43" s="9" t="s">
-        <v>508</v>
-      </c>
-      <c r="P43" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q43" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>North-East</v>
-      </c>
-      <c r="S43" s="9" t="s">
-        <v>508</v>
-      </c>
-      <c r="T43" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U43" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Yola</v>
-      </c>
-      <c r="X43" s="9" t="s">
-        <v>937</v>
-      </c>
-      <c r="Y43" s="9" t="s">
-        <v>643</v>
-      </c>
-      <c r="Z43" s="9" t="s">
-        <v>924</v>
-      </c>
-      <c r="AB43" s="9" t="s">
-        <v>938</v>
-      </c>
-      <c r="AC43" s="9" t="s">
-        <v>643</v>
-      </c>
-      <c r="AD43" s="9" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="44" spans="2:30">
+    </row>
+    <row r="44" spans="2:12">
       <c r="B44" t="s">
         <v>475</v>
       </c>
@@ -29687,46 +28345,8 @@
       <c r="L44" t="s">
         <v>680</v>
       </c>
-      <c r="O44" s="9" t="s">
-        <v>509</v>
-      </c>
-      <c r="P44" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q44" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>South-West</v>
-      </c>
-      <c r="S44" s="9" t="s">
-        <v>509</v>
-      </c>
-      <c r="T44" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U44" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Ikeja</v>
-      </c>
-      <c r="X44" s="9" t="s">
-        <v>937</v>
-      </c>
-      <c r="Y44" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="Z44" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="AB44" s="9" t="s">
-        <v>938</v>
-      </c>
-      <c r="AC44" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="AD44" s="9" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="45" spans="2:30">
+    </row>
+    <row r="45" spans="2:12">
       <c r="B45" t="s">
         <v>475</v>
       </c>
@@ -29754,46 +28374,8 @@
       <c r="L45" t="s">
         <v>681</v>
       </c>
-      <c r="O45" s="9" t="s">
-        <v>510</v>
-      </c>
-      <c r="P45" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q45" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>South-East</v>
-      </c>
-      <c r="S45" s="9" t="s">
-        <v>510</v>
-      </c>
-      <c r="T45" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U45" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Enugu</v>
-      </c>
-      <c r="X45" s="9" t="s">
-        <v>937</v>
-      </c>
-      <c r="Y45" s="9" t="s">
-        <v>645</v>
-      </c>
-      <c r="Z45" s="9" t="s">
-        <v>924</v>
-      </c>
-      <c r="AB45" s="9" t="s">
-        <v>938</v>
-      </c>
-      <c r="AC45" s="9" t="s">
-        <v>645</v>
-      </c>
-      <c r="AD45" s="9" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="46" spans="2:30">
+    </row>
+    <row r="46" spans="2:12">
       <c r="B46" t="s">
         <v>475</v>
       </c>
@@ -29821,28 +28403,8 @@
       <c r="L46" t="s">
         <v>682</v>
       </c>
-      <c r="O46" s="9" t="s">
-        <v>511</v>
-      </c>
-      <c r="P46" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q46" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>South-West</v>
-      </c>
-      <c r="S46" s="9" t="s">
-        <v>511</v>
-      </c>
-      <c r="T46" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U46" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Ikeja</v>
-      </c>
-    </row>
-    <row r="47" spans="2:30">
+    </row>
+    <row r="47" spans="2:12">
       <c r="B47" t="s">
         <v>475</v>
       </c>
@@ -29870,28 +28432,8 @@
       <c r="L47" t="s">
         <v>683</v>
       </c>
-      <c r="O47" s="9" t="s">
-        <v>512</v>
-      </c>
-      <c r="P47" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q47" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>South-South</v>
-      </c>
-      <c r="S47" s="9" t="s">
-        <v>512</v>
-      </c>
-      <c r="T47" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U47" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Port Harcourt</v>
-      </c>
-    </row>
-    <row r="48" spans="2:30">
+    </row>
+    <row r="48" spans="2:12">
       <c r="B48" t="s">
         <v>475</v>
       </c>
@@ -29919,28 +28461,8 @@
       <c r="L48" t="s">
         <v>684</v>
       </c>
-      <c r="O48" s="9" t="s">
-        <v>513</v>
-      </c>
-      <c r="P48" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q48" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>South-South</v>
-      </c>
-      <c r="S48" s="9" t="s">
-        <v>513</v>
-      </c>
-      <c r="T48" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U48" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Benin</v>
-      </c>
-    </row>
-    <row r="49" spans="2:21">
+    </row>
+    <row r="49" spans="2:12">
       <c r="B49" t="s">
         <v>475</v>
       </c>
@@ -29968,28 +28490,8 @@
       <c r="L49" t="s">
         <v>685</v>
       </c>
-      <c r="O49" s="9" t="s">
-        <v>514</v>
-      </c>
-      <c r="P49" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q49" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>North-West</v>
-      </c>
-      <c r="S49" s="9" t="s">
-        <v>514</v>
-      </c>
-      <c r="T49" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U49" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Kano</v>
-      </c>
-    </row>
-    <row r="50" spans="2:21">
+    </row>
+    <row r="50" spans="2:12">
       <c r="B50" t="s">
         <v>475</v>
       </c>
@@ -30017,28 +28519,8 @@
       <c r="L50" t="s">
         <v>686</v>
       </c>
-      <c r="O50" s="9" t="s">
-        <v>515</v>
-      </c>
-      <c r="P50" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q50" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>South-West</v>
-      </c>
-      <c r="S50" s="9" t="s">
-        <v>515</v>
-      </c>
-      <c r="T50" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U50" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Ibadan</v>
-      </c>
-    </row>
-    <row r="51" spans="2:21">
+    </row>
+    <row r="51" spans="2:12">
       <c r="B51" t="s">
         <v>475</v>
       </c>
@@ -30066,28 +28548,8 @@
       <c r="L51" t="s">
         <v>687</v>
       </c>
-      <c r="O51" s="9" t="s">
-        <v>516</v>
-      </c>
-      <c r="P51" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q51" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>North-Central</v>
-      </c>
-      <c r="S51" s="9" t="s">
-        <v>516</v>
-      </c>
-      <c r="T51" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U51" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Ibadan</v>
-      </c>
-    </row>
-    <row r="52" spans="2:21">
+    </row>
+    <row r="52" spans="2:12">
       <c r="B52" t="s">
         <v>475</v>
       </c>
@@ -30115,28 +28577,8 @@
       <c r="L52" t="s">
         <v>688</v>
       </c>
-      <c r="O52" s="9" t="s">
-        <v>517</v>
-      </c>
-      <c r="P52" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q52" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>South-South</v>
-      </c>
-      <c r="S52" s="9" t="s">
-        <v>517</v>
-      </c>
-      <c r="T52" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U52" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Port Harcourt</v>
-      </c>
-    </row>
-    <row r="53" spans="2:21">
+    </row>
+    <row r="53" spans="2:12">
       <c r="B53" t="s">
         <v>475</v>
       </c>
@@ -30164,28 +28606,8 @@
       <c r="L53" t="s">
         <v>689</v>
       </c>
-      <c r="O53" s="9" t="s">
-        <v>518</v>
-      </c>
-      <c r="P53" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q53" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>South-South</v>
-      </c>
-      <c r="S53" s="9" t="s">
-        <v>518</v>
-      </c>
-      <c r="T53" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U53" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Benin</v>
-      </c>
-    </row>
-    <row r="54" spans="2:21">
+    </row>
+    <row r="54" spans="2:12">
       <c r="B54" t="s">
         <v>475</v>
       </c>
@@ -30213,28 +28635,8 @@
       <c r="L54" t="s">
         <v>690</v>
       </c>
-      <c r="O54" s="9" t="s">
-        <v>519</v>
-      </c>
-      <c r="P54" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q54" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>North-Central</v>
-      </c>
-      <c r="S54" s="9" t="s">
-        <v>519</v>
-      </c>
-      <c r="T54" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U54" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Ibadan</v>
-      </c>
-    </row>
-    <row r="55" spans="2:21">
+    </row>
+    <row r="55" spans="2:12">
       <c r="B55" t="s">
         <v>475</v>
       </c>
@@ -30262,28 +28664,8 @@
       <c r="L55" t="s">
         <v>691</v>
       </c>
-      <c r="O55" s="9" t="s">
-        <v>520</v>
-      </c>
-      <c r="P55" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q55" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>South-East</v>
-      </c>
-      <c r="S55" s="9" t="s">
-        <v>520</v>
-      </c>
-      <c r="T55" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U55" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Enugu</v>
-      </c>
-    </row>
-    <row r="56" spans="2:21">
+    </row>
+    <row r="56" spans="2:12">
       <c r="B56" t="s">
         <v>475</v>
       </c>
@@ -30311,28 +28693,8 @@
       <c r="L56" t="s">
         <v>692</v>
       </c>
-      <c r="O56" s="9" t="s">
-        <v>521</v>
-      </c>
-      <c r="P56" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q56" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>North-Central</v>
-      </c>
-      <c r="S56" s="9" t="s">
-        <v>521</v>
-      </c>
-      <c r="T56" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U56" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Abuja</v>
-      </c>
-    </row>
-    <row r="57" spans="2:21">
+    </row>
+    <row r="57" spans="2:12">
       <c r="B57" t="s">
         <v>475</v>
       </c>
@@ -30360,28 +28722,8 @@
       <c r="L57" t="s">
         <v>693</v>
       </c>
-      <c r="O57" s="9" t="s">
-        <v>522</v>
-      </c>
-      <c r="P57" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q57" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>South-South</v>
-      </c>
-      <c r="S57" s="9" t="s">
-        <v>522</v>
-      </c>
-      <c r="T57" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U57" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Benin</v>
-      </c>
-    </row>
-    <row r="58" spans="2:21">
+    </row>
+    <row r="58" spans="2:12">
       <c r="B58" t="s">
         <v>475</v>
       </c>
@@ -30409,28 +28751,8 @@
       <c r="L58" t="s">
         <v>694</v>
       </c>
-      <c r="O58" s="9" t="s">
-        <v>523</v>
-      </c>
-      <c r="P58" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q58" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>North-Central</v>
-      </c>
-      <c r="S58" s="9" t="s">
-        <v>523</v>
-      </c>
-      <c r="T58" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U58" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Abuja</v>
-      </c>
-    </row>
-    <row r="59" spans="2:21">
+    </row>
+    <row r="59" spans="2:12">
       <c r="B59" t="s">
         <v>475</v>
       </c>
@@ -30458,28 +28780,8 @@
       <c r="L59" t="s">
         <v>695</v>
       </c>
-      <c r="O59" s="9" t="s">
-        <v>524</v>
-      </c>
-      <c r="P59" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q59" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>South-West</v>
-      </c>
-      <c r="S59" s="9" t="s">
-        <v>524</v>
-      </c>
-      <c r="T59" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U59" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Ibadan</v>
-      </c>
-    </row>
-    <row r="60" spans="2:21">
+    </row>
+    <row r="60" spans="2:12">
       <c r="B60" t="s">
         <v>475</v>
       </c>
@@ -30507,28 +28809,8 @@
       <c r="L60" t="s">
         <v>696</v>
       </c>
-      <c r="O60" s="9" t="s">
-        <v>525</v>
-      </c>
-      <c r="P60" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q60" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>South-South</v>
-      </c>
-      <c r="S60" s="9" t="s">
-        <v>525</v>
-      </c>
-      <c r="T60" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U60" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Benin</v>
-      </c>
-    </row>
-    <row r="61" spans="2:21">
+    </row>
+    <row r="61" spans="2:12">
       <c r="B61" t="s">
         <v>475</v>
       </c>
@@ -30556,28 +28838,8 @@
       <c r="L61" t="s">
         <v>697</v>
       </c>
-      <c r="O61" s="9" t="s">
-        <v>526</v>
-      </c>
-      <c r="P61" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q61" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>South-South</v>
-      </c>
-      <c r="S61" s="9" t="s">
-        <v>526</v>
-      </c>
-      <c r="T61" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U61" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Benin</v>
-      </c>
-    </row>
-    <row r="62" spans="2:21">
+    </row>
+    <row r="62" spans="2:12">
       <c r="B62" t="s">
         <v>475</v>
       </c>
@@ -30605,28 +28867,8 @@
       <c r="L62" t="s">
         <v>698</v>
       </c>
-      <c r="O62" s="9" t="s">
-        <v>527</v>
-      </c>
-      <c r="P62" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q62" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>South-South</v>
-      </c>
-      <c r="S62" s="9" t="s">
-        <v>527</v>
-      </c>
-      <c r="T62" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U62" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Benin</v>
-      </c>
-    </row>
-    <row r="63" spans="2:21">
+    </row>
+    <row r="63" spans="2:12">
       <c r="B63" t="s">
         <v>475</v>
       </c>
@@ -30654,28 +28896,8 @@
       <c r="L63" t="s">
         <v>699</v>
       </c>
-      <c r="O63" t="s">
-        <v>528</v>
-      </c>
-      <c r="P63" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q63" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>North-West</v>
-      </c>
-      <c r="S63" t="s">
-        <v>528</v>
-      </c>
-      <c r="T63" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U63" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Kano</v>
-      </c>
-    </row>
-    <row r="64" spans="2:21">
+    </row>
+    <row r="64" spans="2:12">
       <c r="B64" t="s">
         <v>475</v>
       </c>
@@ -30703,28 +28925,8 @@
       <c r="L64" t="s">
         <v>700</v>
       </c>
-      <c r="O64" t="s">
-        <v>529</v>
-      </c>
-      <c r="P64" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q64" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>North-West</v>
-      </c>
-      <c r="S64" t="s">
-        <v>529</v>
-      </c>
-      <c r="T64" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U64" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Kano</v>
-      </c>
-    </row>
-    <row r="65" spans="2:21">
+    </row>
+    <row r="65" spans="2:12">
       <c r="B65" t="s">
         <v>475</v>
       </c>
@@ -30752,28 +28954,8 @@
       <c r="L65" t="s">
         <v>701</v>
       </c>
-      <c r="O65" t="s">
-        <v>530</v>
-      </c>
-      <c r="P65" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q65" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>North-Central</v>
-      </c>
-      <c r="S65" t="s">
-        <v>530</v>
-      </c>
-      <c r="T65" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U65" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Abuja</v>
-      </c>
-    </row>
-    <row r="66" spans="2:21">
+    </row>
+    <row r="66" spans="2:12">
       <c r="B66" t="s">
         <v>475</v>
       </c>
@@ -30801,28 +28983,8 @@
       <c r="L66" t="s">
         <v>702</v>
       </c>
-      <c r="O66" t="s">
-        <v>531</v>
-      </c>
-      <c r="P66" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q66" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>South-West</v>
-      </c>
-      <c r="S66" t="s">
-        <v>531</v>
-      </c>
-      <c r="T66" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U66" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Ibadan</v>
-      </c>
-    </row>
-    <row r="67" spans="2:21">
+    </row>
+    <row r="67" spans="2:12">
       <c r="B67" t="s">
         <v>475</v>
       </c>
@@ -30850,28 +29012,8 @@
       <c r="L67" t="s">
         <v>703</v>
       </c>
-      <c r="O67" t="s">
-        <v>532</v>
-      </c>
-      <c r="P67" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q67" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>North-Central</v>
-      </c>
-      <c r="S67" t="s">
-        <v>532</v>
-      </c>
-      <c r="T67" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U67" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Jos</v>
-      </c>
-    </row>
-    <row r="68" spans="2:21">
+    </row>
+    <row r="68" spans="2:12">
       <c r="B68" t="s">
         <v>475</v>
       </c>
@@ -30899,28 +29041,8 @@
       <c r="L68" t="s">
         <v>704</v>
       </c>
-      <c r="O68" t="s">
-        <v>533</v>
-      </c>
-      <c r="P68" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q68" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>South-East</v>
-      </c>
-      <c r="S68" t="s">
-        <v>533</v>
-      </c>
-      <c r="T68" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U68" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Enugu</v>
-      </c>
-    </row>
-    <row r="69" spans="2:21">
+    </row>
+    <row r="69" spans="2:12">
       <c r="B69" t="s">
         <v>475</v>
       </c>
@@ -30948,28 +29070,8 @@
       <c r="L69" t="s">
         <v>705</v>
       </c>
-      <c r="O69" t="s">
-        <v>534</v>
-      </c>
-      <c r="P69" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q69" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>North-Central</v>
-      </c>
-      <c r="S69" t="s">
-        <v>534</v>
-      </c>
-      <c r="T69" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U69" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Abuja</v>
-      </c>
-    </row>
-    <row r="70" spans="2:21">
+    </row>
+    <row r="70" spans="2:12">
       <c r="B70" t="s">
         <v>475</v>
       </c>
@@ -30997,28 +29099,8 @@
       <c r="L70" t="s">
         <v>706</v>
       </c>
-      <c r="O70" t="s">
-        <v>535</v>
-      </c>
-      <c r="P70" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q70" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>South-South</v>
-      </c>
-      <c r="S70" t="s">
-        <v>535</v>
-      </c>
-      <c r="T70" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U70" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Benin</v>
-      </c>
-    </row>
-    <row r="71" spans="2:21">
+    </row>
+    <row r="71" spans="2:12">
       <c r="B71" t="s">
         <v>475</v>
       </c>
@@ -31046,28 +29128,8 @@
       <c r="L71" t="s">
         <v>707</v>
       </c>
-      <c r="O71" t="s">
-        <v>536</v>
-      </c>
-      <c r="P71" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q71" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>South-East</v>
-      </c>
-      <c r="S71" t="s">
-        <v>536</v>
-      </c>
-      <c r="T71" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U71" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Enugu</v>
-      </c>
-    </row>
-    <row r="72" spans="2:21">
+    </row>
+    <row r="72" spans="2:12">
       <c r="B72" t="s">
         <v>475</v>
       </c>
@@ -31095,28 +29157,8 @@
       <c r="L72" t="s">
         <v>708</v>
       </c>
-      <c r="O72" t="s">
-        <v>537</v>
-      </c>
-      <c r="P72" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q72" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>South-South</v>
-      </c>
-      <c r="S72" t="s">
-        <v>537</v>
-      </c>
-      <c r="T72" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U72" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Benin</v>
-      </c>
-    </row>
-    <row r="73" spans="2:21">
+    </row>
+    <row r="73" spans="2:12">
       <c r="B73" t="s">
         <v>475</v>
       </c>
@@ -31144,28 +29186,8 @@
       <c r="L73" t="s">
         <v>709</v>
       </c>
-      <c r="O73" t="s">
-        <v>538</v>
-      </c>
-      <c r="P73" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q73" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>South-West</v>
-      </c>
-      <c r="S73" t="s">
-        <v>538</v>
-      </c>
-      <c r="T73" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U73" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Ibadan</v>
-      </c>
-    </row>
-    <row r="74" spans="2:21">
+    </row>
+    <row r="74" spans="2:12">
       <c r="B74" t="s">
         <v>475</v>
       </c>
@@ -31193,28 +29215,8 @@
       <c r="L74" t="s">
         <v>710</v>
       </c>
-      <c r="O74" t="s">
-        <v>539</v>
-      </c>
-      <c r="P74" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q74" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>North-Central</v>
-      </c>
-      <c r="S74" t="s">
-        <v>539</v>
-      </c>
-      <c r="T74" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U74" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Ibadan</v>
-      </c>
-    </row>
-    <row r="75" spans="2:21">
+    </row>
+    <row r="75" spans="2:12">
       <c r="B75" t="s">
         <v>475</v>
       </c>
@@ -31242,28 +29244,8 @@
       <c r="L75" t="s">
         <v>711</v>
       </c>
-      <c r="O75" t="s">
-        <v>540</v>
-      </c>
-      <c r="P75" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q75" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>South-West</v>
-      </c>
-      <c r="S75" t="s">
-        <v>540</v>
-      </c>
-      <c r="T75" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U75" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Ibadan</v>
-      </c>
-    </row>
-    <row r="76" spans="2:21">
+    </row>
+    <row r="76" spans="2:12">
       <c r="B76" t="s">
         <v>475</v>
       </c>
@@ -31291,28 +29273,8 @@
       <c r="L76" t="s">
         <v>712</v>
       </c>
-      <c r="O76" t="s">
-        <v>541</v>
-      </c>
-      <c r="P76" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q76" s="9" t="str">
-        <f t="shared" ref="Q76:Q139" si="2">VLOOKUP(H76,$Y$12:$Z$45,2,FALSE)</f>
-        <v>South-West</v>
-      </c>
-      <c r="S76" t="s">
-        <v>541</v>
-      </c>
-      <c r="T76" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U76" s="9" t="str">
-        <f t="shared" ref="U76:U139" si="3">VLOOKUP(H76,$AC$12:$AD$45,2,FALSE)</f>
-        <v>Ibadan</v>
-      </c>
-    </row>
-    <row r="77" spans="2:21">
+    </row>
+    <row r="77" spans="2:12">
       <c r="B77" t="s">
         <v>475</v>
       </c>
@@ -31340,28 +29302,8 @@
       <c r="L77" t="s">
         <v>713</v>
       </c>
-      <c r="O77" t="s">
-        <v>542</v>
-      </c>
-      <c r="P77" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q77" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>South-South</v>
-      </c>
-      <c r="S77" t="s">
-        <v>542</v>
-      </c>
-      <c r="T77" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U77" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>Benin</v>
-      </c>
-    </row>
-    <row r="78" spans="2:21">
+    </row>
+    <row r="78" spans="2:12">
       <c r="B78" t="s">
         <v>475</v>
       </c>
@@ -31389,28 +29331,8 @@
       <c r="L78" t="s">
         <v>714</v>
       </c>
-      <c r="O78" t="s">
-        <v>543</v>
-      </c>
-      <c r="P78" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q78" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>South-West</v>
-      </c>
-      <c r="S78" t="s">
-        <v>543</v>
-      </c>
-      <c r="T78" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U78" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>Benin</v>
-      </c>
-    </row>
-    <row r="79" spans="2:21">
+    </row>
+    <row r="79" spans="2:12">
       <c r="B79" t="s">
         <v>475</v>
       </c>
@@ -31438,28 +29360,8 @@
       <c r="L79" t="s">
         <v>715</v>
       </c>
-      <c r="O79" t="s">
-        <v>544</v>
-      </c>
-      <c r="P79" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q79" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>South-South</v>
-      </c>
-      <c r="S79" t="s">
-        <v>544</v>
-      </c>
-      <c r="T79" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U79" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>Port Harcourt</v>
-      </c>
-    </row>
-    <row r="80" spans="2:21">
+    </row>
+    <row r="80" spans="2:12">
       <c r="B80" t="s">
         <v>475</v>
       </c>
@@ -31487,28 +29389,8 @@
       <c r="L80" t="s">
         <v>716</v>
       </c>
-      <c r="O80" t="s">
-        <v>545</v>
-      </c>
-      <c r="P80" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q80" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>South-South</v>
-      </c>
-      <c r="S80" t="s">
-        <v>545</v>
-      </c>
-      <c r="T80" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U80" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>Port Harcourt</v>
-      </c>
-    </row>
-    <row r="81" spans="2:21">
+    </row>
+    <row r="81" spans="2:12">
       <c r="B81" t="s">
         <v>475</v>
       </c>
@@ -31536,28 +29418,8 @@
       <c r="L81" t="s">
         <v>717</v>
       </c>
-      <c r="O81" t="s">
-        <v>546</v>
-      </c>
-      <c r="P81" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q81" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>South-South</v>
-      </c>
-      <c r="S81" t="s">
-        <v>546</v>
-      </c>
-      <c r="T81" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U81" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>Benin</v>
-      </c>
-    </row>
-    <row r="82" spans="2:21">
+    </row>
+    <row r="82" spans="2:12">
       <c r="B82" t="s">
         <v>475</v>
       </c>
@@ -31585,28 +29447,8 @@
       <c r="L82" t="s">
         <v>718</v>
       </c>
-      <c r="O82" t="s">
-        <v>547</v>
-      </c>
-      <c r="P82" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q82" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>South-South</v>
-      </c>
-      <c r="S82" t="s">
-        <v>547</v>
-      </c>
-      <c r="T82" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U82" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>Benin</v>
-      </c>
-    </row>
-    <row r="83" spans="2:21">
+    </row>
+    <row r="83" spans="2:12">
       <c r="B83" t="s">
         <v>475</v>
       </c>
@@ -31634,28 +29476,8 @@
       <c r="L83" t="s">
         <v>719</v>
       </c>
-      <c r="O83" t="s">
-        <v>548</v>
-      </c>
-      <c r="P83" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q83" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>South-South</v>
-      </c>
-      <c r="S83" t="s">
-        <v>548</v>
-      </c>
-      <c r="T83" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U83" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>Benin</v>
-      </c>
-    </row>
-    <row r="84" spans="2:21">
+    </row>
+    <row r="84" spans="2:12">
       <c r="B84" t="s">
         <v>475</v>
       </c>
@@ -31683,28 +29505,8 @@
       <c r="L84" t="s">
         <v>720</v>
       </c>
-      <c r="O84" t="s">
-        <v>549</v>
-      </c>
-      <c r="P84" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q84" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>South-South</v>
-      </c>
-      <c r="S84" t="s">
-        <v>549</v>
-      </c>
-      <c r="T84" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U84" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>Port Harcourt</v>
-      </c>
-    </row>
-    <row r="85" spans="2:21">
+    </row>
+    <row r="85" spans="2:12">
       <c r="B85" t="s">
         <v>475</v>
       </c>
@@ -31732,28 +29534,8 @@
       <c r="L85" t="s">
         <v>721</v>
       </c>
-      <c r="O85" t="s">
-        <v>550</v>
-      </c>
-      <c r="P85" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q85" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>South-South</v>
-      </c>
-      <c r="S85" t="s">
-        <v>550</v>
-      </c>
-      <c r="T85" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U85" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>Port Harcourt</v>
-      </c>
-    </row>
-    <row r="86" spans="2:21">
+    </row>
+    <row r="86" spans="2:12">
       <c r="B86" t="s">
         <v>475</v>
       </c>
@@ -31781,28 +29563,8 @@
       <c r="L86" t="s">
         <v>722</v>
       </c>
-      <c r="O86" t="s">
-        <v>551</v>
-      </c>
-      <c r="P86" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q86" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>South-South</v>
-      </c>
-      <c r="S86" t="s">
-        <v>551</v>
-      </c>
-      <c r="T86" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U86" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>Port Harcourt</v>
-      </c>
-    </row>
-    <row r="87" spans="2:21">
+    </row>
+    <row r="87" spans="2:12">
       <c r="B87" t="s">
         <v>475</v>
       </c>
@@ -31830,28 +29592,8 @@
       <c r="L87" t="s">
         <v>723</v>
       </c>
-      <c r="O87" t="s">
-        <v>552</v>
-      </c>
-      <c r="P87" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q87" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>North-East</v>
-      </c>
-      <c r="S87" t="s">
-        <v>552</v>
-      </c>
-      <c r="T87" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U87" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>Yola</v>
-      </c>
-    </row>
-    <row r="88" spans="2:21">
+    </row>
+    <row r="88" spans="2:12">
       <c r="B88" t="s">
         <v>475</v>
       </c>
@@ -31879,28 +29621,8 @@
       <c r="L88" t="s">
         <v>724</v>
       </c>
-      <c r="O88" t="s">
-        <v>553</v>
-      </c>
-      <c r="P88" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q88" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>North-East</v>
-      </c>
-      <c r="S88" t="s">
-        <v>553</v>
-      </c>
-      <c r="T88" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U88" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>Yola</v>
-      </c>
-    </row>
-    <row r="89" spans="2:21">
+    </row>
+    <row r="89" spans="2:12">
       <c r="B89" t="s">
         <v>475</v>
       </c>
@@ -31928,28 +29650,8 @@
       <c r="L89" t="s">
         <v>725</v>
       </c>
-      <c r="O89" t="s">
-        <v>554</v>
-      </c>
-      <c r="P89" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q89" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>North-East</v>
-      </c>
-      <c r="S89" t="s">
-        <v>554</v>
-      </c>
-      <c r="T89" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U89" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>Yola</v>
-      </c>
-    </row>
-    <row r="90" spans="2:21">
+    </row>
+    <row r="90" spans="2:12">
       <c r="B90" t="s">
         <v>475</v>
       </c>
@@ -31977,28 +29679,8 @@
       <c r="L90" t="s">
         <v>726</v>
       </c>
-      <c r="O90" t="s">
-        <v>555</v>
-      </c>
-      <c r="P90" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q90" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>North-East</v>
-      </c>
-      <c r="S90" t="s">
-        <v>555</v>
-      </c>
-      <c r="T90" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U90" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>Yola</v>
-      </c>
-    </row>
-    <row r="91" spans="2:21">
+    </row>
+    <row r="91" spans="2:12">
       <c r="B91" t="s">
         <v>475</v>
       </c>
@@ -32026,28 +29708,8 @@
       <c r="L91" t="s">
         <v>727</v>
       </c>
-      <c r="O91" t="s">
-        <v>556</v>
-      </c>
-      <c r="P91" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q91" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>North-East</v>
-      </c>
-      <c r="S91" t="s">
-        <v>556</v>
-      </c>
-      <c r="T91" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U91" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>Yola</v>
-      </c>
-    </row>
-    <row r="92" spans="2:21">
+    </row>
+    <row r="92" spans="2:12">
       <c r="B92" t="s">
         <v>475</v>
       </c>
@@ -32075,28 +29737,8 @@
       <c r="L92" t="s">
         <v>728</v>
       </c>
-      <c r="O92" t="s">
-        <v>557</v>
-      </c>
-      <c r="P92" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q92" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>North-East</v>
-      </c>
-      <c r="S92" t="s">
-        <v>557</v>
-      </c>
-      <c r="T92" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U92" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>Yola</v>
-      </c>
-    </row>
-    <row r="93" spans="2:21">
+    </row>
+    <row r="93" spans="2:12">
       <c r="B93" t="s">
         <v>475</v>
       </c>
@@ -32124,28 +29766,8 @@
       <c r="L93" t="s">
         <v>729</v>
       </c>
-      <c r="O93" t="s">
-        <v>558</v>
-      </c>
-      <c r="P93" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q93" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>North-Central</v>
-      </c>
-      <c r="S93" t="s">
-        <v>558</v>
-      </c>
-      <c r="T93" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U93" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>Jos</v>
-      </c>
-    </row>
-    <row r="94" spans="2:21">
+    </row>
+    <row r="94" spans="2:12">
       <c r="B94" t="s">
         <v>475</v>
       </c>
@@ -32173,28 +29795,8 @@
       <c r="L94" t="s">
         <v>730</v>
       </c>
-      <c r="O94" t="s">
-        <v>559</v>
-      </c>
-      <c r="P94" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q94" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>North-Central</v>
-      </c>
-      <c r="S94" t="s">
-        <v>559</v>
-      </c>
-      <c r="T94" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U94" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>Abuja</v>
-      </c>
-    </row>
-    <row r="95" spans="2:21">
+    </row>
+    <row r="95" spans="2:12">
       <c r="B95" t="s">
         <v>475</v>
       </c>
@@ -32222,28 +29824,8 @@
       <c r="L95" t="s">
         <v>731</v>
       </c>
-      <c r="O95" t="s">
-        <v>560</v>
-      </c>
-      <c r="P95" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q95" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>North-Central</v>
-      </c>
-      <c r="S95" t="s">
-        <v>560</v>
-      </c>
-      <c r="T95" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U95" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>Jos</v>
-      </c>
-    </row>
-    <row r="96" spans="2:21">
+    </row>
+    <row r="96" spans="2:12">
       <c r="B96" t="s">
         <v>475</v>
       </c>
@@ -32271,28 +29853,8 @@
       <c r="L96" t="s">
         <v>732</v>
       </c>
-      <c r="O96" t="s">
-        <v>561</v>
-      </c>
-      <c r="P96" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q96" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>North-Central</v>
-      </c>
-      <c r="S96" t="s">
-        <v>561</v>
-      </c>
-      <c r="T96" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U96" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>Jos</v>
-      </c>
-    </row>
-    <row r="97" spans="2:21">
+    </row>
+    <row r="97" spans="2:12">
       <c r="B97" t="s">
         <v>475</v>
       </c>
@@ -32320,28 +29882,8 @@
       <c r="L97" t="s">
         <v>733</v>
       </c>
-      <c r="O97" t="s">
-        <v>562</v>
-      </c>
-      <c r="P97" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q97" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>North-Central</v>
-      </c>
-      <c r="S97" t="s">
-        <v>562</v>
-      </c>
-      <c r="T97" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U97" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>Abuja</v>
-      </c>
-    </row>
-    <row r="98" spans="2:21">
+    </row>
+    <row r="98" spans="2:12">
       <c r="B98" t="s">
         <v>475</v>
       </c>
@@ -32369,28 +29911,8 @@
       <c r="L98" t="s">
         <v>734</v>
       </c>
-      <c r="O98" t="s">
-        <v>563</v>
-      </c>
-      <c r="P98" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q98" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>North-Central</v>
-      </c>
-      <c r="S98" t="s">
-        <v>563</v>
-      </c>
-      <c r="T98" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U98" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>Abuja</v>
-      </c>
-    </row>
-    <row r="99" spans="2:21">
+    </row>
+    <row r="99" spans="2:12">
       <c r="B99" t="s">
         <v>475</v>
       </c>
@@ -32418,28 +29940,8 @@
       <c r="L99" t="s">
         <v>735</v>
       </c>
-      <c r="O99" t="s">
-        <v>564</v>
-      </c>
-      <c r="P99" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q99" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>North-East</v>
-      </c>
-      <c r="S99" t="s">
-        <v>564</v>
-      </c>
-      <c r="T99" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U99" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>Jos</v>
-      </c>
-    </row>
-    <row r="100" spans="2:21">
+    </row>
+    <row r="100" spans="2:12">
       <c r="B100" t="s">
         <v>475</v>
       </c>
@@ -32467,28 +29969,8 @@
       <c r="L100" t="s">
         <v>736</v>
       </c>
-      <c r="O100" t="s">
-        <v>565</v>
-      </c>
-      <c r="P100" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q100" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>North-West</v>
-      </c>
-      <c r="S100" t="s">
-        <v>565</v>
-      </c>
-      <c r="T100" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U100" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>Kano</v>
-      </c>
-    </row>
-    <row r="101" spans="2:21">
+    </row>
+    <row r="101" spans="2:12">
       <c r="B101" t="s">
         <v>475</v>
       </c>
@@ -32516,28 +29998,8 @@
       <c r="L101" t="s">
         <v>737</v>
       </c>
-      <c r="O101" t="s">
-        <v>566</v>
-      </c>
-      <c r="P101" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q101" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>North-West</v>
-      </c>
-      <c r="S101" t="s">
-        <v>566</v>
-      </c>
-      <c r="T101" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U101" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>Kano</v>
-      </c>
-    </row>
-    <row r="102" spans="2:21">
+    </row>
+    <row r="102" spans="2:12">
       <c r="B102" t="s">
         <v>475</v>
       </c>
@@ -32565,28 +30027,8 @@
       <c r="L102" t="s">
         <v>738</v>
       </c>
-      <c r="O102" t="s">
-        <v>567</v>
-      </c>
-      <c r="P102" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q102" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>North-West</v>
-      </c>
-      <c r="S102" t="s">
-        <v>567</v>
-      </c>
-      <c r="T102" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U102" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>Kaduna</v>
-      </c>
-    </row>
-    <row r="103" spans="2:21">
+    </row>
+    <row r="103" spans="2:12">
       <c r="B103" t="s">
         <v>475</v>
       </c>
@@ -32614,28 +30056,8 @@
       <c r="L103" t="s">
         <v>739</v>
       </c>
-      <c r="O103" t="s">
-        <v>568</v>
-      </c>
-      <c r="P103" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q103" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>North-West</v>
-      </c>
-      <c r="S103" t="s">
-        <v>568</v>
-      </c>
-      <c r="T103" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U103" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>Kaduna</v>
-      </c>
-    </row>
-    <row r="104" spans="2:21">
+    </row>
+    <row r="104" spans="2:12">
       <c r="B104" t="s">
         <v>475</v>
       </c>
@@ -32663,28 +30085,8 @@
       <c r="L104" t="s">
         <v>740</v>
       </c>
-      <c r="O104" t="s">
-        <v>569</v>
-      </c>
-      <c r="P104" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q104" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>North-Central</v>
-      </c>
-      <c r="S104" t="s">
-        <v>569</v>
-      </c>
-      <c r="T104" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U104" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>Abuja</v>
-      </c>
-    </row>
-    <row r="105" spans="2:21">
+    </row>
+    <row r="105" spans="2:12">
       <c r="B105" t="s">
         <v>475</v>
       </c>
@@ -32712,28 +30114,8 @@
       <c r="L105" t="s">
         <v>741</v>
       </c>
-      <c r="O105" t="s">
-        <v>570</v>
-      </c>
-      <c r="P105" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q105" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>North-West</v>
-      </c>
-      <c r="S105" t="s">
-        <v>570</v>
-      </c>
-      <c r="T105" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U105" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>Kaduna</v>
-      </c>
-    </row>
-    <row r="106" spans="2:21">
+    </row>
+    <row r="106" spans="2:12">
       <c r="B106" t="s">
         <v>475</v>
       </c>
@@ -32761,28 +30143,8 @@
       <c r="L106" t="s">
         <v>742</v>
       </c>
-      <c r="O106" t="s">
-        <v>571</v>
-      </c>
-      <c r="P106" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q106" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>North-Central</v>
-      </c>
-      <c r="S106" t="s">
-        <v>571</v>
-      </c>
-      <c r="T106" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U106" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>Abuja</v>
-      </c>
-    </row>
-    <row r="107" spans="2:21">
+    </row>
+    <row r="107" spans="2:12">
       <c r="B107" t="s">
         <v>475</v>
       </c>
@@ -32810,28 +30172,8 @@
       <c r="L107" t="s">
         <v>743</v>
       </c>
-      <c r="O107" t="s">
-        <v>572</v>
-      </c>
-      <c r="P107" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q107" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>North-West</v>
-      </c>
-      <c r="S107" t="s">
-        <v>572</v>
-      </c>
-      <c r="T107" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U107" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>Kaduna</v>
-      </c>
-    </row>
-    <row r="108" spans="2:21">
+    </row>
+    <row r="108" spans="2:12">
       <c r="B108" t="s">
         <v>475</v>
       </c>
@@ -32859,28 +30201,8 @@
       <c r="L108" t="s">
         <v>744</v>
       </c>
-      <c r="O108" t="s">
-        <v>573</v>
-      </c>
-      <c r="P108" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q108" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>North-Central</v>
-      </c>
-      <c r="S108" t="s">
-        <v>573</v>
-      </c>
-      <c r="T108" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U108" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>Ibadan</v>
-      </c>
-    </row>
-    <row r="109" spans="2:21">
+    </row>
+    <row r="109" spans="2:12">
       <c r="B109" t="s">
         <v>475</v>
       </c>
@@ -32908,28 +30230,8 @@
       <c r="L109" t="s">
         <v>745</v>
       </c>
-      <c r="O109" t="s">
-        <v>574</v>
-      </c>
-      <c r="P109" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q109" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>North-Central</v>
-      </c>
-      <c r="S109" t="s">
-        <v>574</v>
-      </c>
-      <c r="T109" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U109" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>Jos</v>
-      </c>
-    </row>
-    <row r="110" spans="2:21">
+    </row>
+    <row r="110" spans="2:12">
       <c r="B110" t="s">
         <v>475</v>
       </c>
@@ -32957,28 +30259,8 @@
       <c r="L110" t="s">
         <v>746</v>
       </c>
-      <c r="O110" t="s">
-        <v>575</v>
-      </c>
-      <c r="P110" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q110" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>North-East</v>
-      </c>
-      <c r="S110" t="s">
-        <v>575</v>
-      </c>
-      <c r="T110" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U110" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>Yola</v>
-      </c>
-    </row>
-    <row r="111" spans="2:21">
+    </row>
+    <row r="111" spans="2:12">
       <c r="B111" t="s">
         <v>475</v>
       </c>
@@ -33006,28 +30288,8 @@
       <c r="L111" t="s">
         <v>747</v>
       </c>
-      <c r="O111" t="s">
-        <v>576</v>
-      </c>
-      <c r="P111" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q111" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>North-East</v>
-      </c>
-      <c r="S111" t="s">
-        <v>576</v>
-      </c>
-      <c r="T111" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U111" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>Yola</v>
-      </c>
-    </row>
-    <row r="112" spans="2:21">
+    </row>
+    <row r="112" spans="2:12">
       <c r="B112" t="s">
         <v>475</v>
       </c>
@@ -33055,28 +30317,8 @@
       <c r="L112" t="s">
         <v>748</v>
       </c>
-      <c r="O112" t="s">
-        <v>577</v>
-      </c>
-      <c r="P112" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q112" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>North-East</v>
-      </c>
-      <c r="S112" t="s">
-        <v>577</v>
-      </c>
-      <c r="T112" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U112" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>Yola</v>
-      </c>
-    </row>
-    <row r="113" spans="2:21">
+    </row>
+    <row r="113" spans="2:12">
       <c r="B113" t="s">
         <v>475</v>
       </c>
@@ -33104,28 +30346,8 @@
       <c r="L113" t="s">
         <v>749</v>
       </c>
-      <c r="O113" t="s">
-        <v>578</v>
-      </c>
-      <c r="P113" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q113" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>North-Central</v>
-      </c>
-      <c r="S113" t="s">
-        <v>578</v>
-      </c>
-      <c r="T113" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U113" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>Jos</v>
-      </c>
-    </row>
-    <row r="114" spans="2:21">
+    </row>
+    <row r="114" spans="2:12">
       <c r="B114" t="s">
         <v>475</v>
       </c>
@@ -33153,28 +30375,8 @@
       <c r="L114" t="s">
         <v>750</v>
       </c>
-      <c r="O114" t="s">
-        <v>579</v>
-      </c>
-      <c r="P114" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q114" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>North-Central</v>
-      </c>
-      <c r="S114" t="s">
-        <v>579</v>
-      </c>
-      <c r="T114" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U114" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>Ibadan</v>
-      </c>
-    </row>
-    <row r="115" spans="2:21">
+    </row>
+    <row r="115" spans="2:12">
       <c r="B115" t="s">
         <v>475</v>
       </c>
@@ -33202,28 +30404,8 @@
       <c r="L115" t="s">
         <v>751</v>
       </c>
-      <c r="O115" t="s">
-        <v>580</v>
-      </c>
-      <c r="P115" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q115" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>North-Central</v>
-      </c>
-      <c r="S115" t="s">
-        <v>580</v>
-      </c>
-      <c r="T115" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U115" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>Ibadan</v>
-      </c>
-    </row>
-    <row r="116" spans="2:21">
+    </row>
+    <row r="116" spans="2:12">
       <c r="B116" t="s">
         <v>475</v>
       </c>
@@ -33251,28 +30433,8 @@
       <c r="L116" t="s">
         <v>752</v>
       </c>
-      <c r="O116" t="s">
-        <v>581</v>
-      </c>
-      <c r="P116" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q116" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>Unknown</v>
-      </c>
-      <c r="S116" t="s">
-        <v>581</v>
-      </c>
-      <c r="T116" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U116" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>Unknown</v>
-      </c>
-    </row>
-    <row r="117" spans="2:21">
+    </row>
+    <row r="117" spans="2:12">
       <c r="B117" t="s">
         <v>475</v>
       </c>
@@ -33300,28 +30462,8 @@
       <c r="L117" t="s">
         <v>753</v>
       </c>
-      <c r="O117" t="s">
-        <v>582</v>
-      </c>
-      <c r="P117" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q117" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>North-Central</v>
-      </c>
-      <c r="S117" t="s">
-        <v>582</v>
-      </c>
-      <c r="T117" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U117" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>Abuja</v>
-      </c>
-    </row>
-    <row r="118" spans="2:21">
+    </row>
+    <row r="118" spans="2:12">
       <c r="B118" t="s">
         <v>475</v>
       </c>
@@ -33349,28 +30491,8 @@
       <c r="L118" t="s">
         <v>754</v>
       </c>
-      <c r="O118" t="s">
-        <v>583</v>
-      </c>
-      <c r="P118" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q118" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>North-West</v>
-      </c>
-      <c r="S118" t="s">
-        <v>583</v>
-      </c>
-      <c r="T118" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U118" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>Kaduna</v>
-      </c>
-    </row>
-    <row r="119" spans="2:21">
+    </row>
+    <row r="119" spans="2:12">
       <c r="B119" t="s">
         <v>475</v>
       </c>
@@ -33398,28 +30520,8 @@
       <c r="L119" t="s">
         <v>755</v>
       </c>
-      <c r="O119" t="s">
-        <v>584</v>
-      </c>
-      <c r="P119" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q119" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>North-West</v>
-      </c>
-      <c r="S119" t="s">
-        <v>584</v>
-      </c>
-      <c r="T119" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U119" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>Kaduna</v>
-      </c>
-    </row>
-    <row r="120" spans="2:21">
+    </row>
+    <row r="120" spans="2:12">
       <c r="B120" t="s">
         <v>475</v>
       </c>
@@ -33447,28 +30549,8 @@
       <c r="L120" t="s">
         <v>756</v>
       </c>
-      <c r="O120" t="s">
-        <v>585</v>
-      </c>
-      <c r="P120" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q120" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>North-Central</v>
-      </c>
-      <c r="S120" t="s">
-        <v>585</v>
-      </c>
-      <c r="T120" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U120" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>Abuja</v>
-      </c>
-    </row>
-    <row r="121" spans="2:21">
+    </row>
+    <row r="121" spans="2:12">
       <c r="B121" t="s">
         <v>475</v>
       </c>
@@ -33496,28 +30578,8 @@
       <c r="L121" t="s">
         <v>757</v>
       </c>
-      <c r="O121" t="s">
-        <v>586</v>
-      </c>
-      <c r="P121" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q121" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>North-West</v>
-      </c>
-      <c r="S121" t="s">
-        <v>586</v>
-      </c>
-      <c r="T121" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U121" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>Kaduna</v>
-      </c>
-    </row>
-    <row r="122" spans="2:21">
+    </row>
+    <row r="122" spans="2:12">
       <c r="B122" t="s">
         <v>475</v>
       </c>
@@ -33545,28 +30607,8 @@
       <c r="L122" t="s">
         <v>758</v>
       </c>
-      <c r="O122" t="s">
-        <v>587</v>
-      </c>
-      <c r="P122" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q122" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>North-West</v>
-      </c>
-      <c r="S122" t="s">
-        <v>587</v>
-      </c>
-      <c r="T122" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U122" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>Kaduna</v>
-      </c>
-    </row>
-    <row r="123" spans="2:21">
+    </row>
+    <row r="123" spans="2:12">
       <c r="B123" t="s">
         <v>475</v>
       </c>
@@ -33594,28 +30636,8 @@
       <c r="L123" t="s">
         <v>759</v>
       </c>
-      <c r="O123" t="s">
-        <v>588</v>
-      </c>
-      <c r="P123" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q123" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>North-West</v>
-      </c>
-      <c r="S123" t="s">
-        <v>588</v>
-      </c>
-      <c r="T123" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U123" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>Kaduna</v>
-      </c>
-    </row>
-    <row r="124" spans="2:21">
+    </row>
+    <row r="124" spans="2:12">
       <c r="B124" t="s">
         <v>475</v>
       </c>
@@ -33643,28 +30665,8 @@
       <c r="L124" t="s">
         <v>760</v>
       </c>
-      <c r="O124" t="s">
-        <v>589</v>
-      </c>
-      <c r="P124" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q124" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>North-East</v>
-      </c>
-      <c r="S124" t="s">
-        <v>589</v>
-      </c>
-      <c r="T124" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U124" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>Yola</v>
-      </c>
-    </row>
-    <row r="125" spans="2:21">
+    </row>
+    <row r="125" spans="2:12">
       <c r="B125" t="s">
         <v>475</v>
       </c>
@@ -33692,28 +30694,8 @@
       <c r="L125" t="s">
         <v>761</v>
       </c>
-      <c r="O125" t="s">
-        <v>590</v>
-      </c>
-      <c r="P125" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q125" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>North-East</v>
-      </c>
-      <c r="S125" t="s">
-        <v>590</v>
-      </c>
-      <c r="T125" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U125" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>Yola</v>
-      </c>
-    </row>
-    <row r="126" spans="2:21">
+    </row>
+    <row r="126" spans="2:12">
       <c r="B126" t="s">
         <v>475</v>
       </c>
@@ -33741,28 +30723,8 @@
       <c r="L126" t="s">
         <v>762</v>
       </c>
-      <c r="O126" t="s">
-        <v>591</v>
-      </c>
-      <c r="P126" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q126" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>North-East</v>
-      </c>
-      <c r="S126" t="s">
-        <v>591</v>
-      </c>
-      <c r="T126" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U126" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>Yola</v>
-      </c>
-    </row>
-    <row r="127" spans="2:21">
+    </row>
+    <row r="127" spans="2:12">
       <c r="B127" t="s">
         <v>475</v>
       </c>
@@ -33790,28 +30752,8 @@
       <c r="L127" t="s">
         <v>763</v>
       </c>
-      <c r="O127" t="s">
-        <v>592</v>
-      </c>
-      <c r="P127" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q127" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>North-East</v>
-      </c>
-      <c r="S127" t="s">
-        <v>592</v>
-      </c>
-      <c r="T127" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U127" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>Yola</v>
-      </c>
-    </row>
-    <row r="128" spans="2:21">
+    </row>
+    <row r="128" spans="2:12">
       <c r="B128" t="s">
         <v>475</v>
       </c>
@@ -33839,28 +30781,8 @@
       <c r="L128" t="s">
         <v>764</v>
       </c>
-      <c r="O128" t="s">
-        <v>593</v>
-      </c>
-      <c r="P128" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q128" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>North-East</v>
-      </c>
-      <c r="S128" t="s">
-        <v>593</v>
-      </c>
-      <c r="T128" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U128" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>Jos</v>
-      </c>
-    </row>
-    <row r="129" spans="2:21">
+    </row>
+    <row r="129" spans="2:12">
       <c r="B129" t="s">
         <v>475</v>
       </c>
@@ -33888,28 +30810,8 @@
       <c r="L129" t="s">
         <v>765</v>
       </c>
-      <c r="O129" t="s">
-        <v>594</v>
-      </c>
-      <c r="P129" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q129" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>North-East</v>
-      </c>
-      <c r="S129" t="s">
-        <v>594</v>
-      </c>
-      <c r="T129" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U129" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>Jos</v>
-      </c>
-    </row>
-    <row r="130" spans="2:21">
+    </row>
+    <row r="130" spans="2:12">
       <c r="B130" t="s">
         <v>475</v>
       </c>
@@ -33937,28 +30839,8 @@
       <c r="L130" t="s">
         <v>766</v>
       </c>
-      <c r="O130" t="s">
-        <v>595</v>
-      </c>
-      <c r="P130" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q130" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>North-West</v>
-      </c>
-      <c r="S130" t="s">
-        <v>595</v>
-      </c>
-      <c r="T130" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U130" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>Kano</v>
-      </c>
-    </row>
-    <row r="131" spans="2:21">
+    </row>
+    <row r="131" spans="2:12">
       <c r="B131" t="s">
         <v>475</v>
       </c>
@@ -33986,28 +30868,8 @@
       <c r="L131" t="s">
         <v>767</v>
       </c>
-      <c r="O131" t="s">
-        <v>596</v>
-      </c>
-      <c r="P131" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q131" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>North-West</v>
-      </c>
-      <c r="S131" t="s">
-        <v>596</v>
-      </c>
-      <c r="T131" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U131" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>Kaduna</v>
-      </c>
-    </row>
-    <row r="132" spans="2:21">
+    </row>
+    <row r="132" spans="2:12">
       <c r="B132" t="s">
         <v>475</v>
       </c>
@@ -34035,28 +30897,8 @@
       <c r="L132" t="s">
         <v>768</v>
       </c>
-      <c r="O132" t="s">
-        <v>597</v>
-      </c>
-      <c r="P132" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q132" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>North-East</v>
-      </c>
-      <c r="S132" t="s">
-        <v>597</v>
-      </c>
-      <c r="T132" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U132" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>Jos</v>
-      </c>
-    </row>
-    <row r="133" spans="2:21">
+    </row>
+    <row r="133" spans="2:12">
       <c r="B133" t="s">
         <v>475</v>
       </c>
@@ -34084,28 +30926,8 @@
       <c r="L133" t="s">
         <v>769</v>
       </c>
-      <c r="O133" t="s">
-        <v>598</v>
-      </c>
-      <c r="P133" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q133" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>North-West</v>
-      </c>
-      <c r="S133" t="s">
-        <v>598</v>
-      </c>
-      <c r="T133" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U133" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>Kano</v>
-      </c>
-    </row>
-    <row r="134" spans="2:21">
+    </row>
+    <row r="134" spans="2:12">
       <c r="B134" t="s">
         <v>475</v>
       </c>
@@ -34133,28 +30955,8 @@
       <c r="L134" t="s">
         <v>770</v>
       </c>
-      <c r="O134" t="s">
-        <v>599</v>
-      </c>
-      <c r="P134" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q134" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>North-East</v>
-      </c>
-      <c r="S134" t="s">
-        <v>599</v>
-      </c>
-      <c r="T134" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U134" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>Yola</v>
-      </c>
-    </row>
-    <row r="135" spans="2:21">
+    </row>
+    <row r="135" spans="2:12">
       <c r="B135" t="s">
         <v>475</v>
       </c>
@@ -34182,28 +30984,8 @@
       <c r="L135" t="s">
         <v>771</v>
       </c>
-      <c r="O135" t="s">
-        <v>600</v>
-      </c>
-      <c r="P135" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q135" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>North-East</v>
-      </c>
-      <c r="S135" t="s">
-        <v>600</v>
-      </c>
-      <c r="T135" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U135" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>Jos</v>
-      </c>
-    </row>
-    <row r="136" spans="2:21">
+    </row>
+    <row r="136" spans="2:12">
       <c r="B136" t="s">
         <v>475</v>
       </c>
@@ -34231,28 +31013,8 @@
       <c r="L136" t="s">
         <v>772</v>
       </c>
-      <c r="O136" t="s">
-        <v>601</v>
-      </c>
-      <c r="P136" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q136" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>South-West</v>
-      </c>
-      <c r="S136" t="s">
-        <v>601</v>
-      </c>
-      <c r="T136" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U136" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>Ibadan</v>
-      </c>
-    </row>
-    <row r="137" spans="2:21">
+    </row>
+    <row r="137" spans="2:12">
       <c r="B137" t="s">
         <v>475</v>
       </c>
@@ -34280,28 +31042,8 @@
       <c r="L137" t="s">
         <v>773</v>
       </c>
-      <c r="O137" t="s">
-        <v>602</v>
-      </c>
-      <c r="P137" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q137" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>Unknown</v>
-      </c>
-      <c r="S137" t="s">
-        <v>602</v>
-      </c>
-      <c r="T137" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U137" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>Unknown</v>
-      </c>
-    </row>
-    <row r="138" spans="2:21">
+    </row>
+    <row r="138" spans="2:12">
       <c r="B138" t="s">
         <v>475</v>
       </c>
@@ -34329,28 +31071,8 @@
       <c r="L138" t="s">
         <v>774</v>
       </c>
-      <c r="O138" t="s">
-        <v>603</v>
-      </c>
-      <c r="P138" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q138" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>Unknown</v>
-      </c>
-      <c r="S138" t="s">
-        <v>603</v>
-      </c>
-      <c r="T138" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U138" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>Unknown</v>
-      </c>
-    </row>
-    <row r="139" spans="2:21">
+    </row>
+    <row r="139" spans="2:12">
       <c r="B139" t="s">
         <v>475</v>
       </c>
@@ -34378,28 +31100,8 @@
       <c r="L139" t="s">
         <v>775</v>
       </c>
-      <c r="O139" t="s">
-        <v>604</v>
-      </c>
-      <c r="P139" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q139" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>Unknown</v>
-      </c>
-      <c r="S139" t="s">
-        <v>604</v>
-      </c>
-      <c r="T139" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U139" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>Unknown</v>
-      </c>
-    </row>
-    <row r="140" spans="2:21">
+    </row>
+    <row r="140" spans="2:12">
       <c r="B140" t="s">
         <v>475</v>
       </c>
@@ -34427,28 +31129,8 @@
       <c r="L140" t="s">
         <v>776</v>
       </c>
-      <c r="O140" t="s">
-        <v>605</v>
-      </c>
-      <c r="P140" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q140" s="9" t="str">
-        <f t="shared" ref="Q140:Q145" si="4">VLOOKUP(H140,$Y$12:$Z$45,2,FALSE)</f>
-        <v>Unknown</v>
-      </c>
-      <c r="S140" t="s">
-        <v>605</v>
-      </c>
-      <c r="T140" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U140" s="9" t="str">
-        <f t="shared" ref="U140:U145" si="5">VLOOKUP(H140,$AC$12:$AD$45,2,FALSE)</f>
-        <v>Unknown</v>
-      </c>
-    </row>
-    <row r="141" spans="2:21">
+    </row>
+    <row r="141" spans="2:12">
       <c r="B141" t="s">
         <v>475</v>
       </c>
@@ -34476,28 +31158,8 @@
       <c r="L141" t="s">
         <v>777</v>
       </c>
-      <c r="O141" t="s">
-        <v>606</v>
-      </c>
-      <c r="P141" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q141" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v>Unknown</v>
-      </c>
-      <c r="S141" t="s">
-        <v>606</v>
-      </c>
-      <c r="T141" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U141" s="9" t="str">
-        <f t="shared" si="5"/>
-        <v>Unknown</v>
-      </c>
-    </row>
-    <row r="142" spans="2:21">
+    </row>
+    <row r="142" spans="2:12">
       <c r="B142" t="s">
         <v>475</v>
       </c>
@@ -34525,28 +31187,8 @@
       <c r="L142" t="s">
         <v>778</v>
       </c>
-      <c r="O142" t="s">
-        <v>607</v>
-      </c>
-      <c r="P142" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q142" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v>Unknown</v>
-      </c>
-      <c r="S142" t="s">
-        <v>607</v>
-      </c>
-      <c r="T142" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U142" s="9" t="str">
-        <f t="shared" si="5"/>
-        <v>Unknown</v>
-      </c>
-    </row>
-    <row r="143" spans="2:21">
+    </row>
+    <row r="143" spans="2:12">
       <c r="B143" t="s">
         <v>475</v>
       </c>
@@ -34574,28 +31216,8 @@
       <c r="L143" t="s">
         <v>779</v>
       </c>
-      <c r="O143" t="s">
-        <v>608</v>
-      </c>
-      <c r="P143" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q143" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v>Unknown</v>
-      </c>
-      <c r="S143" t="s">
-        <v>608</v>
-      </c>
-      <c r="T143" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U143" s="9" t="str">
-        <f t="shared" si="5"/>
-        <v>Unknown</v>
-      </c>
-    </row>
-    <row r="144" spans="2:21">
+    </row>
+    <row r="144" spans="2:12">
       <c r="B144" t="s">
         <v>475</v>
       </c>
@@ -34623,28 +31245,8 @@
       <c r="L144" t="s">
         <v>780</v>
       </c>
-      <c r="O144" t="s">
-        <v>609</v>
-      </c>
-      <c r="P144" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q144" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v>Unknown</v>
-      </c>
-      <c r="S144" t="s">
-        <v>609</v>
-      </c>
-      <c r="T144" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U144" s="9" t="str">
-        <f t="shared" si="5"/>
-        <v>Unknown</v>
-      </c>
-    </row>
-    <row r="145" spans="2:21">
+    </row>
+    <row r="145" spans="2:12">
       <c r="B145" t="s">
         <v>475</v>
       </c>
@@ -34671,26 +31273,6 @@
       </c>
       <c r="L145" t="s">
         <v>781</v>
-      </c>
-      <c r="O145" t="s">
-        <v>610</v>
-      </c>
-      <c r="P145" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q145" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v>Unknown</v>
-      </c>
-      <c r="S145" t="s">
-        <v>610</v>
-      </c>
-      <c r="T145" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="U145" s="9" t="str">
-        <f t="shared" si="5"/>
-        <v>Unknown</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_NGA_grids_kan/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_NGA_grids_kan/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NGA_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{96BDD199-9496-4C03-A739-FA4365C0BA1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{ADB1C9C5-A807-4F4D-87E3-D6555A7E9918}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24578,7 +24578,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{968A3CF8-471D-402F-B706-4A6B04C21177}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AAA184C-307E-4BEE-B478-DCAE902B6D29}">
   <dimension ref="B9:H145"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -27316,7 +27316,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{132F03D2-DD83-40E9-A246-CA00D7A1F898}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FB9DB41-6DC9-4049-91DA-BC0D52F1BEB3}">
   <dimension ref="B9:L145"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_NGA_grids_kan/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_NGA_grids_kan/ReportDefs_vervestacks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NGA_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ADB1C9C5-A807-4F4D-87E3-D6555A7E9918}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BFDE066-FFD2-4C4E-8A5A-B162AD1C7A3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ScenMap" sheetId="56" r:id="rId1"/>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5943" uniqueCount="920">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6698" uniqueCount="940">
   <si>
     <t>Unit</t>
   </si>
@@ -2843,6 +2843,66 @@
   </si>
   <si>
     <t>NGA-elc_wof_010</t>
+  </si>
+  <si>
+    <t>Grouping</t>
+  </si>
+  <si>
+    <t>State</t>
+  </si>
+  <si>
+    <t>GroupName</t>
+  </si>
+  <si>
+    <t>Geopolitical</t>
+  </si>
+  <si>
+    <t>North-West</t>
+  </si>
+  <si>
+    <t>North-Central</t>
+  </si>
+  <si>
+    <t>South-West</t>
+  </si>
+  <si>
+    <t>North-East</t>
+  </si>
+  <si>
+    <t>South-South</t>
+  </si>
+  <si>
+    <t>South-East</t>
+  </si>
+  <si>
+    <t>DisCos</t>
+  </si>
+  <si>
+    <t>Abuja</t>
+  </si>
+  <si>
+    <t>Ikeja</t>
+  </si>
+  <si>
+    <t>Jos</t>
+  </si>
+  <si>
+    <t>Yola</t>
+  </si>
+  <si>
+    <t>Port Harcourt</t>
+  </si>
+  <si>
+    <t>Ibadan</t>
+  </si>
+  <si>
+    <t>Benin</t>
+  </si>
+  <si>
+    <t>reg_geopol</t>
+  </si>
+  <si>
+    <t>reg_discom</t>
   </si>
 </sst>
 </file>
@@ -3051,7 +3111,7 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
@@ -3062,6 +3122,12 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="20">
@@ -27317,10 +27383,10 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FB9DB41-6DC9-4049-91DA-BC0D52F1BEB3}">
-  <dimension ref="B9:L145"/>
+  <dimension ref="B9:AD145"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="9" spans="2:12">
+    <row r="9" spans="2:30">
       <c r="B9" t="s">
         <v>59</v>
       </c>
@@ -27330,8 +27396,14 @@
       <c r="J9" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="10" spans="2:12">
+      <c r="O9" t="s">
+        <v>59</v>
+      </c>
+      <c r="S9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="10" spans="2:30">
       <c r="B10" t="s">
         <v>48</v>
       </c>
@@ -27359,8 +27431,35 @@
       <c r="L10" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="11" spans="2:12">
+      <c r="O10" t="s">
+        <v>60</v>
+      </c>
+      <c r="P10" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>50</v>
+      </c>
+      <c r="S10" t="s">
+        <v>60</v>
+      </c>
+      <c r="T10" t="s">
+        <v>48</v>
+      </c>
+      <c r="U10" t="s">
+        <v>50</v>
+      </c>
+      <c r="X10" s="9" t="s">
+        <v>920</v>
+      </c>
+      <c r="Y10" s="9" t="s">
+        <v>921</v>
+      </c>
+      <c r="Z10" s="9" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="11" spans="2:30">
       <c r="B11" t="s">
         <v>475</v>
       </c>
@@ -27388,8 +27487,46 @@
       <c r="L11" t="s">
         <v>647</v>
       </c>
-    </row>
-    <row r="12" spans="2:12">
+      <c r="O11" t="s">
+        <v>476</v>
+      </c>
+      <c r="P11" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q11" t="str">
+        <f>VLOOKUP($H11,$Y$11:$Z$44,2,FALSE)</f>
+        <v>North-West</v>
+      </c>
+      <c r="S11" t="s">
+        <v>476</v>
+      </c>
+      <c r="T11" t="s">
+        <v>939</v>
+      </c>
+      <c r="U11" t="str">
+        <f>VLOOKUP($H11,$AC$11:$AD$44,2,FALSE)</f>
+        <v>Kaduna</v>
+      </c>
+      <c r="X11" s="10" t="s">
+        <v>923</v>
+      </c>
+      <c r="Y11" s="10" t="s">
+        <v>612</v>
+      </c>
+      <c r="Z11" s="10" t="s">
+        <v>924</v>
+      </c>
+      <c r="AB11" s="10" t="s">
+        <v>930</v>
+      </c>
+      <c r="AC11" s="10" t="s">
+        <v>612</v>
+      </c>
+      <c r="AD11" s="10" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="12" spans="2:30">
       <c r="B12" t="s">
         <v>475</v>
       </c>
@@ -27417,8 +27554,46 @@
       <c r="L12" t="s">
         <v>648</v>
       </c>
-    </row>
-    <row r="13" spans="2:12">
+      <c r="O12" t="s">
+        <v>477</v>
+      </c>
+      <c r="P12" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q12" t="str">
+        <f t="shared" ref="Q12:Q75" si="0">VLOOKUP($H12,$Y$11:$Z$44,2,FALSE)</f>
+        <v>North-Central</v>
+      </c>
+      <c r="S12" t="s">
+        <v>477</v>
+      </c>
+      <c r="T12" t="s">
+        <v>939</v>
+      </c>
+      <c r="U12" t="str">
+        <f t="shared" ref="U12:U75" si="1">VLOOKUP($H12,$AC$11:$AD$44,2,FALSE)</f>
+        <v>Abuja</v>
+      </c>
+      <c r="X12" s="10" t="s">
+        <v>923</v>
+      </c>
+      <c r="Y12" s="10" t="s">
+        <v>613</v>
+      </c>
+      <c r="Z12" s="10" t="s">
+        <v>925</v>
+      </c>
+      <c r="AB12" s="10" t="s">
+        <v>930</v>
+      </c>
+      <c r="AC12" s="10" t="s">
+        <v>613</v>
+      </c>
+      <c r="AD12" s="10" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="13" spans="2:30">
       <c r="B13" t="s">
         <v>475</v>
       </c>
@@ -27446,8 +27621,46 @@
       <c r="L13" t="s">
         <v>649</v>
       </c>
-    </row>
-    <row r="14" spans="2:12">
+      <c r="O13" t="s">
+        <v>478</v>
+      </c>
+      <c r="P13" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q13" t="str">
+        <f t="shared" si="0"/>
+        <v>South-West</v>
+      </c>
+      <c r="S13" t="s">
+        <v>478</v>
+      </c>
+      <c r="T13" t="s">
+        <v>939</v>
+      </c>
+      <c r="U13" t="str">
+        <f t="shared" si="1"/>
+        <v>Ikeja</v>
+      </c>
+      <c r="X13" s="10" t="s">
+        <v>923</v>
+      </c>
+      <c r="Y13" s="10" t="s">
+        <v>614</v>
+      </c>
+      <c r="Z13" s="10" t="s">
+        <v>926</v>
+      </c>
+      <c r="AB13" s="10" t="s">
+        <v>930</v>
+      </c>
+      <c r="AC13" s="10" t="s">
+        <v>614</v>
+      </c>
+      <c r="AD13" s="10" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="14" spans="2:30">
       <c r="B14" t="s">
         <v>475</v>
       </c>
@@ -27475,8 +27688,46 @@
       <c r="L14" t="s">
         <v>650</v>
       </c>
-    </row>
-    <row r="15" spans="2:12">
+      <c r="O14" t="s">
+        <v>479</v>
+      </c>
+      <c r="P14" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q14" t="str">
+        <f t="shared" si="0"/>
+        <v>North-Central</v>
+      </c>
+      <c r="S14" t="s">
+        <v>479</v>
+      </c>
+      <c r="T14" t="s">
+        <v>939</v>
+      </c>
+      <c r="U14" t="str">
+        <f t="shared" si="1"/>
+        <v>Abuja</v>
+      </c>
+      <c r="X14" s="10" t="s">
+        <v>923</v>
+      </c>
+      <c r="Y14" s="10" t="s">
+        <v>615</v>
+      </c>
+      <c r="Z14" s="10" t="s">
+        <v>925</v>
+      </c>
+      <c r="AB14" s="10" t="s">
+        <v>930</v>
+      </c>
+      <c r="AC14" s="10" t="s">
+        <v>615</v>
+      </c>
+      <c r="AD14" s="10" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="15" spans="2:30">
       <c r="B15" t="s">
         <v>475</v>
       </c>
@@ -27504,8 +27755,46 @@
       <c r="L15" t="s">
         <v>651</v>
       </c>
-    </row>
-    <row r="16" spans="2:12">
+      <c r="O15" t="s">
+        <v>480</v>
+      </c>
+      <c r="P15" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q15" t="str">
+        <f t="shared" si="0"/>
+        <v>North-Central</v>
+      </c>
+      <c r="S15" t="s">
+        <v>480</v>
+      </c>
+      <c r="T15" t="s">
+        <v>939</v>
+      </c>
+      <c r="U15" t="str">
+        <f t="shared" si="1"/>
+        <v>Jos</v>
+      </c>
+      <c r="X15" s="10" t="s">
+        <v>923</v>
+      </c>
+      <c r="Y15" s="10" t="s">
+        <v>616</v>
+      </c>
+      <c r="Z15" s="10" t="s">
+        <v>925</v>
+      </c>
+      <c r="AB15" s="10" t="s">
+        <v>930</v>
+      </c>
+      <c r="AC15" s="10" t="s">
+        <v>616</v>
+      </c>
+      <c r="AD15" s="10" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="16" spans="2:30">
       <c r="B16" t="s">
         <v>475</v>
       </c>
@@ -27533,8 +27822,46 @@
       <c r="L16" t="s">
         <v>652</v>
       </c>
-    </row>
-    <row r="17" spans="2:12">
+      <c r="O16" t="s">
+        <v>481</v>
+      </c>
+      <c r="P16" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q16" t="str">
+        <f t="shared" si="0"/>
+        <v>North-East</v>
+      </c>
+      <c r="S16" t="s">
+        <v>481</v>
+      </c>
+      <c r="T16" t="s">
+        <v>939</v>
+      </c>
+      <c r="U16" t="str">
+        <f t="shared" si="1"/>
+        <v>Jos</v>
+      </c>
+      <c r="X16" s="10" t="s">
+        <v>923</v>
+      </c>
+      <c r="Y16" s="10" t="s">
+        <v>617</v>
+      </c>
+      <c r="Z16" s="10" t="s">
+        <v>927</v>
+      </c>
+      <c r="AB16" s="10" t="s">
+        <v>930</v>
+      </c>
+      <c r="AC16" s="10" t="s">
+        <v>617</v>
+      </c>
+      <c r="AD16" s="10" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="17" spans="2:30">
       <c r="B17" t="s">
         <v>475</v>
       </c>
@@ -27562,8 +27889,46 @@
       <c r="L17" t="s">
         <v>653</v>
       </c>
-    </row>
-    <row r="18" spans="2:12">
+      <c r="O17" t="s">
+        <v>482</v>
+      </c>
+      <c r="P17" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q17" t="str">
+        <f t="shared" si="0"/>
+        <v>North-East</v>
+      </c>
+      <c r="S17" t="s">
+        <v>482</v>
+      </c>
+      <c r="T17" t="s">
+        <v>939</v>
+      </c>
+      <c r="U17" t="str">
+        <f t="shared" si="1"/>
+        <v>Yola</v>
+      </c>
+      <c r="X17" s="10" t="s">
+        <v>923</v>
+      </c>
+      <c r="Y17" s="10" t="s">
+        <v>618</v>
+      </c>
+      <c r="Z17" s="10" t="s">
+        <v>927</v>
+      </c>
+      <c r="AB17" s="10" t="s">
+        <v>930</v>
+      </c>
+      <c r="AC17" s="10" t="s">
+        <v>618</v>
+      </c>
+      <c r="AD17" s="10" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="18" spans="2:30">
       <c r="B18" t="s">
         <v>475</v>
       </c>
@@ -27591,8 +27956,46 @@
       <c r="L18" t="s">
         <v>654</v>
       </c>
-    </row>
-    <row r="19" spans="2:12">
+      <c r="O18" t="s">
+        <v>483</v>
+      </c>
+      <c r="P18" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q18" t="str">
+        <f t="shared" si="0"/>
+        <v>South-South</v>
+      </c>
+      <c r="S18" t="s">
+        <v>483</v>
+      </c>
+      <c r="T18" t="s">
+        <v>939</v>
+      </c>
+      <c r="U18" t="str">
+        <f t="shared" si="1"/>
+        <v>Port Harcourt</v>
+      </c>
+      <c r="X18" s="10" t="s">
+        <v>923</v>
+      </c>
+      <c r="Y18" s="10" t="s">
+        <v>619</v>
+      </c>
+      <c r="Z18" s="10" t="s">
+        <v>928</v>
+      </c>
+      <c r="AB18" s="10" t="s">
+        <v>930</v>
+      </c>
+      <c r="AC18" s="10" t="s">
+        <v>619</v>
+      </c>
+      <c r="AD18" s="10" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="19" spans="2:30">
       <c r="B19" t="s">
         <v>475</v>
       </c>
@@ -27620,8 +28023,46 @@
       <c r="L19" t="s">
         <v>655</v>
       </c>
-    </row>
-    <row r="20" spans="2:12">
+      <c r="O19" t="s">
+        <v>484</v>
+      </c>
+      <c r="P19" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q19" t="str">
+        <f t="shared" si="0"/>
+        <v>North-West</v>
+      </c>
+      <c r="S19" t="s">
+        <v>484</v>
+      </c>
+      <c r="T19" t="s">
+        <v>939</v>
+      </c>
+      <c r="U19" t="str">
+        <f t="shared" si="1"/>
+        <v>Kano</v>
+      </c>
+      <c r="X19" s="10" t="s">
+        <v>923</v>
+      </c>
+      <c r="Y19" s="10" t="s">
+        <v>620</v>
+      </c>
+      <c r="Z19" s="10" t="s">
+        <v>924</v>
+      </c>
+      <c r="AB19" s="10" t="s">
+        <v>930</v>
+      </c>
+      <c r="AC19" s="10" t="s">
+        <v>620</v>
+      </c>
+      <c r="AD19" s="10" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="20" spans="2:30">
       <c r="B20" t="s">
         <v>475</v>
       </c>
@@ -27649,8 +28090,46 @@
       <c r="L20" t="s">
         <v>656</v>
       </c>
-    </row>
-    <row r="21" spans="2:12">
+      <c r="O20" t="s">
+        <v>485</v>
+      </c>
+      <c r="P20" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q20" t="str">
+        <f t="shared" si="0"/>
+        <v>South-West</v>
+      </c>
+      <c r="S20" t="s">
+        <v>485</v>
+      </c>
+      <c r="T20" t="s">
+        <v>939</v>
+      </c>
+      <c r="U20" t="str">
+        <f t="shared" si="1"/>
+        <v>Ibadan</v>
+      </c>
+      <c r="X20" s="10" t="s">
+        <v>923</v>
+      </c>
+      <c r="Y20" s="10" t="s">
+        <v>621</v>
+      </c>
+      <c r="Z20" s="10" t="s">
+        <v>926</v>
+      </c>
+      <c r="AB20" s="10" t="s">
+        <v>930</v>
+      </c>
+      <c r="AC20" s="10" t="s">
+        <v>621</v>
+      </c>
+      <c r="AD20" s="10" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="21" spans="2:30">
       <c r="B21" t="s">
         <v>475</v>
       </c>
@@ -27678,8 +28157,46 @@
       <c r="L21" t="s">
         <v>657</v>
       </c>
-    </row>
-    <row r="22" spans="2:12">
+      <c r="O21" t="s">
+        <v>486</v>
+      </c>
+      <c r="P21" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q21" t="str">
+        <f t="shared" si="0"/>
+        <v>North-Central</v>
+      </c>
+      <c r="S21" t="s">
+        <v>486</v>
+      </c>
+      <c r="T21" t="s">
+        <v>939</v>
+      </c>
+      <c r="U21" t="str">
+        <f t="shared" si="1"/>
+        <v>Abuja</v>
+      </c>
+      <c r="X21" s="10" t="s">
+        <v>923</v>
+      </c>
+      <c r="Y21" s="10" t="s">
+        <v>622</v>
+      </c>
+      <c r="Z21" s="10" t="s">
+        <v>926</v>
+      </c>
+      <c r="AB21" s="10" t="s">
+        <v>930</v>
+      </c>
+      <c r="AC21" s="10" t="s">
+        <v>622</v>
+      </c>
+      <c r="AD21" s="10" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="22" spans="2:30">
       <c r="B22" t="s">
         <v>475</v>
       </c>
@@ -27707,8 +28224,46 @@
       <c r="L22" t="s">
         <v>658</v>
       </c>
-    </row>
-    <row r="23" spans="2:12">
+      <c r="O22" t="s">
+        <v>487</v>
+      </c>
+      <c r="P22" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q22" t="str">
+        <f t="shared" si="0"/>
+        <v>South-West</v>
+      </c>
+      <c r="S22" t="s">
+        <v>487</v>
+      </c>
+      <c r="T22" t="s">
+        <v>939</v>
+      </c>
+      <c r="U22" t="str">
+        <f t="shared" si="1"/>
+        <v>Ibadan</v>
+      </c>
+      <c r="X22" s="10" t="s">
+        <v>923</v>
+      </c>
+      <c r="Y22" s="10" t="s">
+        <v>623</v>
+      </c>
+      <c r="Z22" s="10" t="s">
+        <v>925</v>
+      </c>
+      <c r="AB22" s="10" t="s">
+        <v>930</v>
+      </c>
+      <c r="AC22" s="10" t="s">
+        <v>623</v>
+      </c>
+      <c r="AD22" s="10" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="23" spans="2:30">
       <c r="B23" t="s">
         <v>475</v>
       </c>
@@ -27736,8 +28291,46 @@
       <c r="L23" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="24" spans="2:12">
+      <c r="O23" t="s">
+        <v>488</v>
+      </c>
+      <c r="P23" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q23" t="str">
+        <f t="shared" si="0"/>
+        <v>North-Central</v>
+      </c>
+      <c r="S23" t="s">
+        <v>488</v>
+      </c>
+      <c r="T23" t="s">
+        <v>939</v>
+      </c>
+      <c r="U23" t="str">
+        <f t="shared" si="1"/>
+        <v>Ibadan</v>
+      </c>
+      <c r="X23" s="10" t="s">
+        <v>923</v>
+      </c>
+      <c r="Y23" s="10" t="s">
+        <v>624</v>
+      </c>
+      <c r="Z23" s="10" t="s">
+        <v>928</v>
+      </c>
+      <c r="AB23" s="10" t="s">
+        <v>930</v>
+      </c>
+      <c r="AC23" s="10" t="s">
+        <v>624</v>
+      </c>
+      <c r="AD23" s="10" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="24" spans="2:30">
       <c r="B24" t="s">
         <v>475</v>
       </c>
@@ -27765,8 +28358,46 @@
       <c r="L24" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="25" spans="2:12">
+      <c r="O24" t="s">
+        <v>489</v>
+      </c>
+      <c r="P24" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q24" t="str">
+        <f t="shared" si="0"/>
+        <v>South-South</v>
+      </c>
+      <c r="S24" t="s">
+        <v>489</v>
+      </c>
+      <c r="T24" t="s">
+        <v>939</v>
+      </c>
+      <c r="U24" t="str">
+        <f t="shared" si="1"/>
+        <v>Benin</v>
+      </c>
+      <c r="X24" s="10" t="s">
+        <v>923</v>
+      </c>
+      <c r="Y24" s="10" t="s">
+        <v>625</v>
+      </c>
+      <c r="Z24" s="10" t="s">
+        <v>929</v>
+      </c>
+      <c r="AB24" s="10" t="s">
+        <v>930</v>
+      </c>
+      <c r="AC24" s="10" t="s">
+        <v>625</v>
+      </c>
+      <c r="AD24" s="10" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="25" spans="2:30">
       <c r="B25" t="s">
         <v>475</v>
       </c>
@@ -27794,8 +28425,46 @@
       <c r="L25" t="s">
         <v>661</v>
       </c>
-    </row>
-    <row r="26" spans="2:12">
+      <c r="O25" t="s">
+        <v>490</v>
+      </c>
+      <c r="P25" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q25" t="str">
+        <f t="shared" si="0"/>
+        <v>South-East</v>
+      </c>
+      <c r="S25" t="s">
+        <v>490</v>
+      </c>
+      <c r="T25" t="s">
+        <v>939</v>
+      </c>
+      <c r="U25" t="str">
+        <f t="shared" si="1"/>
+        <v>Enugu</v>
+      </c>
+      <c r="X25" s="10" t="s">
+        <v>923</v>
+      </c>
+      <c r="Y25" s="10" t="s">
+        <v>626</v>
+      </c>
+      <c r="Z25" s="10" t="s">
+        <v>927</v>
+      </c>
+      <c r="AB25" s="10" t="s">
+        <v>930</v>
+      </c>
+      <c r="AC25" s="10" t="s">
+        <v>626</v>
+      </c>
+      <c r="AD25" s="10" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="26" spans="2:30">
       <c r="B26" t="s">
         <v>475</v>
       </c>
@@ -27823,8 +28492,46 @@
       <c r="L26" t="s">
         <v>662</v>
       </c>
-    </row>
-    <row r="27" spans="2:12">
+      <c r="O26" t="s">
+        <v>491</v>
+      </c>
+      <c r="P26" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q26" t="str">
+        <f t="shared" si="0"/>
+        <v>North-Central</v>
+      </c>
+      <c r="S26" t="s">
+        <v>491</v>
+      </c>
+      <c r="T26" t="s">
+        <v>939</v>
+      </c>
+      <c r="U26" t="str">
+        <f t="shared" si="1"/>
+        <v>Abuja</v>
+      </c>
+      <c r="X26" s="10" t="s">
+        <v>923</v>
+      </c>
+      <c r="Y26" s="10" t="s">
+        <v>627</v>
+      </c>
+      <c r="Z26" s="10" t="s">
+        <v>929</v>
+      </c>
+      <c r="AB26" s="10" t="s">
+        <v>930</v>
+      </c>
+      <c r="AC26" s="10" t="s">
+        <v>627</v>
+      </c>
+      <c r="AD26" s="10" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="27" spans="2:30">
       <c r="B27" t="s">
         <v>475</v>
       </c>
@@ -27852,8 +28559,46 @@
       <c r="L27" t="s">
         <v>663</v>
       </c>
-    </row>
-    <row r="28" spans="2:12">
+      <c r="O27" t="s">
+        <v>492</v>
+      </c>
+      <c r="P27" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q27" t="str">
+        <f t="shared" si="0"/>
+        <v>South-West</v>
+      </c>
+      <c r="S27" t="s">
+        <v>492</v>
+      </c>
+      <c r="T27" t="s">
+        <v>939</v>
+      </c>
+      <c r="U27" t="str">
+        <f t="shared" si="1"/>
+        <v>Ikeja</v>
+      </c>
+      <c r="X27" s="10" t="s">
+        <v>923</v>
+      </c>
+      <c r="Y27" s="10" t="s">
+        <v>628</v>
+      </c>
+      <c r="Z27" s="10" t="s">
+        <v>924</v>
+      </c>
+      <c r="AB27" s="10" t="s">
+        <v>930</v>
+      </c>
+      <c r="AC27" s="10" t="s">
+        <v>628</v>
+      </c>
+      <c r="AD27" s="10" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="28" spans="2:30">
       <c r="B28" t="s">
         <v>475</v>
       </c>
@@ -27881,8 +28626,46 @@
       <c r="L28" t="s">
         <v>664</v>
       </c>
-    </row>
-    <row r="29" spans="2:12">
+      <c r="O28" t="s">
+        <v>493</v>
+      </c>
+      <c r="P28" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q28" t="str">
+        <f t="shared" si="0"/>
+        <v>North-Central</v>
+      </c>
+      <c r="S28" t="s">
+        <v>493</v>
+      </c>
+      <c r="T28" t="s">
+        <v>939</v>
+      </c>
+      <c r="U28" t="str">
+        <f t="shared" si="1"/>
+        <v>Abuja</v>
+      </c>
+      <c r="X28" s="10" t="s">
+        <v>923</v>
+      </c>
+      <c r="Y28" s="10" t="s">
+        <v>629</v>
+      </c>
+      <c r="Z28" s="10" t="s">
+        <v>928</v>
+      </c>
+      <c r="AB28" s="10" t="s">
+        <v>930</v>
+      </c>
+      <c r="AC28" s="10" t="s">
+        <v>629</v>
+      </c>
+      <c r="AD28" s="10" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="29" spans="2:30">
       <c r="B29" t="s">
         <v>475</v>
       </c>
@@ -27910,8 +28693,46 @@
       <c r="L29" t="s">
         <v>665</v>
       </c>
-    </row>
-    <row r="30" spans="2:12">
+      <c r="O29" t="s">
+        <v>494</v>
+      </c>
+      <c r="P29" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q29" t="str">
+        <f t="shared" si="0"/>
+        <v>North-East</v>
+      </c>
+      <c r="S29" t="s">
+        <v>494</v>
+      </c>
+      <c r="T29" t="s">
+        <v>939</v>
+      </c>
+      <c r="U29" t="str">
+        <f t="shared" si="1"/>
+        <v>Yola</v>
+      </c>
+      <c r="X29" s="10" t="s">
+        <v>923</v>
+      </c>
+      <c r="Y29" s="10" t="s">
+        <v>630</v>
+      </c>
+      <c r="Z29" s="10" t="s">
+        <v>926</v>
+      </c>
+      <c r="AB29" s="10" t="s">
+        <v>930</v>
+      </c>
+      <c r="AC29" s="10" t="s">
+        <v>630</v>
+      </c>
+      <c r="AD29" s="10" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="30" spans="2:30">
       <c r="B30" t="s">
         <v>475</v>
       </c>
@@ -27939,8 +28760,46 @@
       <c r="L30" t="s">
         <v>666</v>
       </c>
-    </row>
-    <row r="31" spans="2:12">
+      <c r="O30" t="s">
+        <v>495</v>
+      </c>
+      <c r="P30" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q30" t="str">
+        <f t="shared" si="0"/>
+        <v>South-East</v>
+      </c>
+      <c r="S30" t="s">
+        <v>495</v>
+      </c>
+      <c r="T30" t="s">
+        <v>939</v>
+      </c>
+      <c r="U30" t="str">
+        <f t="shared" si="1"/>
+        <v>Enugu</v>
+      </c>
+      <c r="X30" s="10" t="s">
+        <v>923</v>
+      </c>
+      <c r="Y30" s="10" t="s">
+        <v>631</v>
+      </c>
+      <c r="Z30" s="10" t="s">
+        <v>928</v>
+      </c>
+      <c r="AB30" s="10" t="s">
+        <v>930</v>
+      </c>
+      <c r="AC30" s="10" t="s">
+        <v>631</v>
+      </c>
+      <c r="AD30" s="10" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="31" spans="2:30">
       <c r="B31" t="s">
         <v>475</v>
       </c>
@@ -27968,8 +28827,46 @@
       <c r="L31" t="s">
         <v>667</v>
       </c>
-    </row>
-    <row r="32" spans="2:12">
+      <c r="O31" t="s">
+        <v>496</v>
+      </c>
+      <c r="P31" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q31" t="str">
+        <f t="shared" si="0"/>
+        <v>North-West</v>
+      </c>
+      <c r="S31" t="s">
+        <v>496</v>
+      </c>
+      <c r="T31" t="s">
+        <v>939</v>
+      </c>
+      <c r="U31" t="str">
+        <f t="shared" si="1"/>
+        <v>Kaduna</v>
+      </c>
+      <c r="X31" s="10" t="s">
+        <v>923</v>
+      </c>
+      <c r="Y31" s="10" t="s">
+        <v>632</v>
+      </c>
+      <c r="Z31" s="10" t="s">
+        <v>925</v>
+      </c>
+      <c r="AB31" s="10" t="s">
+        <v>930</v>
+      </c>
+      <c r="AC31" s="10" t="s">
+        <v>632</v>
+      </c>
+      <c r="AD31" s="10" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="32" spans="2:30">
       <c r="B32" t="s">
         <v>475</v>
       </c>
@@ -27997,8 +28894,46 @@
       <c r="L32" t="s">
         <v>668</v>
       </c>
-    </row>
-    <row r="33" spans="2:12">
+      <c r="O32" t="s">
+        <v>497</v>
+      </c>
+      <c r="P32" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q32" t="str">
+        <f t="shared" si="0"/>
+        <v>South-South</v>
+      </c>
+      <c r="S32" t="s">
+        <v>497</v>
+      </c>
+      <c r="T32" t="s">
+        <v>939</v>
+      </c>
+      <c r="U32" t="str">
+        <f t="shared" si="1"/>
+        <v>Port Harcourt</v>
+      </c>
+      <c r="X32" s="10" t="s">
+        <v>923</v>
+      </c>
+      <c r="Y32" s="10" t="s">
+        <v>633</v>
+      </c>
+      <c r="Z32" s="10" t="s">
+        <v>925</v>
+      </c>
+      <c r="AB32" s="10" t="s">
+        <v>930</v>
+      </c>
+      <c r="AC32" s="10" t="s">
+        <v>633</v>
+      </c>
+      <c r="AD32" s="10" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="33" spans="2:30">
       <c r="B33" t="s">
         <v>475</v>
       </c>
@@ -28026,8 +28961,46 @@
       <c r="L33" t="s">
         <v>669</v>
       </c>
-    </row>
-    <row r="34" spans="2:12">
+      <c r="O33" t="s">
+        <v>498</v>
+      </c>
+      <c r="P33" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q33" t="str">
+        <f t="shared" si="0"/>
+        <v>South-South</v>
+      </c>
+      <c r="S33" t="s">
+        <v>498</v>
+      </c>
+      <c r="T33" t="s">
+        <v>939</v>
+      </c>
+      <c r="U33" t="str">
+        <f t="shared" si="1"/>
+        <v>Port Harcourt</v>
+      </c>
+      <c r="X33" s="10" t="s">
+        <v>923</v>
+      </c>
+      <c r="Y33" s="10" t="s">
+        <v>634</v>
+      </c>
+      <c r="Z33" s="10" t="s">
+        <v>926</v>
+      </c>
+      <c r="AB33" s="10" t="s">
+        <v>930</v>
+      </c>
+      <c r="AC33" s="10" t="s">
+        <v>634</v>
+      </c>
+      <c r="AD33" s="10" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="34" spans="2:30">
       <c r="B34" t="s">
         <v>475</v>
       </c>
@@ -28055,8 +29028,46 @@
       <c r="L34" t="s">
         <v>670</v>
       </c>
-    </row>
-    <row r="35" spans="2:12">
+      <c r="O34" t="s">
+        <v>499</v>
+      </c>
+      <c r="P34" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q34" t="str">
+        <f t="shared" si="0"/>
+        <v>South-West</v>
+      </c>
+      <c r="S34" t="s">
+        <v>499</v>
+      </c>
+      <c r="T34" t="s">
+        <v>939</v>
+      </c>
+      <c r="U34" t="str">
+        <f t="shared" si="1"/>
+        <v>Ibadan</v>
+      </c>
+      <c r="X34" s="10" t="s">
+        <v>923</v>
+      </c>
+      <c r="Y34" s="10" t="s">
+        <v>635</v>
+      </c>
+      <c r="Z34" s="10" t="s">
+        <v>927</v>
+      </c>
+      <c r="AB34" s="10" t="s">
+        <v>930</v>
+      </c>
+      <c r="AC34" s="10" t="s">
+        <v>635</v>
+      </c>
+      <c r="AD34" s="10" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30">
       <c r="B35" t="s">
         <v>475</v>
       </c>
@@ -28084,8 +29095,46 @@
       <c r="L35" t="s">
         <v>671</v>
       </c>
-    </row>
-    <row r="36" spans="2:12">
+      <c r="O35" t="s">
+        <v>500</v>
+      </c>
+      <c r="P35" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q35" t="str">
+        <f t="shared" si="0"/>
+        <v>South-South</v>
+      </c>
+      <c r="S35" t="s">
+        <v>500</v>
+      </c>
+      <c r="T35" t="s">
+        <v>939</v>
+      </c>
+      <c r="U35" t="str">
+        <f t="shared" si="1"/>
+        <v>Benin</v>
+      </c>
+      <c r="X35" s="10" t="s">
+        <v>923</v>
+      </c>
+      <c r="Y35" s="10" t="s">
+        <v>636</v>
+      </c>
+      <c r="Z35" s="10" t="s">
+        <v>929</v>
+      </c>
+      <c r="AB35" s="10" t="s">
+        <v>930</v>
+      </c>
+      <c r="AC35" s="10" t="s">
+        <v>636</v>
+      </c>
+      <c r="AD35" s="10" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="36" spans="2:30">
       <c r="B36" t="s">
         <v>475</v>
       </c>
@@ -28113,8 +29162,46 @@
       <c r="L36" t="s">
         <v>672</v>
       </c>
-    </row>
-    <row r="37" spans="2:12">
+      <c r="O36" t="s">
+        <v>501</v>
+      </c>
+      <c r="P36" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q36" t="str">
+        <f t="shared" si="0"/>
+        <v>South-West</v>
+      </c>
+      <c r="S36" t="s">
+        <v>501</v>
+      </c>
+      <c r="T36" t="s">
+        <v>939</v>
+      </c>
+      <c r="U36" t="str">
+        <f t="shared" si="1"/>
+        <v>Ibadan</v>
+      </c>
+      <c r="X36" s="10" t="s">
+        <v>923</v>
+      </c>
+      <c r="Y36" s="10" t="s">
+        <v>637</v>
+      </c>
+      <c r="Z36" s="10" t="s">
+        <v>928</v>
+      </c>
+      <c r="AB36" s="10" t="s">
+        <v>930</v>
+      </c>
+      <c r="AC36" s="10" t="s">
+        <v>637</v>
+      </c>
+      <c r="AD36" s="10" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="37" spans="2:30">
       <c r="B37" t="s">
         <v>475</v>
       </c>
@@ -28142,8 +29229,46 @@
       <c r="L37" t="s">
         <v>673</v>
       </c>
-    </row>
-    <row r="38" spans="2:12">
+      <c r="O37" t="s">
+        <v>502</v>
+      </c>
+      <c r="P37" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q37" t="str">
+        <f t="shared" si="0"/>
+        <v>North-Central</v>
+      </c>
+      <c r="S37" t="s">
+        <v>502</v>
+      </c>
+      <c r="T37" t="s">
+        <v>939</v>
+      </c>
+      <c r="U37" t="str">
+        <f t="shared" si="1"/>
+        <v>Jos</v>
+      </c>
+      <c r="X37" s="10" t="s">
+        <v>923</v>
+      </c>
+      <c r="Y37" s="10" t="s">
+        <v>638</v>
+      </c>
+      <c r="Z37" s="10" t="s">
+        <v>924</v>
+      </c>
+      <c r="AB37" s="10" t="s">
+        <v>930</v>
+      </c>
+      <c r="AC37" s="10" t="s">
+        <v>638</v>
+      </c>
+      <c r="AD37" s="10" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="38" spans="2:30">
       <c r="B38" t="s">
         <v>475</v>
       </c>
@@ -28171,8 +29296,46 @@
       <c r="L38" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="39" spans="2:12">
+      <c r="O38" t="s">
+        <v>503</v>
+      </c>
+      <c r="P38" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q38" t="str">
+        <f t="shared" si="0"/>
+        <v>North-Central</v>
+      </c>
+      <c r="S38" t="s">
+        <v>503</v>
+      </c>
+      <c r="T38" t="s">
+        <v>939</v>
+      </c>
+      <c r="U38" t="str">
+        <f t="shared" si="1"/>
+        <v>Abuja</v>
+      </c>
+      <c r="X38" s="10" t="s">
+        <v>923</v>
+      </c>
+      <c r="Y38" s="10" t="s">
+        <v>639</v>
+      </c>
+      <c r="Z38" s="10" t="s">
+        <v>927</v>
+      </c>
+      <c r="AB38" s="10" t="s">
+        <v>930</v>
+      </c>
+      <c r="AC38" s="10" t="s">
+        <v>639</v>
+      </c>
+      <c r="AD38" s="10" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="39" spans="2:30">
       <c r="B39" t="s">
         <v>475</v>
       </c>
@@ -28200,8 +29363,46 @@
       <c r="L39" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="40" spans="2:12">
+      <c r="O39" t="s">
+        <v>504</v>
+      </c>
+      <c r="P39" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q39" t="str">
+        <f t="shared" si="0"/>
+        <v>North-Central</v>
+      </c>
+      <c r="S39" t="s">
+        <v>504</v>
+      </c>
+      <c r="T39" t="s">
+        <v>939</v>
+      </c>
+      <c r="U39" t="str">
+        <f t="shared" si="1"/>
+        <v>Abuja</v>
+      </c>
+      <c r="X39" s="10" t="s">
+        <v>923</v>
+      </c>
+      <c r="Y39" s="10" t="s">
+        <v>640</v>
+      </c>
+      <c r="Z39" s="10" t="s">
+        <v>925</v>
+      </c>
+      <c r="AB39" s="10" t="s">
+        <v>930</v>
+      </c>
+      <c r="AC39" s="10" t="s">
+        <v>640</v>
+      </c>
+      <c r="AD39" s="10" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="40" spans="2:30">
       <c r="B40" t="s">
         <v>475</v>
       </c>
@@ -28229,8 +29430,46 @@
       <c r="L40" t="s">
         <v>676</v>
       </c>
-    </row>
-    <row r="41" spans="2:12">
+      <c r="O40" t="s">
+        <v>505</v>
+      </c>
+      <c r="P40" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q40" t="str">
+        <f t="shared" si="0"/>
+        <v>South-West</v>
+      </c>
+      <c r="S40" t="s">
+        <v>505</v>
+      </c>
+      <c r="T40" t="s">
+        <v>939</v>
+      </c>
+      <c r="U40" t="str">
+        <f t="shared" si="1"/>
+        <v>Benin</v>
+      </c>
+      <c r="X40" s="10" t="s">
+        <v>923</v>
+      </c>
+      <c r="Y40" s="10" t="s">
+        <v>641</v>
+      </c>
+      <c r="Z40" s="10" t="s">
+        <v>927</v>
+      </c>
+      <c r="AB40" s="10" t="s">
+        <v>930</v>
+      </c>
+      <c r="AC40" s="10" t="s">
+        <v>641</v>
+      </c>
+      <c r="AD40" s="10" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="41" spans="2:30">
       <c r="B41" t="s">
         <v>475</v>
       </c>
@@ -28258,8 +29497,46 @@
       <c r="L41" t="s">
         <v>677</v>
       </c>
-    </row>
-    <row r="42" spans="2:12">
+      <c r="O41" t="s">
+        <v>506</v>
+      </c>
+      <c r="P41" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q41" t="str">
+        <f t="shared" si="0"/>
+        <v>South-South</v>
+      </c>
+      <c r="S41" t="s">
+        <v>506</v>
+      </c>
+      <c r="T41" t="s">
+        <v>939</v>
+      </c>
+      <c r="U41" t="str">
+        <f t="shared" si="1"/>
+        <v>Benin</v>
+      </c>
+      <c r="X41" s="10" t="s">
+        <v>923</v>
+      </c>
+      <c r="Y41" s="10" t="s">
+        <v>642</v>
+      </c>
+      <c r="Z41" s="10" t="s">
+        <v>924</v>
+      </c>
+      <c r="AB41" s="10" t="s">
+        <v>930</v>
+      </c>
+      <c r="AC41" s="10" t="s">
+        <v>642</v>
+      </c>
+      <c r="AD41" s="10" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="42" spans="2:30">
       <c r="B42" t="s">
         <v>475</v>
       </c>
@@ -28287,8 +29564,46 @@
       <c r="L42" t="s">
         <v>678</v>
       </c>
-    </row>
-    <row r="43" spans="2:12">
+      <c r="O42" t="s">
+        <v>507</v>
+      </c>
+      <c r="P42" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q42" t="str">
+        <f t="shared" si="0"/>
+        <v>South-South</v>
+      </c>
+      <c r="S42" t="s">
+        <v>507</v>
+      </c>
+      <c r="T42" t="s">
+        <v>939</v>
+      </c>
+      <c r="U42" t="str">
+        <f t="shared" si="1"/>
+        <v>Benin</v>
+      </c>
+      <c r="X42" s="10" t="s">
+        <v>923</v>
+      </c>
+      <c r="Y42" s="10" t="s">
+        <v>643</v>
+      </c>
+      <c r="Z42" s="10" t="s">
+        <v>924</v>
+      </c>
+      <c r="AB42" s="10" t="s">
+        <v>930</v>
+      </c>
+      <c r="AC42" s="10" t="s">
+        <v>643</v>
+      </c>
+      <c r="AD42" s="10" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30">
       <c r="B43" t="s">
         <v>475</v>
       </c>
@@ -28316,8 +29631,46 @@
       <c r="L43" t="s">
         <v>679</v>
       </c>
-    </row>
-    <row r="44" spans="2:12">
+      <c r="O43" t="s">
+        <v>508</v>
+      </c>
+      <c r="P43" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q43" t="str">
+        <f t="shared" si="0"/>
+        <v>North-East</v>
+      </c>
+      <c r="S43" t="s">
+        <v>508</v>
+      </c>
+      <c r="T43" t="s">
+        <v>939</v>
+      </c>
+      <c r="U43" t="str">
+        <f t="shared" si="1"/>
+        <v>Yola</v>
+      </c>
+      <c r="X43" s="10" t="s">
+        <v>923</v>
+      </c>
+      <c r="Y43" s="10" t="s">
+        <v>644</v>
+      </c>
+      <c r="Z43" s="10" t="s">
+        <v>644</v>
+      </c>
+      <c r="AB43" s="10" t="s">
+        <v>930</v>
+      </c>
+      <c r="AC43" s="10" t="s">
+        <v>644</v>
+      </c>
+      <c r="AD43" s="10" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30">
       <c r="B44" t="s">
         <v>475</v>
       </c>
@@ -28345,8 +29698,46 @@
       <c r="L44" t="s">
         <v>680</v>
       </c>
-    </row>
-    <row r="45" spans="2:12">
+      <c r="O44" t="s">
+        <v>509</v>
+      </c>
+      <c r="P44" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q44" t="str">
+        <f t="shared" si="0"/>
+        <v>South-West</v>
+      </c>
+      <c r="S44" t="s">
+        <v>509</v>
+      </c>
+      <c r="T44" t="s">
+        <v>939</v>
+      </c>
+      <c r="U44" t="str">
+        <f t="shared" si="1"/>
+        <v>Ikeja</v>
+      </c>
+      <c r="X44" s="10" t="s">
+        <v>923</v>
+      </c>
+      <c r="Y44" s="10" t="s">
+        <v>645</v>
+      </c>
+      <c r="Z44" s="10" t="s">
+        <v>924</v>
+      </c>
+      <c r="AB44" s="10" t="s">
+        <v>930</v>
+      </c>
+      <c r="AC44" s="10" t="s">
+        <v>645</v>
+      </c>
+      <c r="AD44" s="10" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30">
       <c r="B45" t="s">
         <v>475</v>
       </c>
@@ -28374,8 +29765,28 @@
       <c r="L45" t="s">
         <v>681</v>
       </c>
-    </row>
-    <row r="46" spans="2:12">
+      <c r="O45" t="s">
+        <v>510</v>
+      </c>
+      <c r="P45" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q45" t="str">
+        <f t="shared" si="0"/>
+        <v>South-East</v>
+      </c>
+      <c r="S45" t="s">
+        <v>510</v>
+      </c>
+      <c r="T45" t="s">
+        <v>939</v>
+      </c>
+      <c r="U45" t="str">
+        <f t="shared" si="1"/>
+        <v>Enugu</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30">
       <c r="B46" t="s">
         <v>475</v>
       </c>
@@ -28403,8 +29814,28 @@
       <c r="L46" t="s">
         <v>682</v>
       </c>
-    </row>
-    <row r="47" spans="2:12">
+      <c r="O46" t="s">
+        <v>511</v>
+      </c>
+      <c r="P46" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q46" t="str">
+        <f t="shared" si="0"/>
+        <v>South-West</v>
+      </c>
+      <c r="S46" t="s">
+        <v>511</v>
+      </c>
+      <c r="T46" t="s">
+        <v>939</v>
+      </c>
+      <c r="U46" t="str">
+        <f t="shared" si="1"/>
+        <v>Ikeja</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30">
       <c r="B47" t="s">
         <v>475</v>
       </c>
@@ -28432,8 +29863,28 @@
       <c r="L47" t="s">
         <v>683</v>
       </c>
-    </row>
-    <row r="48" spans="2:12">
+      <c r="O47" t="s">
+        <v>512</v>
+      </c>
+      <c r="P47" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q47" t="str">
+        <f t="shared" si="0"/>
+        <v>South-South</v>
+      </c>
+      <c r="S47" t="s">
+        <v>512</v>
+      </c>
+      <c r="T47" t="s">
+        <v>939</v>
+      </c>
+      <c r="U47" t="str">
+        <f t="shared" si="1"/>
+        <v>Port Harcourt</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30">
       <c r="B48" t="s">
         <v>475</v>
       </c>
@@ -28461,8 +29912,28 @@
       <c r="L48" t="s">
         <v>684</v>
       </c>
-    </row>
-    <row r="49" spans="2:12">
+      <c r="O48" t="s">
+        <v>513</v>
+      </c>
+      <c r="P48" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q48" t="str">
+        <f t="shared" si="0"/>
+        <v>South-South</v>
+      </c>
+      <c r="S48" t="s">
+        <v>513</v>
+      </c>
+      <c r="T48" t="s">
+        <v>939</v>
+      </c>
+      <c r="U48" t="str">
+        <f t="shared" si="1"/>
+        <v>Benin</v>
+      </c>
+    </row>
+    <row r="49" spans="2:21">
       <c r="B49" t="s">
         <v>475</v>
       </c>
@@ -28490,8 +29961,28 @@
       <c r="L49" t="s">
         <v>685</v>
       </c>
-    </row>
-    <row r="50" spans="2:12">
+      <c r="O49" t="s">
+        <v>514</v>
+      </c>
+      <c r="P49" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q49" t="str">
+        <f t="shared" si="0"/>
+        <v>North-West</v>
+      </c>
+      <c r="S49" t="s">
+        <v>514</v>
+      </c>
+      <c r="T49" t="s">
+        <v>939</v>
+      </c>
+      <c r="U49" t="str">
+        <f t="shared" si="1"/>
+        <v>Kano</v>
+      </c>
+    </row>
+    <row r="50" spans="2:21">
       <c r="B50" t="s">
         <v>475</v>
       </c>
@@ -28519,8 +30010,28 @@
       <c r="L50" t="s">
         <v>686</v>
       </c>
-    </row>
-    <row r="51" spans="2:12">
+      <c r="O50" t="s">
+        <v>515</v>
+      </c>
+      <c r="P50" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q50" t="str">
+        <f t="shared" si="0"/>
+        <v>South-West</v>
+      </c>
+      <c r="S50" t="s">
+        <v>515</v>
+      </c>
+      <c r="T50" t="s">
+        <v>939</v>
+      </c>
+      <c r="U50" t="str">
+        <f t="shared" si="1"/>
+        <v>Ibadan</v>
+      </c>
+    </row>
+    <row r="51" spans="2:21">
       <c r="B51" t="s">
         <v>475</v>
       </c>
@@ -28548,8 +30059,28 @@
       <c r="L51" t="s">
         <v>687</v>
       </c>
-    </row>
-    <row r="52" spans="2:12">
+      <c r="O51" t="s">
+        <v>516</v>
+      </c>
+      <c r="P51" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q51" t="str">
+        <f t="shared" si="0"/>
+        <v>North-Central</v>
+      </c>
+      <c r="S51" t="s">
+        <v>516</v>
+      </c>
+      <c r="T51" t="s">
+        <v>939</v>
+      </c>
+      <c r="U51" t="str">
+        <f t="shared" si="1"/>
+        <v>Ibadan</v>
+      </c>
+    </row>
+    <row r="52" spans="2:21">
       <c r="B52" t="s">
         <v>475</v>
       </c>
@@ -28577,8 +30108,28 @@
       <c r="L52" t="s">
         <v>688</v>
       </c>
-    </row>
-    <row r="53" spans="2:12">
+      <c r="O52" t="s">
+        <v>517</v>
+      </c>
+      <c r="P52" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q52" t="str">
+        <f t="shared" si="0"/>
+        <v>South-South</v>
+      </c>
+      <c r="S52" t="s">
+        <v>517</v>
+      </c>
+      <c r="T52" t="s">
+        <v>939</v>
+      </c>
+      <c r="U52" t="str">
+        <f t="shared" si="1"/>
+        <v>Port Harcourt</v>
+      </c>
+    </row>
+    <row r="53" spans="2:21">
       <c r="B53" t="s">
         <v>475</v>
       </c>
@@ -28606,8 +30157,28 @@
       <c r="L53" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="54" spans="2:12">
+      <c r="O53" t="s">
+        <v>518</v>
+      </c>
+      <c r="P53" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q53" t="str">
+        <f t="shared" si="0"/>
+        <v>South-South</v>
+      </c>
+      <c r="S53" t="s">
+        <v>518</v>
+      </c>
+      <c r="T53" t="s">
+        <v>939</v>
+      </c>
+      <c r="U53" t="str">
+        <f t="shared" si="1"/>
+        <v>Benin</v>
+      </c>
+    </row>
+    <row r="54" spans="2:21">
       <c r="B54" t="s">
         <v>475</v>
       </c>
@@ -28635,8 +30206,28 @@
       <c r="L54" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="55" spans="2:12">
+      <c r="O54" t="s">
+        <v>519</v>
+      </c>
+      <c r="P54" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q54" t="str">
+        <f t="shared" si="0"/>
+        <v>North-Central</v>
+      </c>
+      <c r="S54" t="s">
+        <v>519</v>
+      </c>
+      <c r="T54" t="s">
+        <v>939</v>
+      </c>
+      <c r="U54" t="str">
+        <f t="shared" si="1"/>
+        <v>Ibadan</v>
+      </c>
+    </row>
+    <row r="55" spans="2:21">
       <c r="B55" t="s">
         <v>475</v>
       </c>
@@ -28664,8 +30255,28 @@
       <c r="L55" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="56" spans="2:12">
+      <c r="O55" t="s">
+        <v>520</v>
+      </c>
+      <c r="P55" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q55" t="str">
+        <f t="shared" si="0"/>
+        <v>South-East</v>
+      </c>
+      <c r="S55" t="s">
+        <v>520</v>
+      </c>
+      <c r="T55" t="s">
+        <v>939</v>
+      </c>
+      <c r="U55" t="str">
+        <f t="shared" si="1"/>
+        <v>Enugu</v>
+      </c>
+    </row>
+    <row r="56" spans="2:21">
       <c r="B56" t="s">
         <v>475</v>
       </c>
@@ -28693,8 +30304,28 @@
       <c r="L56" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="57" spans="2:12">
+      <c r="O56" t="s">
+        <v>521</v>
+      </c>
+      <c r="P56" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q56" t="str">
+        <f t="shared" si="0"/>
+        <v>North-Central</v>
+      </c>
+      <c r="S56" t="s">
+        <v>521</v>
+      </c>
+      <c r="T56" t="s">
+        <v>939</v>
+      </c>
+      <c r="U56" t="str">
+        <f t="shared" si="1"/>
+        <v>Abuja</v>
+      </c>
+    </row>
+    <row r="57" spans="2:21">
       <c r="B57" t="s">
         <v>475</v>
       </c>
@@ -28722,8 +30353,28 @@
       <c r="L57" t="s">
         <v>693</v>
       </c>
-    </row>
-    <row r="58" spans="2:12">
+      <c r="O57" t="s">
+        <v>522</v>
+      </c>
+      <c r="P57" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q57" t="str">
+        <f t="shared" si="0"/>
+        <v>South-South</v>
+      </c>
+      <c r="S57" t="s">
+        <v>522</v>
+      </c>
+      <c r="T57" t="s">
+        <v>939</v>
+      </c>
+      <c r="U57" t="str">
+        <f t="shared" si="1"/>
+        <v>Benin</v>
+      </c>
+    </row>
+    <row r="58" spans="2:21">
       <c r="B58" t="s">
         <v>475</v>
       </c>
@@ -28751,8 +30402,28 @@
       <c r="L58" t="s">
         <v>694</v>
       </c>
-    </row>
-    <row r="59" spans="2:12">
+      <c r="O58" t="s">
+        <v>523</v>
+      </c>
+      <c r="P58" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q58" t="str">
+        <f t="shared" si="0"/>
+        <v>North-Central</v>
+      </c>
+      <c r="S58" t="s">
+        <v>523</v>
+      </c>
+      <c r="T58" t="s">
+        <v>939</v>
+      </c>
+      <c r="U58" t="str">
+        <f t="shared" si="1"/>
+        <v>Abuja</v>
+      </c>
+    </row>
+    <row r="59" spans="2:21">
       <c r="B59" t="s">
         <v>475</v>
       </c>
@@ -28780,8 +30451,28 @@
       <c r="L59" t="s">
         <v>695</v>
       </c>
-    </row>
-    <row r="60" spans="2:12">
+      <c r="O59" t="s">
+        <v>524</v>
+      </c>
+      <c r="P59" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q59" t="str">
+        <f t="shared" si="0"/>
+        <v>South-West</v>
+      </c>
+      <c r="S59" t="s">
+        <v>524</v>
+      </c>
+      <c r="T59" t="s">
+        <v>939</v>
+      </c>
+      <c r="U59" t="str">
+        <f t="shared" si="1"/>
+        <v>Ibadan</v>
+      </c>
+    </row>
+    <row r="60" spans="2:21">
       <c r="B60" t="s">
         <v>475</v>
       </c>
@@ -28809,8 +30500,28 @@
       <c r="L60" t="s">
         <v>696</v>
       </c>
-    </row>
-    <row r="61" spans="2:12">
+      <c r="O60" t="s">
+        <v>525</v>
+      </c>
+      <c r="P60" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q60" t="str">
+        <f t="shared" si="0"/>
+        <v>South-South</v>
+      </c>
+      <c r="S60" t="s">
+        <v>525</v>
+      </c>
+      <c r="T60" t="s">
+        <v>939</v>
+      </c>
+      <c r="U60" t="str">
+        <f t="shared" si="1"/>
+        <v>Benin</v>
+      </c>
+    </row>
+    <row r="61" spans="2:21">
       <c r="B61" t="s">
         <v>475</v>
       </c>
@@ -28838,8 +30549,28 @@
       <c r="L61" t="s">
         <v>697</v>
       </c>
-    </row>
-    <row r="62" spans="2:12">
+      <c r="O61" t="s">
+        <v>526</v>
+      </c>
+      <c r="P61" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q61" t="str">
+        <f t="shared" si="0"/>
+        <v>South-South</v>
+      </c>
+      <c r="S61" t="s">
+        <v>526</v>
+      </c>
+      <c r="T61" t="s">
+        <v>939</v>
+      </c>
+      <c r="U61" t="str">
+        <f t="shared" si="1"/>
+        <v>Benin</v>
+      </c>
+    </row>
+    <row r="62" spans="2:21">
       <c r="B62" t="s">
         <v>475</v>
       </c>
@@ -28867,8 +30598,28 @@
       <c r="L62" t="s">
         <v>698</v>
       </c>
-    </row>
-    <row r="63" spans="2:12">
+      <c r="O62" t="s">
+        <v>527</v>
+      </c>
+      <c r="P62" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q62" t="str">
+        <f t="shared" si="0"/>
+        <v>South-South</v>
+      </c>
+      <c r="S62" t="s">
+        <v>527</v>
+      </c>
+      <c r="T62" t="s">
+        <v>939</v>
+      </c>
+      <c r="U62" t="str">
+        <f t="shared" si="1"/>
+        <v>Benin</v>
+      </c>
+    </row>
+    <row r="63" spans="2:21">
       <c r="B63" t="s">
         <v>475</v>
       </c>
@@ -28896,8 +30647,28 @@
       <c r="L63" t="s">
         <v>699</v>
       </c>
-    </row>
-    <row r="64" spans="2:12">
+      <c r="O63" t="s">
+        <v>528</v>
+      </c>
+      <c r="P63" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q63" t="str">
+        <f t="shared" si="0"/>
+        <v>North-West</v>
+      </c>
+      <c r="S63" t="s">
+        <v>528</v>
+      </c>
+      <c r="T63" t="s">
+        <v>939</v>
+      </c>
+      <c r="U63" t="str">
+        <f t="shared" si="1"/>
+        <v>Kano</v>
+      </c>
+    </row>
+    <row r="64" spans="2:21">
       <c r="B64" t="s">
         <v>475</v>
       </c>
@@ -28925,8 +30696,28 @@
       <c r="L64" t="s">
         <v>700</v>
       </c>
-    </row>
-    <row r="65" spans="2:12">
+      <c r="O64" t="s">
+        <v>529</v>
+      </c>
+      <c r="P64" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q64" t="str">
+        <f t="shared" si="0"/>
+        <v>North-West</v>
+      </c>
+      <c r="S64" t="s">
+        <v>529</v>
+      </c>
+      <c r="T64" t="s">
+        <v>939</v>
+      </c>
+      <c r="U64" t="str">
+        <f t="shared" si="1"/>
+        <v>Kano</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21">
       <c r="B65" t="s">
         <v>475</v>
       </c>
@@ -28954,8 +30745,28 @@
       <c r="L65" t="s">
         <v>701</v>
       </c>
-    </row>
-    <row r="66" spans="2:12">
+      <c r="O65" t="s">
+        <v>530</v>
+      </c>
+      <c r="P65" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q65" t="str">
+        <f t="shared" si="0"/>
+        <v>North-Central</v>
+      </c>
+      <c r="S65" t="s">
+        <v>530</v>
+      </c>
+      <c r="T65" t="s">
+        <v>939</v>
+      </c>
+      <c r="U65" t="str">
+        <f t="shared" si="1"/>
+        <v>Abuja</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21">
       <c r="B66" t="s">
         <v>475</v>
       </c>
@@ -28983,8 +30794,28 @@
       <c r="L66" t="s">
         <v>702</v>
       </c>
-    </row>
-    <row r="67" spans="2:12">
+      <c r="O66" t="s">
+        <v>531</v>
+      </c>
+      <c r="P66" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q66" t="str">
+        <f t="shared" si="0"/>
+        <v>South-West</v>
+      </c>
+      <c r="S66" t="s">
+        <v>531</v>
+      </c>
+      <c r="T66" t="s">
+        <v>939</v>
+      </c>
+      <c r="U66" t="str">
+        <f t="shared" si="1"/>
+        <v>Ibadan</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21">
       <c r="B67" t="s">
         <v>475</v>
       </c>
@@ -29012,8 +30843,28 @@
       <c r="L67" t="s">
         <v>703</v>
       </c>
-    </row>
-    <row r="68" spans="2:12">
+      <c r="O67" t="s">
+        <v>532</v>
+      </c>
+      <c r="P67" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q67" t="str">
+        <f t="shared" si="0"/>
+        <v>North-Central</v>
+      </c>
+      <c r="S67" t="s">
+        <v>532</v>
+      </c>
+      <c r="T67" t="s">
+        <v>939</v>
+      </c>
+      <c r="U67" t="str">
+        <f t="shared" si="1"/>
+        <v>Jos</v>
+      </c>
+    </row>
+    <row r="68" spans="2:21">
       <c r="B68" t="s">
         <v>475</v>
       </c>
@@ -29041,8 +30892,28 @@
       <c r="L68" t="s">
         <v>704</v>
       </c>
-    </row>
-    <row r="69" spans="2:12">
+      <c r="O68" t="s">
+        <v>533</v>
+      </c>
+      <c r="P68" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q68" t="str">
+        <f t="shared" si="0"/>
+        <v>South-East</v>
+      </c>
+      <c r="S68" t="s">
+        <v>533</v>
+      </c>
+      <c r="T68" t="s">
+        <v>939</v>
+      </c>
+      <c r="U68" t="str">
+        <f t="shared" si="1"/>
+        <v>Enugu</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21">
       <c r="B69" t="s">
         <v>475</v>
       </c>
@@ -29070,8 +30941,28 @@
       <c r="L69" t="s">
         <v>705</v>
       </c>
-    </row>
-    <row r="70" spans="2:12">
+      <c r="O69" t="s">
+        <v>534</v>
+      </c>
+      <c r="P69" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q69" t="str">
+        <f t="shared" si="0"/>
+        <v>North-Central</v>
+      </c>
+      <c r="S69" t="s">
+        <v>534</v>
+      </c>
+      <c r="T69" t="s">
+        <v>939</v>
+      </c>
+      <c r="U69" t="str">
+        <f t="shared" si="1"/>
+        <v>Abuja</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21">
       <c r="B70" t="s">
         <v>475</v>
       </c>
@@ -29099,8 +30990,28 @@
       <c r="L70" t="s">
         <v>706</v>
       </c>
-    </row>
-    <row r="71" spans="2:12">
+      <c r="O70" t="s">
+        <v>535</v>
+      </c>
+      <c r="P70" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q70" t="str">
+        <f t="shared" si="0"/>
+        <v>South-South</v>
+      </c>
+      <c r="S70" t="s">
+        <v>535</v>
+      </c>
+      <c r="T70" t="s">
+        <v>939</v>
+      </c>
+      <c r="U70" t="str">
+        <f t="shared" si="1"/>
+        <v>Benin</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21">
       <c r="B71" t="s">
         <v>475</v>
       </c>
@@ -29128,8 +31039,28 @@
       <c r="L71" t="s">
         <v>707</v>
       </c>
-    </row>
-    <row r="72" spans="2:12">
+      <c r="O71" t="s">
+        <v>536</v>
+      </c>
+      <c r="P71" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q71" t="str">
+        <f t="shared" si="0"/>
+        <v>South-East</v>
+      </c>
+      <c r="S71" t="s">
+        <v>536</v>
+      </c>
+      <c r="T71" t="s">
+        <v>939</v>
+      </c>
+      <c r="U71" t="str">
+        <f t="shared" si="1"/>
+        <v>Enugu</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21">
       <c r="B72" t="s">
         <v>475</v>
       </c>
@@ -29157,8 +31088,28 @@
       <c r="L72" t="s">
         <v>708</v>
       </c>
-    </row>
-    <row r="73" spans="2:12">
+      <c r="O72" t="s">
+        <v>537</v>
+      </c>
+      <c r="P72" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q72" t="str">
+        <f t="shared" si="0"/>
+        <v>South-South</v>
+      </c>
+      <c r="S72" t="s">
+        <v>537</v>
+      </c>
+      <c r="T72" t="s">
+        <v>939</v>
+      </c>
+      <c r="U72" t="str">
+        <f t="shared" si="1"/>
+        <v>Benin</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21">
       <c r="B73" t="s">
         <v>475</v>
       </c>
@@ -29186,8 +31137,28 @@
       <c r="L73" t="s">
         <v>709</v>
       </c>
-    </row>
-    <row r="74" spans="2:12">
+      <c r="O73" t="s">
+        <v>538</v>
+      </c>
+      <c r="P73" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q73" t="str">
+        <f t="shared" si="0"/>
+        <v>South-West</v>
+      </c>
+      <c r="S73" t="s">
+        <v>538</v>
+      </c>
+      <c r="T73" t="s">
+        <v>939</v>
+      </c>
+      <c r="U73" t="str">
+        <f t="shared" si="1"/>
+        <v>Ibadan</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21">
       <c r="B74" t="s">
         <v>475</v>
       </c>
@@ -29215,8 +31186,28 @@
       <c r="L74" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="75" spans="2:12">
+      <c r="O74" t="s">
+        <v>539</v>
+      </c>
+      <c r="P74" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q74" t="str">
+        <f t="shared" si="0"/>
+        <v>North-Central</v>
+      </c>
+      <c r="S74" t="s">
+        <v>539</v>
+      </c>
+      <c r="T74" t="s">
+        <v>939</v>
+      </c>
+      <c r="U74" t="str">
+        <f t="shared" si="1"/>
+        <v>Ibadan</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21">
       <c r="B75" t="s">
         <v>475</v>
       </c>
@@ -29244,8 +31235,28 @@
       <c r="L75" t="s">
         <v>711</v>
       </c>
-    </row>
-    <row r="76" spans="2:12">
+      <c r="O75" t="s">
+        <v>540</v>
+      </c>
+      <c r="P75" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q75" t="str">
+        <f t="shared" si="0"/>
+        <v>South-West</v>
+      </c>
+      <c r="S75" t="s">
+        <v>540</v>
+      </c>
+      <c r="T75" t="s">
+        <v>939</v>
+      </c>
+      <c r="U75" t="str">
+        <f t="shared" si="1"/>
+        <v>Ibadan</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21">
       <c r="B76" t="s">
         <v>475</v>
       </c>
@@ -29273,8 +31284,28 @@
       <c r="L76" t="s">
         <v>712</v>
       </c>
-    </row>
-    <row r="77" spans="2:12">
+      <c r="O76" t="s">
+        <v>541</v>
+      </c>
+      <c r="P76" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q76" t="str">
+        <f t="shared" ref="Q76:Q139" si="2">VLOOKUP($H76,$Y$11:$Z$44,2,FALSE)</f>
+        <v>South-West</v>
+      </c>
+      <c r="S76" t="s">
+        <v>541</v>
+      </c>
+      <c r="T76" t="s">
+        <v>939</v>
+      </c>
+      <c r="U76" t="str">
+        <f t="shared" ref="U76:U139" si="3">VLOOKUP($H76,$AC$11:$AD$44,2,FALSE)</f>
+        <v>Ibadan</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21">
       <c r="B77" t="s">
         <v>475</v>
       </c>
@@ -29302,8 +31333,28 @@
       <c r="L77" t="s">
         <v>713</v>
       </c>
-    </row>
-    <row r="78" spans="2:12">
+      <c r="O77" t="s">
+        <v>542</v>
+      </c>
+      <c r="P77" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q77" t="str">
+        <f t="shared" si="2"/>
+        <v>South-South</v>
+      </c>
+      <c r="S77" t="s">
+        <v>542</v>
+      </c>
+      <c r="T77" t="s">
+        <v>939</v>
+      </c>
+      <c r="U77" t="str">
+        <f t="shared" si="3"/>
+        <v>Benin</v>
+      </c>
+    </row>
+    <row r="78" spans="2:21">
       <c r="B78" t="s">
         <v>475</v>
       </c>
@@ -29331,8 +31382,28 @@
       <c r="L78" t="s">
         <v>714</v>
       </c>
-    </row>
-    <row r="79" spans="2:12">
+      <c r="O78" t="s">
+        <v>543</v>
+      </c>
+      <c r="P78" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q78" t="str">
+        <f t="shared" si="2"/>
+        <v>South-West</v>
+      </c>
+      <c r="S78" t="s">
+        <v>543</v>
+      </c>
+      <c r="T78" t="s">
+        <v>939</v>
+      </c>
+      <c r="U78" t="str">
+        <f t="shared" si="3"/>
+        <v>Benin</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21">
       <c r="B79" t="s">
         <v>475</v>
       </c>
@@ -29360,8 +31431,28 @@
       <c r="L79" t="s">
         <v>715</v>
       </c>
-    </row>
-    <row r="80" spans="2:12">
+      <c r="O79" t="s">
+        <v>544</v>
+      </c>
+      <c r="P79" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q79" t="str">
+        <f t="shared" si="2"/>
+        <v>South-South</v>
+      </c>
+      <c r="S79" t="s">
+        <v>544</v>
+      </c>
+      <c r="T79" t="s">
+        <v>939</v>
+      </c>
+      <c r="U79" t="str">
+        <f t="shared" si="3"/>
+        <v>Port Harcourt</v>
+      </c>
+    </row>
+    <row r="80" spans="2:21">
       <c r="B80" t="s">
         <v>475</v>
       </c>
@@ -29389,8 +31480,28 @@
       <c r="L80" t="s">
         <v>716</v>
       </c>
-    </row>
-    <row r="81" spans="2:12">
+      <c r="O80" t="s">
+        <v>545</v>
+      </c>
+      <c r="P80" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q80" t="str">
+        <f t="shared" si="2"/>
+        <v>South-South</v>
+      </c>
+      <c r="S80" t="s">
+        <v>545</v>
+      </c>
+      <c r="T80" t="s">
+        <v>939</v>
+      </c>
+      <c r="U80" t="str">
+        <f t="shared" si="3"/>
+        <v>Port Harcourt</v>
+      </c>
+    </row>
+    <row r="81" spans="2:21">
       <c r="B81" t="s">
         <v>475</v>
       </c>
@@ -29418,8 +31529,28 @@
       <c r="L81" t="s">
         <v>717</v>
       </c>
-    </row>
-    <row r="82" spans="2:12">
+      <c r="O81" t="s">
+        <v>546</v>
+      </c>
+      <c r="P81" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q81" t="str">
+        <f t="shared" si="2"/>
+        <v>South-South</v>
+      </c>
+      <c r="S81" t="s">
+        <v>546</v>
+      </c>
+      <c r="T81" t="s">
+        <v>939</v>
+      </c>
+      <c r="U81" t="str">
+        <f t="shared" si="3"/>
+        <v>Benin</v>
+      </c>
+    </row>
+    <row r="82" spans="2:21">
       <c r="B82" t="s">
         <v>475</v>
       </c>
@@ -29447,8 +31578,28 @@
       <c r="L82" t="s">
         <v>718</v>
       </c>
-    </row>
-    <row r="83" spans="2:12">
+      <c r="O82" t="s">
+        <v>547</v>
+      </c>
+      <c r="P82" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q82" t="str">
+        <f t="shared" si="2"/>
+        <v>South-South</v>
+      </c>
+      <c r="S82" t="s">
+        <v>547</v>
+      </c>
+      <c r="T82" t="s">
+        <v>939</v>
+      </c>
+      <c r="U82" t="str">
+        <f t="shared" si="3"/>
+        <v>Benin</v>
+      </c>
+    </row>
+    <row r="83" spans="2:21">
       <c r="B83" t="s">
         <v>475</v>
       </c>
@@ -29476,8 +31627,28 @@
       <c r="L83" t="s">
         <v>719</v>
       </c>
-    </row>
-    <row r="84" spans="2:12">
+      <c r="O83" t="s">
+        <v>548</v>
+      </c>
+      <c r="P83" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q83" t="str">
+        <f t="shared" si="2"/>
+        <v>South-South</v>
+      </c>
+      <c r="S83" t="s">
+        <v>548</v>
+      </c>
+      <c r="T83" t="s">
+        <v>939</v>
+      </c>
+      <c r="U83" t="str">
+        <f t="shared" si="3"/>
+        <v>Benin</v>
+      </c>
+    </row>
+    <row r="84" spans="2:21">
       <c r="B84" t="s">
         <v>475</v>
       </c>
@@ -29505,8 +31676,28 @@
       <c r="L84" t="s">
         <v>720</v>
       </c>
-    </row>
-    <row r="85" spans="2:12">
+      <c r="O84" t="s">
+        <v>549</v>
+      </c>
+      <c r="P84" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q84" t="str">
+        <f t="shared" si="2"/>
+        <v>South-South</v>
+      </c>
+      <c r="S84" t="s">
+        <v>549</v>
+      </c>
+      <c r="T84" t="s">
+        <v>939</v>
+      </c>
+      <c r="U84" t="str">
+        <f t="shared" si="3"/>
+        <v>Port Harcourt</v>
+      </c>
+    </row>
+    <row r="85" spans="2:21">
       <c r="B85" t="s">
         <v>475</v>
       </c>
@@ -29534,8 +31725,28 @@
       <c r="L85" t="s">
         <v>721</v>
       </c>
-    </row>
-    <row r="86" spans="2:12">
+      <c r="O85" t="s">
+        <v>550</v>
+      </c>
+      <c r="P85" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q85" t="str">
+        <f t="shared" si="2"/>
+        <v>South-South</v>
+      </c>
+      <c r="S85" t="s">
+        <v>550</v>
+      </c>
+      <c r="T85" t="s">
+        <v>939</v>
+      </c>
+      <c r="U85" t="str">
+        <f t="shared" si="3"/>
+        <v>Port Harcourt</v>
+      </c>
+    </row>
+    <row r="86" spans="2:21">
       <c r="B86" t="s">
         <v>475</v>
       </c>
@@ -29563,8 +31774,28 @@
       <c r="L86" t="s">
         <v>722</v>
       </c>
-    </row>
-    <row r="87" spans="2:12">
+      <c r="O86" t="s">
+        <v>551</v>
+      </c>
+      <c r="P86" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q86" t="str">
+        <f t="shared" si="2"/>
+        <v>South-South</v>
+      </c>
+      <c r="S86" t="s">
+        <v>551</v>
+      </c>
+      <c r="T86" t="s">
+        <v>939</v>
+      </c>
+      <c r="U86" t="str">
+        <f t="shared" si="3"/>
+        <v>Port Harcourt</v>
+      </c>
+    </row>
+    <row r="87" spans="2:21">
       <c r="B87" t="s">
         <v>475</v>
       </c>
@@ -29592,8 +31823,28 @@
       <c r="L87" t="s">
         <v>723</v>
       </c>
-    </row>
-    <row r="88" spans="2:12">
+      <c r="O87" t="s">
+        <v>552</v>
+      </c>
+      <c r="P87" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q87" t="str">
+        <f t="shared" si="2"/>
+        <v>North-East</v>
+      </c>
+      <c r="S87" t="s">
+        <v>552</v>
+      </c>
+      <c r="T87" t="s">
+        <v>939</v>
+      </c>
+      <c r="U87" t="str">
+        <f t="shared" si="3"/>
+        <v>Yola</v>
+      </c>
+    </row>
+    <row r="88" spans="2:21">
       <c r="B88" t="s">
         <v>475</v>
       </c>
@@ -29621,8 +31872,28 @@
       <c r="L88" t="s">
         <v>724</v>
       </c>
-    </row>
-    <row r="89" spans="2:12">
+      <c r="O88" t="s">
+        <v>553</v>
+      </c>
+      <c r="P88" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q88" t="str">
+        <f t="shared" si="2"/>
+        <v>North-East</v>
+      </c>
+      <c r="S88" t="s">
+        <v>553</v>
+      </c>
+      <c r="T88" t="s">
+        <v>939</v>
+      </c>
+      <c r="U88" t="str">
+        <f t="shared" si="3"/>
+        <v>Yola</v>
+      </c>
+    </row>
+    <row r="89" spans="2:21">
       <c r="B89" t="s">
         <v>475</v>
       </c>
@@ -29650,8 +31921,28 @@
       <c r="L89" t="s">
         <v>725</v>
       </c>
-    </row>
-    <row r="90" spans="2:12">
+      <c r="O89" t="s">
+        <v>554</v>
+      </c>
+      <c r="P89" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q89" t="str">
+        <f t="shared" si="2"/>
+        <v>North-East</v>
+      </c>
+      <c r="S89" t="s">
+        <v>554</v>
+      </c>
+      <c r="T89" t="s">
+        <v>939</v>
+      </c>
+      <c r="U89" t="str">
+        <f t="shared" si="3"/>
+        <v>Yola</v>
+      </c>
+    </row>
+    <row r="90" spans="2:21">
       <c r="B90" t="s">
         <v>475</v>
       </c>
@@ -29679,8 +31970,28 @@
       <c r="L90" t="s">
         <v>726</v>
       </c>
-    </row>
-    <row r="91" spans="2:12">
+      <c r="O90" t="s">
+        <v>555</v>
+      </c>
+      <c r="P90" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q90" t="str">
+        <f t="shared" si="2"/>
+        <v>North-East</v>
+      </c>
+      <c r="S90" t="s">
+        <v>555</v>
+      </c>
+      <c r="T90" t="s">
+        <v>939</v>
+      </c>
+      <c r="U90" t="str">
+        <f t="shared" si="3"/>
+        <v>Yola</v>
+      </c>
+    </row>
+    <row r="91" spans="2:21">
       <c r="B91" t="s">
         <v>475</v>
       </c>
@@ -29708,8 +32019,28 @@
       <c r="L91" t="s">
         <v>727</v>
       </c>
-    </row>
-    <row r="92" spans="2:12">
+      <c r="O91" t="s">
+        <v>556</v>
+      </c>
+      <c r="P91" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q91" t="str">
+        <f t="shared" si="2"/>
+        <v>North-East</v>
+      </c>
+      <c r="S91" t="s">
+        <v>556</v>
+      </c>
+      <c r="T91" t="s">
+        <v>939</v>
+      </c>
+      <c r="U91" t="str">
+        <f t="shared" si="3"/>
+        <v>Yola</v>
+      </c>
+    </row>
+    <row r="92" spans="2:21">
       <c r="B92" t="s">
         <v>475</v>
       </c>
@@ -29737,8 +32068,28 @@
       <c r="L92" t="s">
         <v>728</v>
       </c>
-    </row>
-    <row r="93" spans="2:12">
+      <c r="O92" t="s">
+        <v>557</v>
+      </c>
+      <c r="P92" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q92" t="str">
+        <f t="shared" si="2"/>
+        <v>North-East</v>
+      </c>
+      <c r="S92" t="s">
+        <v>557</v>
+      </c>
+      <c r="T92" t="s">
+        <v>939</v>
+      </c>
+      <c r="U92" t="str">
+        <f t="shared" si="3"/>
+        <v>Yola</v>
+      </c>
+    </row>
+    <row r="93" spans="2:21">
       <c r="B93" t="s">
         <v>475</v>
       </c>
@@ -29766,8 +32117,28 @@
       <c r="L93" t="s">
         <v>729</v>
       </c>
-    </row>
-    <row r="94" spans="2:12">
+      <c r="O93" t="s">
+        <v>558</v>
+      </c>
+      <c r="P93" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q93" t="str">
+        <f t="shared" si="2"/>
+        <v>North-Central</v>
+      </c>
+      <c r="S93" t="s">
+        <v>558</v>
+      </c>
+      <c r="T93" t="s">
+        <v>939</v>
+      </c>
+      <c r="U93" t="str">
+        <f t="shared" si="3"/>
+        <v>Jos</v>
+      </c>
+    </row>
+    <row r="94" spans="2:21">
       <c r="B94" t="s">
         <v>475</v>
       </c>
@@ -29795,8 +32166,28 @@
       <c r="L94" t="s">
         <v>730</v>
       </c>
-    </row>
-    <row r="95" spans="2:12">
+      <c r="O94" t="s">
+        <v>559</v>
+      </c>
+      <c r="P94" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q94" t="str">
+        <f t="shared" si="2"/>
+        <v>North-Central</v>
+      </c>
+      <c r="S94" t="s">
+        <v>559</v>
+      </c>
+      <c r="T94" t="s">
+        <v>939</v>
+      </c>
+      <c r="U94" t="str">
+        <f t="shared" si="3"/>
+        <v>Abuja</v>
+      </c>
+    </row>
+    <row r="95" spans="2:21">
       <c r="B95" t="s">
         <v>475</v>
       </c>
@@ -29824,8 +32215,28 @@
       <c r="L95" t="s">
         <v>731</v>
       </c>
-    </row>
-    <row r="96" spans="2:12">
+      <c r="O95" t="s">
+        <v>560</v>
+      </c>
+      <c r="P95" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q95" t="str">
+        <f t="shared" si="2"/>
+        <v>North-Central</v>
+      </c>
+      <c r="S95" t="s">
+        <v>560</v>
+      </c>
+      <c r="T95" t="s">
+        <v>939</v>
+      </c>
+      <c r="U95" t="str">
+        <f t="shared" si="3"/>
+        <v>Jos</v>
+      </c>
+    </row>
+    <row r="96" spans="2:21">
       <c r="B96" t="s">
         <v>475</v>
       </c>
@@ -29853,8 +32264,28 @@
       <c r="L96" t="s">
         <v>732</v>
       </c>
-    </row>
-    <row r="97" spans="2:12">
+      <c r="O96" t="s">
+        <v>561</v>
+      </c>
+      <c r="P96" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q96" t="str">
+        <f t="shared" si="2"/>
+        <v>North-Central</v>
+      </c>
+      <c r="S96" t="s">
+        <v>561</v>
+      </c>
+      <c r="T96" t="s">
+        <v>939</v>
+      </c>
+      <c r="U96" t="str">
+        <f t="shared" si="3"/>
+        <v>Jos</v>
+      </c>
+    </row>
+    <row r="97" spans="2:21">
       <c r="B97" t="s">
         <v>475</v>
       </c>
@@ -29882,8 +32313,28 @@
       <c r="L97" t="s">
         <v>733</v>
       </c>
-    </row>
-    <row r="98" spans="2:12">
+      <c r="O97" t="s">
+        <v>562</v>
+      </c>
+      <c r="P97" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q97" t="str">
+        <f t="shared" si="2"/>
+        <v>North-Central</v>
+      </c>
+      <c r="S97" t="s">
+        <v>562</v>
+      </c>
+      <c r="T97" t="s">
+        <v>939</v>
+      </c>
+      <c r="U97" t="str">
+        <f t="shared" si="3"/>
+        <v>Abuja</v>
+      </c>
+    </row>
+    <row r="98" spans="2:21">
       <c r="B98" t="s">
         <v>475</v>
       </c>
@@ -29911,8 +32362,28 @@
       <c r="L98" t="s">
         <v>734</v>
       </c>
-    </row>
-    <row r="99" spans="2:12">
+      <c r="O98" t="s">
+        <v>563</v>
+      </c>
+      <c r="P98" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q98" t="str">
+        <f t="shared" si="2"/>
+        <v>North-Central</v>
+      </c>
+      <c r="S98" t="s">
+        <v>563</v>
+      </c>
+      <c r="T98" t="s">
+        <v>939</v>
+      </c>
+      <c r="U98" t="str">
+        <f t="shared" si="3"/>
+        <v>Abuja</v>
+      </c>
+    </row>
+    <row r="99" spans="2:21">
       <c r="B99" t="s">
         <v>475</v>
       </c>
@@ -29940,8 +32411,28 @@
       <c r="L99" t="s">
         <v>735</v>
       </c>
-    </row>
-    <row r="100" spans="2:12">
+      <c r="O99" t="s">
+        <v>564</v>
+      </c>
+      <c r="P99" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q99" t="str">
+        <f t="shared" si="2"/>
+        <v>North-East</v>
+      </c>
+      <c r="S99" t="s">
+        <v>564</v>
+      </c>
+      <c r="T99" t="s">
+        <v>939</v>
+      </c>
+      <c r="U99" t="str">
+        <f t="shared" si="3"/>
+        <v>Jos</v>
+      </c>
+    </row>
+    <row r="100" spans="2:21">
       <c r="B100" t="s">
         <v>475</v>
       </c>
@@ -29969,8 +32460,28 @@
       <c r="L100" t="s">
         <v>736</v>
       </c>
-    </row>
-    <row r="101" spans="2:12">
+      <c r="O100" t="s">
+        <v>565</v>
+      </c>
+      <c r="P100" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q100" t="str">
+        <f t="shared" si="2"/>
+        <v>North-West</v>
+      </c>
+      <c r="S100" t="s">
+        <v>565</v>
+      </c>
+      <c r="T100" t="s">
+        <v>939</v>
+      </c>
+      <c r="U100" t="str">
+        <f t="shared" si="3"/>
+        <v>Kano</v>
+      </c>
+    </row>
+    <row r="101" spans="2:21">
       <c r="B101" t="s">
         <v>475</v>
       </c>
@@ -29998,8 +32509,28 @@
       <c r="L101" t="s">
         <v>737</v>
       </c>
-    </row>
-    <row r="102" spans="2:12">
+      <c r="O101" t="s">
+        <v>566</v>
+      </c>
+      <c r="P101" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q101" t="str">
+        <f t="shared" si="2"/>
+        <v>North-West</v>
+      </c>
+      <c r="S101" t="s">
+        <v>566</v>
+      </c>
+      <c r="T101" t="s">
+        <v>939</v>
+      </c>
+      <c r="U101" t="str">
+        <f t="shared" si="3"/>
+        <v>Kano</v>
+      </c>
+    </row>
+    <row r="102" spans="2:21">
       <c r="B102" t="s">
         <v>475</v>
       </c>
@@ -30027,8 +32558,28 @@
       <c r="L102" t="s">
         <v>738</v>
       </c>
-    </row>
-    <row r="103" spans="2:12">
+      <c r="O102" t="s">
+        <v>567</v>
+      </c>
+      <c r="P102" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q102" t="str">
+        <f t="shared" si="2"/>
+        <v>North-West</v>
+      </c>
+      <c r="S102" t="s">
+        <v>567</v>
+      </c>
+      <c r="T102" t="s">
+        <v>939</v>
+      </c>
+      <c r="U102" t="str">
+        <f t="shared" si="3"/>
+        <v>Kaduna</v>
+      </c>
+    </row>
+    <row r="103" spans="2:21">
       <c r="B103" t="s">
         <v>475</v>
       </c>
@@ -30056,8 +32607,28 @@
       <c r="L103" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="104" spans="2:12">
+      <c r="O103" t="s">
+        <v>568</v>
+      </c>
+      <c r="P103" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q103" t="str">
+        <f t="shared" si="2"/>
+        <v>North-West</v>
+      </c>
+      <c r="S103" t="s">
+        <v>568</v>
+      </c>
+      <c r="T103" t="s">
+        <v>939</v>
+      </c>
+      <c r="U103" t="str">
+        <f t="shared" si="3"/>
+        <v>Kaduna</v>
+      </c>
+    </row>
+    <row r="104" spans="2:21">
       <c r="B104" t="s">
         <v>475</v>
       </c>
@@ -30085,8 +32656,28 @@
       <c r="L104" t="s">
         <v>740</v>
       </c>
-    </row>
-    <row r="105" spans="2:12">
+      <c r="O104" t="s">
+        <v>569</v>
+      </c>
+      <c r="P104" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q104" t="str">
+        <f t="shared" si="2"/>
+        <v>North-Central</v>
+      </c>
+      <c r="S104" t="s">
+        <v>569</v>
+      </c>
+      <c r="T104" t="s">
+        <v>939</v>
+      </c>
+      <c r="U104" t="str">
+        <f t="shared" si="3"/>
+        <v>Abuja</v>
+      </c>
+    </row>
+    <row r="105" spans="2:21">
       <c r="B105" t="s">
         <v>475</v>
       </c>
@@ -30114,8 +32705,28 @@
       <c r="L105" t="s">
         <v>741</v>
       </c>
-    </row>
-    <row r="106" spans="2:12">
+      <c r="O105" t="s">
+        <v>570</v>
+      </c>
+      <c r="P105" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q105" t="str">
+        <f t="shared" si="2"/>
+        <v>North-West</v>
+      </c>
+      <c r="S105" t="s">
+        <v>570</v>
+      </c>
+      <c r="T105" t="s">
+        <v>939</v>
+      </c>
+      <c r="U105" t="str">
+        <f t="shared" si="3"/>
+        <v>Kaduna</v>
+      </c>
+    </row>
+    <row r="106" spans="2:21">
       <c r="B106" t="s">
         <v>475</v>
       </c>
@@ -30143,8 +32754,28 @@
       <c r="L106" t="s">
         <v>742</v>
       </c>
-    </row>
-    <row r="107" spans="2:12">
+      <c r="O106" t="s">
+        <v>571</v>
+      </c>
+      <c r="P106" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q106" t="str">
+        <f t="shared" si="2"/>
+        <v>North-Central</v>
+      </c>
+      <c r="S106" t="s">
+        <v>571</v>
+      </c>
+      <c r="T106" t="s">
+        <v>939</v>
+      </c>
+      <c r="U106" t="str">
+        <f t="shared" si="3"/>
+        <v>Abuja</v>
+      </c>
+    </row>
+    <row r="107" spans="2:21">
       <c r="B107" t="s">
         <v>475</v>
       </c>
@@ -30172,8 +32803,28 @@
       <c r="L107" t="s">
         <v>743</v>
       </c>
-    </row>
-    <row r="108" spans="2:12">
+      <c r="O107" t="s">
+        <v>572</v>
+      </c>
+      <c r="P107" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q107" t="str">
+        <f t="shared" si="2"/>
+        <v>North-West</v>
+      </c>
+      <c r="S107" t="s">
+        <v>572</v>
+      </c>
+      <c r="T107" t="s">
+        <v>939</v>
+      </c>
+      <c r="U107" t="str">
+        <f t="shared" si="3"/>
+        <v>Kaduna</v>
+      </c>
+    </row>
+    <row r="108" spans="2:21">
       <c r="B108" t="s">
         <v>475</v>
       </c>
@@ -30201,8 +32852,28 @@
       <c r="L108" t="s">
         <v>744</v>
       </c>
-    </row>
-    <row r="109" spans="2:12">
+      <c r="O108" t="s">
+        <v>573</v>
+      </c>
+      <c r="P108" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q108" t="str">
+        <f t="shared" si="2"/>
+        <v>North-Central</v>
+      </c>
+      <c r="S108" t="s">
+        <v>573</v>
+      </c>
+      <c r="T108" t="s">
+        <v>939</v>
+      </c>
+      <c r="U108" t="str">
+        <f t="shared" si="3"/>
+        <v>Ibadan</v>
+      </c>
+    </row>
+    <row r="109" spans="2:21">
       <c r="B109" t="s">
         <v>475</v>
       </c>
@@ -30230,8 +32901,28 @@
       <c r="L109" t="s">
         <v>745</v>
       </c>
-    </row>
-    <row r="110" spans="2:12">
+      <c r="O109" t="s">
+        <v>574</v>
+      </c>
+      <c r="P109" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q109" t="str">
+        <f t="shared" si="2"/>
+        <v>North-Central</v>
+      </c>
+      <c r="S109" t="s">
+        <v>574</v>
+      </c>
+      <c r="T109" t="s">
+        <v>939</v>
+      </c>
+      <c r="U109" t="str">
+        <f t="shared" si="3"/>
+        <v>Jos</v>
+      </c>
+    </row>
+    <row r="110" spans="2:21">
       <c r="B110" t="s">
         <v>475</v>
       </c>
@@ -30259,8 +32950,28 @@
       <c r="L110" t="s">
         <v>746</v>
       </c>
-    </row>
-    <row r="111" spans="2:12">
+      <c r="O110" t="s">
+        <v>575</v>
+      </c>
+      <c r="P110" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q110" t="str">
+        <f t="shared" si="2"/>
+        <v>North-East</v>
+      </c>
+      <c r="S110" t="s">
+        <v>575</v>
+      </c>
+      <c r="T110" t="s">
+        <v>939</v>
+      </c>
+      <c r="U110" t="str">
+        <f t="shared" si="3"/>
+        <v>Yola</v>
+      </c>
+    </row>
+    <row r="111" spans="2:21">
       <c r="B111" t="s">
         <v>475</v>
       </c>
@@ -30288,8 +32999,28 @@
       <c r="L111" t="s">
         <v>747</v>
       </c>
-    </row>
-    <row r="112" spans="2:12">
+      <c r="O111" t="s">
+        <v>576</v>
+      </c>
+      <c r="P111" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q111" t="str">
+        <f t="shared" si="2"/>
+        <v>North-East</v>
+      </c>
+      <c r="S111" t="s">
+        <v>576</v>
+      </c>
+      <c r="T111" t="s">
+        <v>939</v>
+      </c>
+      <c r="U111" t="str">
+        <f t="shared" si="3"/>
+        <v>Yola</v>
+      </c>
+    </row>
+    <row r="112" spans="2:21">
       <c r="B112" t="s">
         <v>475</v>
       </c>
@@ -30317,8 +33048,28 @@
       <c r="L112" t="s">
         <v>748</v>
       </c>
-    </row>
-    <row r="113" spans="2:12">
+      <c r="O112" t="s">
+        <v>577</v>
+      </c>
+      <c r="P112" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q112" t="str">
+        <f t="shared" si="2"/>
+        <v>North-East</v>
+      </c>
+      <c r="S112" t="s">
+        <v>577</v>
+      </c>
+      <c r="T112" t="s">
+        <v>939</v>
+      </c>
+      <c r="U112" t="str">
+        <f t="shared" si="3"/>
+        <v>Yola</v>
+      </c>
+    </row>
+    <row r="113" spans="2:21">
       <c r="B113" t="s">
         <v>475</v>
       </c>
@@ -30346,8 +33097,28 @@
       <c r="L113" t="s">
         <v>749</v>
       </c>
-    </row>
-    <row r="114" spans="2:12">
+      <c r="O113" t="s">
+        <v>578</v>
+      </c>
+      <c r="P113" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q113" t="str">
+        <f t="shared" si="2"/>
+        <v>North-Central</v>
+      </c>
+      <c r="S113" t="s">
+        <v>578</v>
+      </c>
+      <c r="T113" t="s">
+        <v>939</v>
+      </c>
+      <c r="U113" t="str">
+        <f t="shared" si="3"/>
+        <v>Jos</v>
+      </c>
+    </row>
+    <row r="114" spans="2:21">
       <c r="B114" t="s">
         <v>475</v>
       </c>
@@ -30375,8 +33146,28 @@
       <c r="L114" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="115" spans="2:12">
+      <c r="O114" t="s">
+        <v>579</v>
+      </c>
+      <c r="P114" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q114" t="str">
+        <f t="shared" si="2"/>
+        <v>North-Central</v>
+      </c>
+      <c r="S114" t="s">
+        <v>579</v>
+      </c>
+      <c r="T114" t="s">
+        <v>939</v>
+      </c>
+      <c r="U114" t="str">
+        <f t="shared" si="3"/>
+        <v>Ibadan</v>
+      </c>
+    </row>
+    <row r="115" spans="2:21">
       <c r="B115" t="s">
         <v>475</v>
       </c>
@@ -30404,8 +33195,28 @@
       <c r="L115" t="s">
         <v>751</v>
       </c>
-    </row>
-    <row r="116" spans="2:12">
+      <c r="O115" t="s">
+        <v>580</v>
+      </c>
+      <c r="P115" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q115" t="str">
+        <f t="shared" si="2"/>
+        <v>North-Central</v>
+      </c>
+      <c r="S115" t="s">
+        <v>580</v>
+      </c>
+      <c r="T115" t="s">
+        <v>939</v>
+      </c>
+      <c r="U115" t="str">
+        <f t="shared" si="3"/>
+        <v>Ibadan</v>
+      </c>
+    </row>
+    <row r="116" spans="2:21">
       <c r="B116" t="s">
         <v>475</v>
       </c>
@@ -30433,8 +33244,28 @@
       <c r="L116" t="s">
         <v>752</v>
       </c>
-    </row>
-    <row r="117" spans="2:12">
+      <c r="O116" t="s">
+        <v>581</v>
+      </c>
+      <c r="P116" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q116" t="str">
+        <f t="shared" si="2"/>
+        <v>Unknown</v>
+      </c>
+      <c r="S116" t="s">
+        <v>581</v>
+      </c>
+      <c r="T116" t="s">
+        <v>939</v>
+      </c>
+      <c r="U116" t="str">
+        <f t="shared" si="3"/>
+        <v>Unknown</v>
+      </c>
+    </row>
+    <row r="117" spans="2:21">
       <c r="B117" t="s">
         <v>475</v>
       </c>
@@ -30462,8 +33293,28 @@
       <c r="L117" t="s">
         <v>753</v>
       </c>
-    </row>
-    <row r="118" spans="2:12">
+      <c r="O117" t="s">
+        <v>582</v>
+      </c>
+      <c r="P117" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q117" t="str">
+        <f t="shared" si="2"/>
+        <v>North-Central</v>
+      </c>
+      <c r="S117" t="s">
+        <v>582</v>
+      </c>
+      <c r="T117" t="s">
+        <v>939</v>
+      </c>
+      <c r="U117" t="str">
+        <f t="shared" si="3"/>
+        <v>Abuja</v>
+      </c>
+    </row>
+    <row r="118" spans="2:21">
       <c r="B118" t="s">
         <v>475</v>
       </c>
@@ -30491,8 +33342,28 @@
       <c r="L118" t="s">
         <v>754</v>
       </c>
-    </row>
-    <row r="119" spans="2:12">
+      <c r="O118" t="s">
+        <v>583</v>
+      </c>
+      <c r="P118" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q118" t="str">
+        <f t="shared" si="2"/>
+        <v>North-West</v>
+      </c>
+      <c r="S118" t="s">
+        <v>583</v>
+      </c>
+      <c r="T118" t="s">
+        <v>939</v>
+      </c>
+      <c r="U118" t="str">
+        <f t="shared" si="3"/>
+        <v>Kaduna</v>
+      </c>
+    </row>
+    <row r="119" spans="2:21">
       <c r="B119" t="s">
         <v>475</v>
       </c>
@@ -30520,8 +33391,28 @@
       <c r="L119" t="s">
         <v>755</v>
       </c>
-    </row>
-    <row r="120" spans="2:12">
+      <c r="O119" t="s">
+        <v>584</v>
+      </c>
+      <c r="P119" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q119" t="str">
+        <f t="shared" si="2"/>
+        <v>North-West</v>
+      </c>
+      <c r="S119" t="s">
+        <v>584</v>
+      </c>
+      <c r="T119" t="s">
+        <v>939</v>
+      </c>
+      <c r="U119" t="str">
+        <f t="shared" si="3"/>
+        <v>Kaduna</v>
+      </c>
+    </row>
+    <row r="120" spans="2:21">
       <c r="B120" t="s">
         <v>475</v>
       </c>
@@ -30549,8 +33440,28 @@
       <c r="L120" t="s">
         <v>756</v>
       </c>
-    </row>
-    <row r="121" spans="2:12">
+      <c r="O120" t="s">
+        <v>585</v>
+      </c>
+      <c r="P120" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q120" t="str">
+        <f t="shared" si="2"/>
+        <v>North-Central</v>
+      </c>
+      <c r="S120" t="s">
+        <v>585</v>
+      </c>
+      <c r="T120" t="s">
+        <v>939</v>
+      </c>
+      <c r="U120" t="str">
+        <f t="shared" si="3"/>
+        <v>Abuja</v>
+      </c>
+    </row>
+    <row r="121" spans="2:21">
       <c r="B121" t="s">
         <v>475</v>
       </c>
@@ -30578,8 +33489,28 @@
       <c r="L121" t="s">
         <v>757</v>
       </c>
-    </row>
-    <row r="122" spans="2:12">
+      <c r="O121" t="s">
+        <v>586</v>
+      </c>
+      <c r="P121" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q121" t="str">
+        <f t="shared" si="2"/>
+        <v>North-West</v>
+      </c>
+      <c r="S121" t="s">
+        <v>586</v>
+      </c>
+      <c r="T121" t="s">
+        <v>939</v>
+      </c>
+      <c r="U121" t="str">
+        <f t="shared" si="3"/>
+        <v>Kaduna</v>
+      </c>
+    </row>
+    <row r="122" spans="2:21">
       <c r="B122" t="s">
         <v>475</v>
       </c>
@@ -30607,8 +33538,28 @@
       <c r="L122" t="s">
         <v>758</v>
       </c>
-    </row>
-    <row r="123" spans="2:12">
+      <c r="O122" t="s">
+        <v>587</v>
+      </c>
+      <c r="P122" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q122" t="str">
+        <f t="shared" si="2"/>
+        <v>North-West</v>
+      </c>
+      <c r="S122" t="s">
+        <v>587</v>
+      </c>
+      <c r="T122" t="s">
+        <v>939</v>
+      </c>
+      <c r="U122" t="str">
+        <f t="shared" si="3"/>
+        <v>Kaduna</v>
+      </c>
+    </row>
+    <row r="123" spans="2:21">
       <c r="B123" t="s">
         <v>475</v>
       </c>
@@ -30636,8 +33587,28 @@
       <c r="L123" t="s">
         <v>759</v>
       </c>
-    </row>
-    <row r="124" spans="2:12">
+      <c r="O123" t="s">
+        <v>588</v>
+      </c>
+      <c r="P123" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q123" t="str">
+        <f t="shared" si="2"/>
+        <v>North-West</v>
+      </c>
+      <c r="S123" t="s">
+        <v>588</v>
+      </c>
+      <c r="T123" t="s">
+        <v>939</v>
+      </c>
+      <c r="U123" t="str">
+        <f t="shared" si="3"/>
+        <v>Kaduna</v>
+      </c>
+    </row>
+    <row r="124" spans="2:21">
       <c r="B124" t="s">
         <v>475</v>
       </c>
@@ -30665,8 +33636,28 @@
       <c r="L124" t="s">
         <v>760</v>
       </c>
-    </row>
-    <row r="125" spans="2:12">
+      <c r="O124" t="s">
+        <v>589</v>
+      </c>
+      <c r="P124" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q124" t="str">
+        <f t="shared" si="2"/>
+        <v>North-East</v>
+      </c>
+      <c r="S124" t="s">
+        <v>589</v>
+      </c>
+      <c r="T124" t="s">
+        <v>939</v>
+      </c>
+      <c r="U124" t="str">
+        <f t="shared" si="3"/>
+        <v>Yola</v>
+      </c>
+    </row>
+    <row r="125" spans="2:21">
       <c r="B125" t="s">
         <v>475</v>
       </c>
@@ -30694,8 +33685,28 @@
       <c r="L125" t="s">
         <v>761</v>
       </c>
-    </row>
-    <row r="126" spans="2:12">
+      <c r="O125" t="s">
+        <v>590</v>
+      </c>
+      <c r="P125" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q125" t="str">
+        <f t="shared" si="2"/>
+        <v>North-East</v>
+      </c>
+      <c r="S125" t="s">
+        <v>590</v>
+      </c>
+      <c r="T125" t="s">
+        <v>939</v>
+      </c>
+      <c r="U125" t="str">
+        <f t="shared" si="3"/>
+        <v>Yola</v>
+      </c>
+    </row>
+    <row r="126" spans="2:21">
       <c r="B126" t="s">
         <v>475</v>
       </c>
@@ -30723,8 +33734,28 @@
       <c r="L126" t="s">
         <v>762</v>
       </c>
-    </row>
-    <row r="127" spans="2:12">
+      <c r="O126" t="s">
+        <v>591</v>
+      </c>
+      <c r="P126" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q126" t="str">
+        <f t="shared" si="2"/>
+        <v>North-East</v>
+      </c>
+      <c r="S126" t="s">
+        <v>591</v>
+      </c>
+      <c r="T126" t="s">
+        <v>939</v>
+      </c>
+      <c r="U126" t="str">
+        <f t="shared" si="3"/>
+        <v>Yola</v>
+      </c>
+    </row>
+    <row r="127" spans="2:21">
       <c r="B127" t="s">
         <v>475</v>
       </c>
@@ -30752,8 +33783,28 @@
       <c r="L127" t="s">
         <v>763</v>
       </c>
-    </row>
-    <row r="128" spans="2:12">
+      <c r="O127" t="s">
+        <v>592</v>
+      </c>
+      <c r="P127" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q127" t="str">
+        <f t="shared" si="2"/>
+        <v>North-East</v>
+      </c>
+      <c r="S127" t="s">
+        <v>592</v>
+      </c>
+      <c r="T127" t="s">
+        <v>939</v>
+      </c>
+      <c r="U127" t="str">
+        <f t="shared" si="3"/>
+        <v>Yola</v>
+      </c>
+    </row>
+    <row r="128" spans="2:21">
       <c r="B128" t="s">
         <v>475</v>
       </c>
@@ -30781,8 +33832,28 @@
       <c r="L128" t="s">
         <v>764</v>
       </c>
-    </row>
-    <row r="129" spans="2:12">
+      <c r="O128" t="s">
+        <v>593</v>
+      </c>
+      <c r="P128" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q128" t="str">
+        <f t="shared" si="2"/>
+        <v>North-East</v>
+      </c>
+      <c r="S128" t="s">
+        <v>593</v>
+      </c>
+      <c r="T128" t="s">
+        <v>939</v>
+      </c>
+      <c r="U128" t="str">
+        <f t="shared" si="3"/>
+        <v>Jos</v>
+      </c>
+    </row>
+    <row r="129" spans="2:21">
       <c r="B129" t="s">
         <v>475</v>
       </c>
@@ -30810,8 +33881,28 @@
       <c r="L129" t="s">
         <v>765</v>
       </c>
-    </row>
-    <row r="130" spans="2:12">
+      <c r="O129" t="s">
+        <v>594</v>
+      </c>
+      <c r="P129" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q129" t="str">
+        <f t="shared" si="2"/>
+        <v>North-East</v>
+      </c>
+      <c r="S129" t="s">
+        <v>594</v>
+      </c>
+      <c r="T129" t="s">
+        <v>939</v>
+      </c>
+      <c r="U129" t="str">
+        <f t="shared" si="3"/>
+        <v>Jos</v>
+      </c>
+    </row>
+    <row r="130" spans="2:21">
       <c r="B130" t="s">
         <v>475</v>
       </c>
@@ -30839,8 +33930,28 @@
       <c r="L130" t="s">
         <v>766</v>
       </c>
-    </row>
-    <row r="131" spans="2:12">
+      <c r="O130" t="s">
+        <v>595</v>
+      </c>
+      <c r="P130" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q130" t="str">
+        <f t="shared" si="2"/>
+        <v>North-West</v>
+      </c>
+      <c r="S130" t="s">
+        <v>595</v>
+      </c>
+      <c r="T130" t="s">
+        <v>939</v>
+      </c>
+      <c r="U130" t="str">
+        <f t="shared" si="3"/>
+        <v>Kano</v>
+      </c>
+    </row>
+    <row r="131" spans="2:21">
       <c r="B131" t="s">
         <v>475</v>
       </c>
@@ -30868,8 +33979,28 @@
       <c r="L131" t="s">
         <v>767</v>
       </c>
-    </row>
-    <row r="132" spans="2:12">
+      <c r="O131" t="s">
+        <v>596</v>
+      </c>
+      <c r="P131" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q131" t="str">
+        <f t="shared" si="2"/>
+        <v>North-West</v>
+      </c>
+      <c r="S131" t="s">
+        <v>596</v>
+      </c>
+      <c r="T131" t="s">
+        <v>939</v>
+      </c>
+      <c r="U131" t="str">
+        <f t="shared" si="3"/>
+        <v>Kaduna</v>
+      </c>
+    </row>
+    <row r="132" spans="2:21">
       <c r="B132" t="s">
         <v>475</v>
       </c>
@@ -30897,8 +34028,28 @@
       <c r="L132" t="s">
         <v>768</v>
       </c>
-    </row>
-    <row r="133" spans="2:12">
+      <c r="O132" t="s">
+        <v>597</v>
+      </c>
+      <c r="P132" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q132" t="str">
+        <f t="shared" si="2"/>
+        <v>North-East</v>
+      </c>
+      <c r="S132" t="s">
+        <v>597</v>
+      </c>
+      <c r="T132" t="s">
+        <v>939</v>
+      </c>
+      <c r="U132" t="str">
+        <f t="shared" si="3"/>
+        <v>Jos</v>
+      </c>
+    </row>
+    <row r="133" spans="2:21">
       <c r="B133" t="s">
         <v>475</v>
       </c>
@@ -30926,8 +34077,28 @@
       <c r="L133" t="s">
         <v>769</v>
       </c>
-    </row>
-    <row r="134" spans="2:12">
+      <c r="O133" t="s">
+        <v>598</v>
+      </c>
+      <c r="P133" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q133" t="str">
+        <f t="shared" si="2"/>
+        <v>North-West</v>
+      </c>
+      <c r="S133" t="s">
+        <v>598</v>
+      </c>
+      <c r="T133" t="s">
+        <v>939</v>
+      </c>
+      <c r="U133" t="str">
+        <f t="shared" si="3"/>
+        <v>Kano</v>
+      </c>
+    </row>
+    <row r="134" spans="2:21">
       <c r="B134" t="s">
         <v>475</v>
       </c>
@@ -30955,8 +34126,28 @@
       <c r="L134" t="s">
         <v>770</v>
       </c>
-    </row>
-    <row r="135" spans="2:12">
+      <c r="O134" t="s">
+        <v>599</v>
+      </c>
+      <c r="P134" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q134" t="str">
+        <f t="shared" si="2"/>
+        <v>North-East</v>
+      </c>
+      <c r="S134" t="s">
+        <v>599</v>
+      </c>
+      <c r="T134" t="s">
+        <v>939</v>
+      </c>
+      <c r="U134" t="str">
+        <f t="shared" si="3"/>
+        <v>Yola</v>
+      </c>
+    </row>
+    <row r="135" spans="2:21">
       <c r="B135" t="s">
         <v>475</v>
       </c>
@@ -30984,8 +34175,28 @@
       <c r="L135" t="s">
         <v>771</v>
       </c>
-    </row>
-    <row r="136" spans="2:12">
+      <c r="O135" t="s">
+        <v>600</v>
+      </c>
+      <c r="P135" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q135" t="str">
+        <f t="shared" si="2"/>
+        <v>North-East</v>
+      </c>
+      <c r="S135" t="s">
+        <v>600</v>
+      </c>
+      <c r="T135" t="s">
+        <v>939</v>
+      </c>
+      <c r="U135" t="str">
+        <f t="shared" si="3"/>
+        <v>Jos</v>
+      </c>
+    </row>
+    <row r="136" spans="2:21">
       <c r="B136" t="s">
         <v>475</v>
       </c>
@@ -31013,8 +34224,28 @@
       <c r="L136" t="s">
         <v>772</v>
       </c>
-    </row>
-    <row r="137" spans="2:12">
+      <c r="O136" t="s">
+        <v>601</v>
+      </c>
+      <c r="P136" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q136" t="str">
+        <f t="shared" si="2"/>
+        <v>South-West</v>
+      </c>
+      <c r="S136" t="s">
+        <v>601</v>
+      </c>
+      <c r="T136" t="s">
+        <v>939</v>
+      </c>
+      <c r="U136" t="str">
+        <f t="shared" si="3"/>
+        <v>Ibadan</v>
+      </c>
+    </row>
+    <row r="137" spans="2:21">
       <c r="B137" t="s">
         <v>475</v>
       </c>
@@ -31042,8 +34273,28 @@
       <c r="L137" t="s">
         <v>773</v>
       </c>
-    </row>
-    <row r="138" spans="2:12">
+      <c r="O137" t="s">
+        <v>602</v>
+      </c>
+      <c r="P137" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q137" t="str">
+        <f t="shared" si="2"/>
+        <v>Unknown</v>
+      </c>
+      <c r="S137" t="s">
+        <v>602</v>
+      </c>
+      <c r="T137" t="s">
+        <v>939</v>
+      </c>
+      <c r="U137" t="str">
+        <f t="shared" si="3"/>
+        <v>Unknown</v>
+      </c>
+    </row>
+    <row r="138" spans="2:21">
       <c r="B138" t="s">
         <v>475</v>
       </c>
@@ -31071,8 +34322,28 @@
       <c r="L138" t="s">
         <v>774</v>
       </c>
-    </row>
-    <row r="139" spans="2:12">
+      <c r="O138" t="s">
+        <v>603</v>
+      </c>
+      <c r="P138" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q138" t="str">
+        <f t="shared" si="2"/>
+        <v>Unknown</v>
+      </c>
+      <c r="S138" t="s">
+        <v>603</v>
+      </c>
+      <c r="T138" t="s">
+        <v>939</v>
+      </c>
+      <c r="U138" t="str">
+        <f t="shared" si="3"/>
+        <v>Unknown</v>
+      </c>
+    </row>
+    <row r="139" spans="2:21">
       <c r="B139" t="s">
         <v>475</v>
       </c>
@@ -31100,8 +34371,28 @@
       <c r="L139" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="140" spans="2:12">
+      <c r="O139" t="s">
+        <v>604</v>
+      </c>
+      <c r="P139" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q139" t="str">
+        <f t="shared" si="2"/>
+        <v>Unknown</v>
+      </c>
+      <c r="S139" t="s">
+        <v>604</v>
+      </c>
+      <c r="T139" t="s">
+        <v>939</v>
+      </c>
+      <c r="U139" t="str">
+        <f t="shared" si="3"/>
+        <v>Unknown</v>
+      </c>
+    </row>
+    <row r="140" spans="2:21">
       <c r="B140" t="s">
         <v>475</v>
       </c>
@@ -31129,8 +34420,28 @@
       <c r="L140" t="s">
         <v>776</v>
       </c>
-    </row>
-    <row r="141" spans="2:12">
+      <c r="O140" t="s">
+        <v>605</v>
+      </c>
+      <c r="P140" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q140" t="str">
+        <f t="shared" ref="Q140:Q145" si="4">VLOOKUP($H140,$Y$11:$Z$44,2,FALSE)</f>
+        <v>Unknown</v>
+      </c>
+      <c r="S140" t="s">
+        <v>605</v>
+      </c>
+      <c r="T140" t="s">
+        <v>939</v>
+      </c>
+      <c r="U140" t="str">
+        <f t="shared" ref="U140:U145" si="5">VLOOKUP($H140,$AC$11:$AD$44,2,FALSE)</f>
+        <v>Unknown</v>
+      </c>
+    </row>
+    <row r="141" spans="2:21">
       <c r="B141" t="s">
         <v>475</v>
       </c>
@@ -31158,8 +34469,28 @@
       <c r="L141" t="s">
         <v>777</v>
       </c>
-    </row>
-    <row r="142" spans="2:12">
+      <c r="O141" t="s">
+        <v>606</v>
+      </c>
+      <c r="P141" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q141" t="str">
+        <f t="shared" si="4"/>
+        <v>Unknown</v>
+      </c>
+      <c r="S141" t="s">
+        <v>606</v>
+      </c>
+      <c r="T141" t="s">
+        <v>939</v>
+      </c>
+      <c r="U141" t="str">
+        <f t="shared" si="5"/>
+        <v>Unknown</v>
+      </c>
+    </row>
+    <row r="142" spans="2:21">
       <c r="B142" t="s">
         <v>475</v>
       </c>
@@ -31187,8 +34518,28 @@
       <c r="L142" t="s">
         <v>778</v>
       </c>
-    </row>
-    <row r="143" spans="2:12">
+      <c r="O142" t="s">
+        <v>607</v>
+      </c>
+      <c r="P142" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q142" t="str">
+        <f t="shared" si="4"/>
+        <v>Unknown</v>
+      </c>
+      <c r="S142" t="s">
+        <v>607</v>
+      </c>
+      <c r="T142" t="s">
+        <v>939</v>
+      </c>
+      <c r="U142" t="str">
+        <f t="shared" si="5"/>
+        <v>Unknown</v>
+      </c>
+    </row>
+    <row r="143" spans="2:21">
       <c r="B143" t="s">
         <v>475</v>
       </c>
@@ -31216,8 +34567,28 @@
       <c r="L143" t="s">
         <v>779</v>
       </c>
-    </row>
-    <row r="144" spans="2:12">
+      <c r="O143" t="s">
+        <v>608</v>
+      </c>
+      <c r="P143" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q143" t="str">
+        <f t="shared" si="4"/>
+        <v>Unknown</v>
+      </c>
+      <c r="S143" t="s">
+        <v>608</v>
+      </c>
+      <c r="T143" t="s">
+        <v>939</v>
+      </c>
+      <c r="U143" t="str">
+        <f t="shared" si="5"/>
+        <v>Unknown</v>
+      </c>
+    </row>
+    <row r="144" spans="2:21">
       <c r="B144" t="s">
         <v>475</v>
       </c>
@@ -31245,8 +34616,28 @@
       <c r="L144" t="s">
         <v>780</v>
       </c>
-    </row>
-    <row r="145" spans="2:12">
+      <c r="O144" t="s">
+        <v>609</v>
+      </c>
+      <c r="P144" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q144" t="str">
+        <f t="shared" si="4"/>
+        <v>Unknown</v>
+      </c>
+      <c r="S144" t="s">
+        <v>609</v>
+      </c>
+      <c r="T144" t="s">
+        <v>939</v>
+      </c>
+      <c r="U144" t="str">
+        <f t="shared" si="5"/>
+        <v>Unknown</v>
+      </c>
+    </row>
+    <row r="145" spans="2:21">
       <c r="B145" t="s">
         <v>475</v>
       </c>
@@ -31273,6 +34664,26 @@
       </c>
       <c r="L145" t="s">
         <v>781</v>
+      </c>
+      <c r="O145" t="s">
+        <v>610</v>
+      </c>
+      <c r="P145" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q145" t="str">
+        <f t="shared" si="4"/>
+        <v>Unknown</v>
+      </c>
+      <c r="S145" t="s">
+        <v>610</v>
+      </c>
+      <c r="T145" t="s">
+        <v>939</v>
+      </c>
+      <c r="U145" t="str">
+        <f t="shared" si="5"/>
+        <v>Unknown</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_NGA_grids_kan/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_NGA_grids_kan/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NGA_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AA1A6AB4-3624-42D3-B442-A54D5249DA2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B96AD263-768F-4677-98D6-75F4ADA15286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3340,7 +3340,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB33D683-33F5-40E1-9503-C46345F64118}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70F70D5C-7E83-49BD-9DBA-671211EB6DC2}">
   <dimension ref="B9:H145"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -22557,7 +22557,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28C43500-B4C7-4EA5-8CC8-66ED43B0A11D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB24B721-A272-438A-8E4C-C9B44FAD93BA}">
   <dimension ref="B9:L145"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
